--- a/bancos/SISOR/BASE_DETALHAMENTO_OBRAS.xlsx
+++ b/bancos/SISOR/BASE_DETALHAMENTO_OBRAS.xlsx
@@ -2757,7 +2757,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>ATENDIMENTOS ESCOLAS ESTADUAIS - CAIXAS ESCOLARES E CONVÊNIOS</t>
+          <t>OBRA - PROBLEMAS ESTRUTURAIS, ALÉM DE REFORMA E AMPLIAÇÃO DO PRÉDIO EE DR LAURO CORREA DO AMARAL</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2772,6 +2772,22 @@
         <is>
           <t>Sim</t>
         </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Região Intermediária de Varginha</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>GUAPÉ</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>387600</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2801,7 +2817,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>OBRA - PROBLEMAS ESTRUTURAIS, ALÉM DE REFORMA E AMPLIAÇÃO DO PRÉDIO EE DR LAURO CORREA DO AMARAL</t>
+          <t>CONCLUSÃO DA OBRA DE CONTENÇÃO DE TALUDE E RECUPERAÇÕES NA CONSTRUÇÃO EE ANTÔNIO MARINHO CAMPOS</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2819,16 +2835,16 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Região Intermediária de Varginha</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>GUAPÉ</t>
+          <t>IBIRITÉ</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>387600</v>
+        <v>361760</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -2861,7 +2877,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>CONCLUSÃO DA OBRA DE CONTENÇÃO DE TALUDE E RECUPERAÇÕES NA CONSTRUÇÃO EE ANTÔNIO MARINHO CAMPOS</t>
+          <t>OBRA DE CONTENÇÃO, REFORMA E REFORÇO ESTRUTURAL DO PRÉDIO EE ANTÔNIO PAPINI</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2879,16 +2895,16 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Ipatinga</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>IBIRITÉ</t>
+          <t>JOÃO MONLEVADE</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>361760</v>
+        <v>218500</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
@@ -2921,7 +2937,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>OBRA DE CONTENÇÃO, REFORMA E REFORÇO ESTRUTURAL DO PRÉDIO EE ANTÔNIO PAPINI</t>
+          <t>OBRA PARA REFORMA/RESTAURAÇÃO E  REPAROS ESTRUTURAIS EE DUQUE DE CAXIAS</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2939,16 +2955,16 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Região Intermediária de Ipatinga</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>JOÃO MONLEVADE</t>
+          <t>JUIZ DE FORA</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>218500</v>
+        <v>1976000</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -2981,7 +2997,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>OBRA PARA REFORMA/RESTAURAÇÃO E  REPAROS ESTRUTURAIS EE DUQUE DE CAXIAS</t>
+          <t>OBRA DE CONSTRUÇÃO DA SEDESEDE DA SRE DE MONTES CLAROS</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -2999,16 +3015,16 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Montes Claros</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>JUIZ DE FORA</t>
+          <t>MONTES CLAROS</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>1976000</v>
+        <v>805600</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -3041,7 +3057,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>OBRA DE CONSTRUÇÃO DA SEDESEDE DA SRE DE MONTES CLAROS</t>
+          <t>OBRAS DE CONTENÇÃO EE AUGUSTO DE LIMA</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3059,16 +3075,16 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Região Intermediária de Montes Claros</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>MONTES CLAROS</t>
+          <t>NOVA LIMA</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>805600</v>
+        <v>760000</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -3101,7 +3117,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>OBRAS DE CONTENÇÃO EE AUGUSTO DE LIMA</t>
+          <t>OBRA PARA SOLUÇÃO DE PROBLEMAS  ESTRUTURAIS NO EDIFÍCIO, INCLUINDO INFILTRAÇÃO NAS PAREDES, DETERIORAÇÃO DO GUARDA-CORPO NA FACHADA, ABATIMENTO NO PISO, ASSOALHO DANIFICADO E INCLINAÇÃO DA FACHADA.EE PROFESSOR PINHEIRO CAMPOS</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3119,16 +3135,16 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Divinópolis</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>NOVA LIMA</t>
+          <t>OLIVEIRA</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>760000</v>
+        <v>653600</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -3161,12 +3177,12 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>OBRA PARA SOLUÇÃO DE PROBLEMAS  ESTRUTURAIS NO EDIFÍCIO, INCLUINDO INFILTRAÇÃO NAS PAREDES, DETERIORAÇÃO DO GUARDA-CORPO NA FACHADA, ABATIMENTO NO PISO, ASSOALHO DANIFICADO E INCLINAÇÃO DA FACHADA.EE PROFESSOR PINHEIRO CAMPOS</t>
+          <t>REFORMA GERAL E RESTAURAÇÃO EE DOM PEDRO II</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="M45" t="n">
@@ -3179,16 +3195,16 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Região Intermediária de Divinópolis</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>OLIVEIRA</t>
+          <t>OURO PRETO</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>653600</v>
+        <v>1204600</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
@@ -3221,12 +3237,12 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>REFORMA GERAL E RESTAURAÇÃO EE DOM PEDRO II</t>
+          <t>OBRA PARA RESTAURAÇÃO EE PROFESSOR ANTÔNIO DIAS MACIEL</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="M46" t="n">
@@ -3239,16 +3255,16 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Patos de Minas</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>OURO PRETO</t>
+          <t>PATOS DE MINAS</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>1204600</v>
+        <v>1927740</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
@@ -3281,7 +3297,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>OBRA PARA RESTAURAÇÃO EE PROFESSOR ANTÔNIO DIAS MACIEL</t>
+          <t>OBRA RESTAURAÇÃO INSTITUTO DE EDUCAÇÃO DE JUIZ DE FORA</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3299,16 +3315,16 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Região Intermediária de Patos de Minas</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>PATOS DE MINAS</t>
+          <t>JUIZ DE FORA</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>1927740</v>
+        <v>653600</v>
       </c>
       <c r="R47" t="n">
         <v>0</v>
@@ -3341,7 +3357,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>OBRA RESTAURAÇÃO INSTITUTO DE EDUCAÇÃO DE JUIZ DE FORA</t>
+          <t>OBRA - PROBLEMAS REFERENTES À CONTENÇÃO DE TALUDE E DRENAGEM PLUVIALEE HENRIQUE BURNIER</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3368,7 +3384,7 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>653600</v>
+        <v>19000</v>
       </c>
       <c r="R48" t="n">
         <v>0</v>
@@ -3401,7 +3417,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>OBRA - PROBLEMAS REFERENTES À CONTENÇÃO DE TALUDE E DRENAGEM PLUVIALEE HENRIQUE BURNIER</t>
+          <t>OBRA - PROBLEMAS REFERENTES À CONTENÇÃO DE TALUDE E DRENAGEM PLUVIALEE BATISTA DE OLIVEIRA</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3461,7 +3477,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>OBRA - PROBLEMAS REFERENTES À CONTENÇÃO DE TALUDE E DRENAGEM PLUVIALEE BATISTA DE OLIVEIRA</t>
+          <t>OBRA REFORMA, RESTAURAÇÃO E AMPLIAÇÃOEE ANA ROCHA (PREDIO EE FREI LEOPOLDO)</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3479,16 +3495,16 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Patos de Minas</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>JUIZ DE FORA</t>
+          <t>MATUTINA</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>19000</v>
+        <v>1318600</v>
       </c>
       <c r="R50" t="n">
         <v>0</v>
@@ -3521,12 +3537,12 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>OBRA REFORMA, RESTAURAÇÃO E AMPLIAÇÃOEE ANA ROCHA (PREDIO EE FREI LEOPOLDO)</t>
+          <t>OBRA PARA REFORMA DA EDIFICAÇÃO E EXECUÇÃO DAS OBRAS DE ESTABILIZAÇÃO DE TALUDE, REFORÇO DA CONTENÇÃO E CONSTRUÇÃO DE NOVO MURO DE DIVISA EE JULIETA DE OLIVEIRA MACEDO</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="M51" t="n">
@@ -3539,16 +3555,16 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Região Intermediária de Patos de Minas</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>MATUTINA</t>
+          <t>MURIAÉ</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>1318600</v>
+        <v>653600</v>
       </c>
       <c r="R51" t="n">
         <v>0</v>
@@ -3581,12 +3597,12 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>OBRA PARA REFORMA DA EDIFICAÇÃO E EXECUÇÃO DAS OBRAS DE ESTABILIZAÇÃO DE TALUDE, REFORÇO DA CONTENÇÃO E CONSTRUÇÃO DE NOVO MURO DE DIVISA EE JULIETA DE OLIVEIRA MACEDO</t>
+          <t>CONSTRUÇÃO DE PRÉDIO DA SEDE DA SRE DE MURIAÉ</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="M52" t="n">
@@ -3608,7 +3624,7 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>653600</v>
+        <v>19000</v>
       </c>
       <c r="R52" t="n">
         <v>0</v>
@@ -3641,7 +3657,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>CONSTRUÇÃO DE PRÉDIO DA SEDE DA SRE DE MURIAÉ</t>
+          <t>OBRA DE REFORMA SEDE DA SRE DE NOVA ERA</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3659,12 +3675,12 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Ipatinga</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>MURIAÉ</t>
+          <t>NOVA ERA</t>
         </is>
       </c>
       <c r="Q53" t="n">
@@ -3701,7 +3717,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>OBRA DE REFORMA SEDE DA SRE DE NOVA ERA</t>
+          <t>OBRAS PARA PROBLEMAS ESTRUTURAIS NO AUDITÓRIO (ESTRUTURA PISO E TELHADO) - REFORMA GERAL E RESTAURAÇÃO - PRÉDIO TOMBADOEE FRANCISCO FERNANDES</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3719,16 +3735,16 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Região Intermediária de Ipatinga</t>
+          <t>Região Intermediária de Divinópolis</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>NOVA ERA</t>
+          <t>OLIVEIRA</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>19000</v>
+        <v>760000</v>
       </c>
       <c r="R54" t="n">
         <v>0</v>
@@ -3761,7 +3777,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>OBRAS PARA PROBLEMAS ESTRUTURAIS NO AUDITÓRIO (ESTRUTURA PISO E TELHADO) - REFORMA GERAL E RESTAURAÇÃO - PRÉDIO TOMBADOEE FRANCISCO FERNANDES</t>
+          <t xml:space="preserve">OBRA PARA REFORMA GERAL / RESTAURAÇÃO EE CONSELHEIRO AFONSO PENA </t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3779,16 +3795,16 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Região Intermediária de Divinópolis</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>OLIVEIRA</t>
+          <t>PARAOPEBA</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>760000</v>
+        <v>19000</v>
       </c>
       <c r="R55" t="n">
         <v>0</v>
@@ -3821,7 +3837,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBRA PARA REFORMA GERAL / RESTAURAÇÃO EE CONSELHEIRO AFONSO PENA </t>
+          <t>OBRA PARA RESTAURAÇÃOEE DOM LUSTOSA</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3839,12 +3855,12 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Patos de Minas</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>PARAOPEBA</t>
+          <t>PATROCÍNIO</t>
         </is>
       </c>
       <c r="Q56" t="n">
@@ -3881,7 +3897,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>OBRA PARA RESTAURAÇÃOEE DOM LUSTOSA</t>
+          <t>OBRA DE RESTAURAÇÃOSEDE DA SRE DE PATROCÍNIO</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3941,7 +3957,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>OBRA DE RESTAURAÇÃOSEDE DA SRE DE PATROCÍNIO</t>
+          <t>OBRA PARA REFORMA E RESTAURAÇÃO DO PRÉDIOEE FRANCISCA BOTELHO</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -3959,16 +3975,16 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Região Intermediária de Patos de Minas</t>
+          <t>Região Intermediária de Divinópolis</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>PATROCÍNIO</t>
+          <t>PITANGUI</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>19000</v>
+        <v>434720</v>
       </c>
       <c r="R58" t="n">
         <v>0</v>
@@ -4001,7 +4017,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>OBRA PARA REFORMA E RESTAURAÇÃO DO PRÉDIOEE FRANCISCA BOTELHO</t>
+          <t>OBRA  DE REFORMA E RESTAURAÇÃOCESEC TANCREDO NEVES (PRÉDIO OCUPADO ANTERIORMENTE PELA EE FARNESE MACIEL )</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4019,16 +4035,16 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Região Intermediária de Divinópolis</t>
+          <t>Região Intermediária de Patos de Minas</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>PITANGUI</t>
+          <t>PRESIDENTE OLEGÁRIO</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>434720</v>
+        <v>221160</v>
       </c>
       <c r="R59" t="n">
         <v>0</v>
@@ -4061,7 +4077,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>OBRA  DE REFORMA E RESTAURAÇÃOCESEC TANCREDO NEVES (PRÉDIO OCUPADO ANTERIORMENTE PELA EE FARNESE MACIEL )</t>
+          <t>CONCLUSÃO DA OBRA DE REFORMA E RESTAURAÇÃO EE JOAO DOS SANTOS</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4079,16 +4095,16 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>Região Intermediária de Patos de Minas</t>
+          <t>Região Intermediária de Barbacena</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>PRESIDENTE OLEGÁRIO</t>
+          <t>SÃO JOÃO DEL REI</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>221160</v>
+        <v>1748000</v>
       </c>
       <c r="R60" t="n">
         <v>0</v>
@@ -4121,7 +4137,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>CONCLUSÃO DA OBRA DE REFORMA E RESTAURAÇÃO EE JOAO DOS SANTOS</t>
+          <t>OBRA PARA SOLUÇÃO DE PROBLEMAS ESTRUTURAISSEDE DA SRE DE SETE LAGOAS</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4139,16 +4155,16 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>Região Intermediária de Barbacena</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>SÃO JOÃO DEL REI</t>
+          <t>SETE LAGOAS</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>1748000</v>
+        <v>479560</v>
       </c>
       <c r="R61" t="n">
         <v>0</v>
@@ -4181,7 +4197,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>OBRA PARA SOLUÇÃO DE PROBLEMAS ESTRUTURAISSEDE DA SRE DE SETE LAGOAS</t>
+          <t>OBRA PARA REPAROS ESTRUTURAIS (EXECUÇÃO DO REFORÇO DE FUNDAÇÃO E SERVIÇOS CORRELATOS) - 1A ETAPAEE DEPUTADO CARLOS PEIXOTO FILHO</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -4199,16 +4215,16 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>SETE LAGOAS</t>
+          <t>UBÁ</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>479560</v>
+        <v>228000</v>
       </c>
       <c r="R62" t="n">
         <v>0</v>
@@ -4241,12 +4257,12 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>OBRA PARA REPAROS ESTRUTURAIS (EXECUÇÃO DO REFORÇO DE FUNDAÇÃO E SERVIÇOS CORRELATOS) - 1A ETAPAEE DEPUTADO CARLOS PEIXOTO FILHO</t>
+          <t>CONSTRUÇÃO DE ESCOLA - 16 SALAS DE AULA (NO BAIRRO JARDIM CÉLIA)EE 13 DE MAIO</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="M63" t="n">
@@ -4259,16 +4275,16 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Uberlândia</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>UBÁ</t>
+          <t>UBERLÂNDIA</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>228000</v>
+        <v>2552080</v>
       </c>
       <c r="R63" t="n">
         <v>0</v>
@@ -4301,12 +4317,12 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>CONSTRUÇÃO DE ESCOLA - 16 SALAS DE AULA (NO BAIRRO JARDIM CÉLIA)EE 13 DE MAIO</t>
+          <t>REFORMA / REFORÇO ESTRUTURALEE CORAÇÃO DE JESUS</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="M64" t="n">
@@ -4319,16 +4335,16 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberlândia</t>
+          <t>Região Intermediária de Varginha</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>UBERLÂNDIA</t>
+          <t>VARGINHA</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>2552080</v>
+        <v>1386240</v>
       </c>
       <c r="R64" t="n">
         <v>0</v>
@@ -4361,7 +4377,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>REFORMA / REFORÇO ESTRUTURALEE CORAÇÃO DE JESUS</t>
+          <t>OBRA PARA REFORMA/RESTAURAÇÃO EE BRASIL</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4388,7 +4404,7 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>1386240</v>
+        <v>1900000</v>
       </c>
       <c r="R65" t="n">
         <v>0</v>
@@ -4421,7 +4437,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>OBRA PARA REFORMA/RESTAURAÇÃO EE BRASIL</t>
+          <t>OBRA DE REFORMA E RESTAURAÇÃOEE DR. JOÃO PINHEIRO</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -4444,11 +4460,11 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>VARGINHA</t>
+          <t>SÃO GONÇALO DO SAPUCAÍ</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>1900000</v>
+        <v>1008140</v>
       </c>
       <c r="R66" t="n">
         <v>0</v>
@@ -4481,7 +4497,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>OBRA DE REFORMA E RESTAURAÇÃOEE DR. JOÃO PINHEIRO</t>
+          <t>OBRAS PARA MURO DE ARRIMO E DRENAGEM, ALÉM DE REFORMA/RESTAURAÇÃO EE MINISTRO EDMUNDO LINS</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4499,16 +4515,16 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>Região Intermediária de Varginha</t>
+          <t>Região Intermediária de Teófilo Otoni</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>SÃO GONÇALO DO SAPUCAÍ</t>
+          <t>SERRO</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>1008140</v>
+        <v>380000</v>
       </c>
       <c r="R67" t="n">
         <v>0</v>
@@ -4541,7 +4557,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>OBRAS PARA MURO DE ARRIMO E DRENAGEM, ALÉM DE REFORMA/RESTAURAÇÃO EE MINISTRO EDMUNDO LINS</t>
+          <t>OBRA PARA REFORMA E RESTAURAÇÃOEE DR. ARTHUR BERNARDES</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4559,16 +4575,16 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Região Intermediária de Teófilo Otoni</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>SERRO</t>
+          <t>SETE LAGOAS</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>380000</v>
+        <v>228000</v>
       </c>
       <c r="R68" t="n">
         <v>0</v>
@@ -4601,7 +4617,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>OBRA PARA REFORMA E RESTAURAÇÃOEE DR. ARTHUR BERNARDES</t>
+          <t>OBRA PARA SOLUÇÃO DE PROBLEMAS ESTRUTURAISEE HAYDÉE DE SOUZA ABREU</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4619,16 +4635,16 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Ipatinga</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>SETE LAGOAS</t>
+          <t>TIMÓTEO</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>228000</v>
+        <v>539600</v>
       </c>
       <c r="R69" t="n">
         <v>0</v>
@@ -4661,7 +4677,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>OBRA PARA SOLUÇÃO DE PROBLEMAS ESTRUTURAISEE HAYDÉE DE SOUZA ABREU</t>
+          <t>OBRA - MANUTENÇÃO E REVISÃO COMPLETA DAS COBERTURAS; PINTURA EXTERNA E INTERNA; RESTAURO DE ESQUADRIAS;  REVISÃO DE TODA A REDE ELÉTRICA; RESTAURO DA PINTURA ARTÍSTICA DO RODATETO E PROSPECÇÃO EXPLORATÓRIA NO HALL DE ENTRADA, VISANDO AVALIAR A EXISTÊ</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4679,16 +4695,16 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>Região Intermediária de Ipatinga</t>
+          <t>Região Intermediária de Uberlândia</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>TIMÓTEO</t>
+          <t>UBERLÂNDIA</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>539600</v>
+        <v>19000</v>
       </c>
       <c r="R70" t="n">
         <v>0</v>
@@ -4721,12 +4737,12 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>OBRA - MANUTENÇÃO E REVISÃO COMPLETA DAS COBERTURAS; PINTURA EXTERNA E INTERNA; RESTAURO DE ESQUADRIAS;  REVISÃO DE TODA A REDE ELÉTRICA; RESTAURO DA PINTURA ARTÍSTICA DO RODATETO E PROSPECÇÃO EXPLORATÓRIA NO HALL DE ENTRADA, VISANDO AVALIAR A EXISTÊ</t>
+          <t>OBRA PARA RESTAURAÇÃO EE AFONSO PENA</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="M71" t="n">
@@ -4739,16 +4755,16 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberlândia</t>
+          <t>Região Intermediária de Varginha</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>UBERLÂNDIA</t>
+          <t>VARGINHA</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>19000</v>
+        <v>2074800</v>
       </c>
       <c r="R71" t="n">
         <v>0</v>
@@ -4756,32 +4772,35 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>1261</v>
+        <v>1301</v>
       </c>
       <c r="B72" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C72" t="n">
-        <v>368</v>
+        <v>451</v>
       </c>
       <c r="D72" t="n">
-        <v>168</v>
+        <v>81</v>
       </c>
       <c r="E72" t="n">
-        <v>4519</v>
+        <v>1037</v>
       </c>
       <c r="F72" t="n">
         <v>1</v>
       </c>
       <c r="G72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H72" t="n">
         <v>71</v>
       </c>
+      <c r="I72" t="n">
+        <v>12404</v>
+      </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>OBRA PARA RESTAURAÇÃO EE AFONSO PENA</t>
+          <t>DC-018/2023-Execução das serviço de Aumento de capacidade e Recuperação de Rodovia (aumento de capacidade) no trecho Três Pontas - Varginhas (Estaca 80 a 610), com 10,60 km de extensão, na Rodovia MG-167</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4789,12 +4808,9 @@
           <t>EXECUÇÃO</t>
         </is>
       </c>
-      <c r="M72" t="n">
-        <v>1</v>
-      </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -4804,14 +4820,14 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>VARGINHA</t>
+          <t>TRÊS PONTAS</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>2074800</v>
+        <v>280106</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>519640</v>
       </c>
     </row>
     <row r="73">
@@ -4840,11 +4856,11 @@
         <v>72</v>
       </c>
       <c r="I73" t="n">
-        <v>12404</v>
+        <v>12780</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>DC-018/2023-Execução das serviço de Aumento de capacidade e Recuperação de Rodovia (aumento de capacidade) no trecho Três Pontas - Varginhas (Estaca 80 a 610), com 10,60 km de extensão, na Rodovia MG-167</t>
+          <t>Execução das obras de Implantação de Passarela na Rodovia MG-010, Km 15+850, trecho Belo Horizonte - Lagoa Santa (Cidade Administrativa), extensão de 312,00 m</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -4859,19 +4875,19 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>Região Intermediária de Varginha</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>TRÊS PONTAS</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>280106</v>
+        <v>894720</v>
       </c>
       <c r="R73" t="n">
-        <v>519640</v>
+        <v>4087644</v>
       </c>
     </row>
     <row r="74">
@@ -4900,11 +4916,11 @@
         <v>73</v>
       </c>
       <c r="I74" t="n">
-        <v>12780</v>
+        <v>10397</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Execução das obras de Implantação de Passarela na Rodovia MG-010, Km 15+850, trecho Belo Horizonte - Lagoa Santa (Cidade Administrativa), extensão de 312,00 m</t>
+          <t>PRC-22.021/18 -Melhoramento e pavimentação no trecho Ibertioga  Piedade do Rio Grande, na Rodovia MG/338, extensão de 13,25km</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -4919,19 +4935,19 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Barbacena</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>IBERTIOGA</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>894720</v>
+        <v>8264640</v>
       </c>
       <c r="R74" t="n">
-        <v>4087644</v>
+        <v>19153735</v>
       </c>
     </row>
     <row r="75">
@@ -4960,11 +4976,11 @@
         <v>74</v>
       </c>
       <c r="I75" t="n">
-        <v>10397</v>
+        <v>12850</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>PRC-22.021/18 -Melhoramento e pavimentação no trecho Ibertioga  Piedade do Rio Grande, na Rodovia MG/338, extensão de 13,25km</t>
+          <t>Melhoramento e pavimentação do trecho de Jaboticatubas - Lagoa Santa, em rodovia Municipal.</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -4979,19 +4995,19 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>Região Intermediária de Barbacena</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>IBERTIOGA</t>
+          <t>JABOTICATUBAS</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>8264640</v>
+        <v>3155040</v>
       </c>
       <c r="R75" t="n">
-        <v>19153735</v>
+        <v>23943007</v>
       </c>
     </row>
     <row r="76">
@@ -5020,11 +5036,11 @@
         <v>75</v>
       </c>
       <c r="I76" t="n">
-        <v>12850</v>
+        <v>12634</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Melhoramento e pavimentação do trecho de Jaboticatubas - Lagoa Santa, em rodovia Municipal.</t>
+          <t>Melhoramento e pavimentação do Trecho Itapagipe - Entrº 364 (Campina Verde) MGC 154 - LOTE 01</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -5039,19 +5055,19 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Uberaba</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>JABOTICATUBAS</t>
+          <t>ITAPAGIPE</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>3155040</v>
+        <v>4840800</v>
       </c>
       <c r="R76" t="n">
-        <v>23943007</v>
+        <v>26593690</v>
       </c>
     </row>
     <row r="77">
@@ -5080,11 +5096,11 @@
         <v>76</v>
       </c>
       <c r="I77" t="n">
-        <v>12634</v>
+        <v>12785</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Melhoramento e pavimentação do Trecho Itapagipe - Entrº 364 (Campina Verde) MGC 154 - LOTE 01</t>
+          <t>Execução da Obra de Engenharia de Melhoramento e pavimentação da Interseção de acesso ao Presídio de Iturama, na via Municipal, com extensão de 2,000 km.</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5104,14 +5120,14 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>ITAPAGIPE</t>
+          <t>ITURAMA</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>4840800</v>
+        <v>613500</v>
       </c>
       <c r="R77" t="n">
-        <v>26593690</v>
+        <v>2870210</v>
       </c>
     </row>
     <row r="78">
@@ -5140,11 +5156,11 @@
         <v>77</v>
       </c>
       <c r="I78" t="n">
-        <v>12785</v>
+        <v>12824</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Execução da Obra de Engenharia de Melhoramento e pavimentação da Interseção de acesso ao Presídio de Iturama, na via Municipal, com extensão de 2,000 km.</t>
+          <t>Melhoramento e Pavimentação em Rodovia de Ligação no trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 - Segmento 1 (0 a 835), extensão: 16,700 km e Segmento 2 (835 a 1250), extensão 8,300 km.</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -5159,19 +5175,19 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberaba</t>
+          <t>Região Intermediária de Patos de Minas</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>ITURAMA</t>
+          <t>PARACATU</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>613500</v>
+        <v>5963400</v>
       </c>
       <c r="R78" t="n">
-        <v>2870210</v>
+        <v>23280000</v>
       </c>
     </row>
     <row r="79">
@@ -5200,11 +5216,11 @@
         <v>78</v>
       </c>
       <c r="I79" t="n">
-        <v>12824</v>
+        <v>4716</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Melhoramento e Pavimentação em Rodovia de Ligação no trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 - Segmento 1 (0 a 835), extensão: 16,700 km e Segmento 2 (835 a 1250), extensão 8,300 km.</t>
+          <t>Entr. BR/365-Entr. LMG/782 (p/ Iraí de Minas), Monte Carmelo-Chapada de Minas e Pindaibas-Ent.BR/365</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -5219,19 +5235,19 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>Região Intermediária de Patos de Minas</t>
+          <t>Região Intermediária de Uberlândia</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>PARACATU</t>
+          <t>MONTE CARMELO</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>5963400</v>
+        <v>3620820</v>
       </c>
       <c r="R79" t="n">
-        <v>23280000</v>
+        <v>19100000</v>
       </c>
     </row>
     <row r="80">
@@ -5259,17 +5275,14 @@
       <c r="H80" t="n">
         <v>79</v>
       </c>
-      <c r="I80" t="n">
-        <v>4716</v>
-      </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Entr. BR/365-Entr. LMG/782 (p/ Iraí de Minas), Monte Carmelo-Chapada de Minas e Pindaibas-Ent.BR/365</t>
+          <t>Recapeamento de vias / pavimentação de trecho rodoviário / pavimentação e obra de arte especial no trecho viário; para melhoria da infraestrutura viária do Estado de Minas Gerais (8 propostas de novos convênios)</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -5279,19 +5292,19 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberlândia</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>MONTE CARMELO</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>3620820</v>
+        <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>19100000</v>
+        <v>11755000</v>
       </c>
     </row>
     <row r="81">
@@ -5305,10 +5318,10 @@
         <v>451</v>
       </c>
       <c r="D81" t="n">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="E81" t="n">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="F81" t="n">
         <v>1</v>
@@ -5319,14 +5332,17 @@
       <c r="H81" t="n">
         <v>80</v>
       </c>
+      <c r="I81" t="n">
+        <v>11140</v>
+      </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Recapeamento de vias / pavimentação de trecho rodoviário / pavimentação e obra de arte especial no trecho viário; para melhoria da infraestrutura viária do Estado de Minas Gerais (8 propostas de novos convênios)</t>
+          <t xml:space="preserve">CONSTRUÇÃO DE 64 UNIDADES HABITACIONAIS PAC FNHIS </t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -5336,19 +5352,19 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>CONTAGEM</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>1839798</v>
       </c>
       <c r="R81" t="n">
-        <v>11755000</v>
+        <v>3269655</v>
       </c>
     </row>
     <row r="82">
@@ -5377,11 +5393,11 @@
         <v>81</v>
       </c>
       <c r="I82" t="n">
-        <v>11140</v>
+        <v>11531</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONSTRUÇÃO DE 64 UNIDADES HABITACIONAIS PAC FNHIS </t>
+          <t>REQUALIFICAÇÃO URBANA E AMBIENTAL DO RIBEIRÃO ARRUDAS - FNHIS/2009 - Continuidade da execução do PTTS (Programa de Trabalho Técnico-Social)</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -5405,10 +5421,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>1839798</v>
+        <v>222899</v>
       </c>
       <c r="R82" t="n">
-        <v>3269655</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -5425,7 +5441,7 @@
         <v>99</v>
       </c>
       <c r="E83" t="n">
-        <v>1038</v>
+        <v>4262</v>
       </c>
       <c r="F83" t="n">
         <v>1</v>
@@ -5436,12 +5452,9 @@
       <c r="H83" t="n">
         <v>82</v>
       </c>
-      <c r="I83" t="n">
-        <v>11531</v>
-      </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>REQUALIFICAÇÃO URBANA E AMBIENTAL DO RIBEIRÃO ARRUDAS - FNHIS/2009 - Continuidade da execução do PTTS (Programa de Trabalho Técnico-Social)</t>
+          <t>Aquisição de materiais para obras - mata-burros, vigas metálicas e bueiros metálicos</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -5456,16 +5469,16 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>CONTAGEM</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>222899</v>
+        <v>10932874</v>
       </c>
       <c r="R83" t="n">
         <v>0</v>
@@ -5476,16 +5489,16 @@
         <v>1301</v>
       </c>
       <c r="B84" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C84" t="n">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D84" t="n">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="E84" t="n">
-        <v>4262</v>
+        <v>4290</v>
       </c>
       <c r="F84" t="n">
         <v>1</v>
@@ -5496,9 +5509,12 @@
       <c r="H84" t="n">
         <v>83</v>
       </c>
+      <c r="I84" t="n">
+        <v>12510</v>
+      </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Aquisição de materiais para obras - mata-burros, vigas metálicas e bueiros metálicos</t>
+          <t xml:space="preserve"> tratamento viário para implantação de sistema BRS em dois corredores de importância metropolitana na Região Metropolitana de Belo Horizonte (RMBH)</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -5513,19 +5529,19 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>10932874</v>
+        <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>0</v>
+        <v>40000000</v>
       </c>
     </row>
     <row r="85">
@@ -5553,17 +5569,14 @@
       <c r="H85" t="n">
         <v>84</v>
       </c>
-      <c r="I85" t="n">
-        <v>12510</v>
-      </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t xml:space="preserve"> tratamento viário para implantação de sistema BRS em dois corredores de importância metropolitana na Região Metropolitana de Belo Horizonte (RMBH)</t>
+          <t>Pagamento reajuste previsão INCC - Contrato de repasse 970648 (PAC MOBILIDADE - Obra Av Brasília)</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -5582,10 +5595,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>0</v>
+        <v>478579</v>
       </c>
       <c r="R85" t="n">
-        <v>40000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -5615,7 +5628,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Pagamento reajuste previsão INCC - Contrato de repasse 970648 (PAC MOBILIDADE - Obra Av Brasília)</t>
+          <t>Pagamento reajuste previsão INCC - Contrato de repasse 970648 (PAC MOBILIDADE - Obra Av Civilização/Vilarinho)</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -5639,7 +5652,7 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>478579</v>
+        <v>2246479</v>
       </c>
       <c r="R86" t="n">
         <v>0</v>
@@ -5672,7 +5685,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Pagamento reajuste previsão INCC - Contrato de repasse 970648 (PAC MOBILIDADE - Obra Av Civilização/Vilarinho)</t>
+          <t>Pagamento reajuste previsão INCC - Contrato de repasse 970648 (PAC MOBILIDADE -  Obras Estações  BRT MG10)</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -5696,7 +5709,7 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>2246479</v>
+        <v>156926</v>
       </c>
       <c r="R87" t="n">
         <v>0</v>
@@ -5707,16 +5720,16 @@
         <v>1301</v>
       </c>
       <c r="B88" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C88" t="n">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D88" t="n">
-        <v>117</v>
+        <v>139</v>
       </c>
       <c r="E88" t="n">
-        <v>4290</v>
+        <v>1036</v>
       </c>
       <c r="F88" t="n">
         <v>1</v>
@@ -5727,14 +5740,17 @@
       <c r="H88" t="n">
         <v>87</v>
       </c>
+      <c r="I88" t="n">
+        <v>12453</v>
+      </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Pagamento reajuste previsão INCC - Contrato de repasse 970648 (PAC MOBILIDADE -  Obras Estações  BRT MG10)</t>
+          <t>LOTE 1 EXECUCAO DAS OBRAS DE ESTABILIZACAO E CONTENCAO DE ENCOSTAS EM AREAS URBANAS EM ALEM PARAIBA</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -5744,19 +5760,19 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>ALÉM PARAÍBA</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>156926</v>
+        <v>0</v>
       </c>
       <c r="R88" t="n">
-        <v>0</v>
+        <v>539924</v>
       </c>
     </row>
     <row r="89">
@@ -5785,11 +5801,11 @@
         <v>88</v>
       </c>
       <c r="I89" t="n">
-        <v>12453</v>
+        <v>12454</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>LOTE 1 EXECUCAO DAS OBRAS DE ESTABILIZACAO E CONTENCAO DE ENCOSTAS EM AREAS URBANAS EM ALEM PARAIBA</t>
+          <t>LOTE  2 -  EXECUCAO DAS OBRAS DE ESTABILIZACAO E CONTENCAO DE ENCOSTAS EM AREAS URBANAS EM MURIAE</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -5809,14 +5825,14 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>ALÉM PARAÍBA</t>
+          <t>MURIAÉ</t>
         </is>
       </c>
       <c r="Q89" t="n">
         <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>539924</v>
+        <v>15337533</v>
       </c>
     </row>
     <row r="90">
@@ -5845,11 +5861,11 @@
         <v>89</v>
       </c>
       <c r="I90" t="n">
-        <v>12454</v>
+        <v>11521</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>LOTE  2 -  EXECUCAO DAS OBRAS DE ESTABILIZACAO E CONTENCAO DE ENCOSTAS EM AREAS URBANAS EM MURIAE</t>
+          <t>Obras de contenção de encostas em Sabará - Intervenção em setores de risco alto e muito alto, no âmbito do Programa PAC Gestão de Riscos e Resposta a Desastres.</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -5864,19 +5880,19 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>MURIAÉ</t>
+          <t>SABARÁ</t>
         </is>
       </c>
       <c r="Q90" t="n">
         <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>15337533</v>
+        <v>1440021</v>
       </c>
     </row>
     <row r="91">
@@ -5905,11 +5921,11 @@
         <v>90</v>
       </c>
       <c r="I91" t="n">
-        <v>11521</v>
+        <v>11519</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Obras de contenção de encostas em Sabará - Intervenção em setores de risco alto e muito alto, no âmbito do Programa PAC Gestão de Riscos e Resposta a Desastres.</t>
+          <t>Obras de contenção de encostas em João Monlevade - Intervenção em setores de risco alto e muito alto, no âmbito do Programa PAC Gestão de Riscos e Resposta a Desastres.</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -5924,19 +5940,19 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Ipatinga</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>SABARÁ</t>
+          <t>JOÃO MONLEVADE</t>
         </is>
       </c>
       <c r="Q91" t="n">
         <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>1440021</v>
+        <v>6942767</v>
       </c>
     </row>
     <row r="92">
@@ -5965,16 +5981,16 @@
         <v>91</v>
       </c>
       <c r="I92" t="n">
-        <v>11519</v>
+        <v>11512</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Obras de contenção de encostas em João Monlevade - Intervenção em setores de risco alto e muito alto, no âmbito do Programa PAC Gestão de Riscos e Resposta a Desastres.</t>
+          <t>bras de contenção de encostas em Timóteo - Intervenção em setores de risco alto e muito alto, no âmbito do Programa PAC Gestão de Riscos e Respostas a Desastres.</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -5989,14 +6005,14 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>JOÃO MONLEVADE</t>
+          <t>TIMÓTEO</t>
         </is>
       </c>
       <c r="Q92" t="n">
         <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>6942767</v>
+        <v>14686005</v>
       </c>
     </row>
     <row r="93">
@@ -6025,16 +6041,16 @@
         <v>92</v>
       </c>
       <c r="I93" t="n">
-        <v>11512</v>
+        <v>11514</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>bras de contenção de encostas em Timóteo - Intervenção em setores de risco alto e muito alto, no âmbito do Programa PAC Gestão de Riscos e Respostas a Desastres.</t>
+          <t>Obras de Contenção de encostas em Ouro Preto - Intervenção em setores de risco alto e muito alto, no ambito do programa PAC gestão de riscos e resposta a desastres.</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -6044,19 +6060,19 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>Região Intermediária de Ipatinga</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>TIMÓTEO</t>
+          <t>OURO PRETO</t>
         </is>
       </c>
       <c r="Q93" t="n">
         <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>14686005</v>
+        <v>52160376</v>
       </c>
     </row>
     <row r="94">
@@ -6085,11 +6101,11 @@
         <v>93</v>
       </c>
       <c r="I94" t="n">
-        <v>11514</v>
+        <v>11511</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Obras de Contenção de encostas em Ouro Preto - Intervenção em setores de risco alto e muito alto, no ambito do programa PAC gestão de riscos e resposta a desastres.</t>
+          <t>Obras de Contenção de encostas em Manhumirim, Lajinha, Ervália,Sabinópolis e Diogo de Vasconcelos - Intervenção em setores de risco alto e muito alto. No ambito do Programa PAC gestão de riscos e proposta a desastres.</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -6104,19 +6120,19 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>OURO PRETO</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q94" t="n">
         <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>52160376</v>
+        <v>20521500</v>
       </c>
     </row>
     <row r="95">
@@ -6145,11 +6161,11 @@
         <v>94</v>
       </c>
       <c r="I95" t="n">
-        <v>11511</v>
+        <v>11520</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Obras de Contenção de encostas em Manhumirim, Lajinha, Ervália,Sabinópolis e Diogo de Vasconcelos - Intervenção em setores de risco alto e muito alto. No ambito do Programa PAC gestão de riscos e proposta a desastres.</t>
+          <t>Obras de contenção de encostas em Santa Luzia - Intervenção em setores de risco alto e muito alto, no âmbito do Programa PAC Gestão de Riscos e Resposta a Desastres.</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -6164,19 +6180,19 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>SANTA LUZIA</t>
         </is>
       </c>
       <c r="Q95" t="n">
         <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>20521500</v>
+        <v>6952445</v>
       </c>
     </row>
     <row r="96">
@@ -6205,11 +6221,11 @@
         <v>95</v>
       </c>
       <c r="I96" t="n">
-        <v>11520</v>
+        <v>11513</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Obras de contenção de encostas em Santa Luzia - Intervenção em setores de risco alto e muito alto, no âmbito do Programa PAC Gestão de Riscos e Resposta a Desastres.</t>
+          <t>Obras de Contenção de encostas em Ewbank da Câmara, Matias Barbosa e Visconde do Rio Branco - Intervenção em setores de risco alto e muito alto, no ambito do programa PAC gestão de riscos e proposta a desastre.</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -6224,19 +6240,19 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>SANTA LUZIA</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q96" t="n">
         <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>6952445</v>
+        <v>12959175</v>
       </c>
     </row>
     <row r="97">
@@ -6265,11 +6281,11 @@
         <v>96</v>
       </c>
       <c r="I97" t="n">
-        <v>11513</v>
+        <v>11977</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Obras de Contenção de encostas em Ewbank da Câmara, Matias Barbosa e Visconde do Rio Branco - Intervenção em setores de risco alto e muito alto, no ambito do programa PAC gestão de riscos e proposta a desastre.</t>
+          <t>Execução de Obras de Contenção de Encostas em Cataguases/MG - Intervenção em setores de risco alto e muito alto, no âmbito do programa PAC Gestão de Riscos e Resposta a Desastres.</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -6284,19 +6300,19 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>CATAGUASES</t>
         </is>
       </c>
       <c r="Q97" t="n">
         <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>12959175</v>
+        <v>38244490</v>
       </c>
     </row>
     <row r="98">
@@ -6325,11 +6341,11 @@
         <v>97</v>
       </c>
       <c r="I98" t="n">
-        <v>11977</v>
+        <v>11162</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Execução de Obras de Contenção de Encostas em Cataguases/MG - Intervenção em setores de risco alto e muito alto, no âmbito do programa PAC Gestão de Riscos e Resposta a Desastres.</t>
+          <t>OBRAS DE ESTABILIZAÇÃO E CONTENÇÃO DE ENCOSTAS E DESLIZAMENTOS EM ÁREAS URBANAS</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -6344,19 +6360,19 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>CATAGUASES</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>0</v>
+        <v>9858067</v>
       </c>
       <c r="R98" t="n">
-        <v>38244490</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -6373,7 +6389,7 @@
         <v>139</v>
       </c>
       <c r="E99" t="n">
-        <v>1036</v>
+        <v>1039</v>
       </c>
       <c r="F99" t="n">
         <v>1</v>
@@ -6385,11 +6401,11 @@
         <v>98</v>
       </c>
       <c r="I99" t="n">
-        <v>11162</v>
+        <v>12699</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>OBRAS DE ESTABILIZAÇÃO E CONTENÇÃO DE ENCOSTAS E DESLIZAMENTOS EM ÁREAS URBANAS</t>
+          <t>SERVIÇOS TÉCNICOS ESPECIALIZADOS PARA A CONCLUSÃO DA IMPLEMENTAÇÃO DO PTTS  PROJETO DE TRABALHO TÉCNICO SOCIAL- PROGRAMA DE REQUALIFICAÇÃO URBANA E AMBIENTAL E CONTROLE DE CHEIAS DO CÓRREGO FERRUGEM</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -6404,16 +6420,16 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>CONTAGEM</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>9858067</v>
+        <v>299895</v>
       </c>
       <c r="R99" t="n">
         <v>0</v>
@@ -6445,11 +6461,11 @@
         <v>99</v>
       </c>
       <c r="I100" t="n">
-        <v>12699</v>
+        <v>11536</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>SERVIÇOS TÉCNICOS ESPECIALIZADOS PARA A CONCLUSÃO DA IMPLEMENTAÇÃO DO PTTS  PROJETO DE TRABALHO TÉCNICO SOCIAL- PROGRAMA DE REQUALIFICAÇÃO URBANA E AMBIENTAL E CONTROLE DE CHEIAS DO CÓRREGO FERRUGEM</t>
+          <t>Construção de 192 unidades habitacionais referente a 2ª etapa da Requalificação urbana e ambiental do Córrego Ferrugem</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -6473,7 +6489,7 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>299895</v>
+        <v>4565604</v>
       </c>
       <c r="R100" t="n">
         <v>0</v>
@@ -6493,7 +6509,7 @@
         <v>139</v>
       </c>
       <c r="E101" t="n">
-        <v>1039</v>
+        <v>1041</v>
       </c>
       <c r="F101" t="n">
         <v>1</v>
@@ -6505,11 +6521,11 @@
         <v>100</v>
       </c>
       <c r="I101" t="n">
-        <v>11536</v>
+        <v>11855</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Construção de 192 unidades habitacionais referente a 2ª etapa da Requalificação urbana e ambiental do Córrego Ferrugem</t>
+          <t>REMANESCENTE DAS OBRAS DE INFRAESTRUTURA PARA A CONCLUSAO DAS BACIAS DO CONTROLE DE CHEIAS DO CORREGO RIACHO DAS PEDRAS.</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -6533,10 +6549,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>4565604</v>
+        <v>6286532</v>
       </c>
       <c r="R101" t="n">
-        <v>0</v>
+        <v>2728583</v>
       </c>
     </row>
     <row r="102">
@@ -6565,11 +6581,11 @@
         <v>101</v>
       </c>
       <c r="I102" t="n">
-        <v>11855</v>
+        <v>11973</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>REMANESCENTE DAS OBRAS DE INFRAESTRUTURA PARA A CONCLUSAO DAS BACIAS DO CONTROLE DE CHEIAS DO CORREGO RIACHO DAS PEDRAS.</t>
+          <t>execução do Plano de Trabalho Técnico-Social - PTTS, que é uma exigência do contrato de financiamento PAC RIACHO</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -6593,27 +6609,27 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>6286532</v>
+        <v>193263</v>
       </c>
       <c r="R102" t="n">
-        <v>2728583</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>1301</v>
+        <v>1371</v>
       </c>
       <c r="B103" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C103" t="n">
-        <v>451</v>
+        <v>511</v>
       </c>
       <c r="D103" t="n">
-        <v>139</v>
+        <v>101</v>
       </c>
       <c r="E103" t="n">
-        <v>1041</v>
+        <v>4118</v>
       </c>
       <c r="F103" t="n">
         <v>1</v>
@@ -6624,17 +6640,14 @@
       <c r="H103" t="n">
         <v>102</v>
       </c>
-      <c r="I103" t="n">
-        <v>11973</v>
-      </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>execução do Plano de Trabalho Técnico-Social - PTTS, que é uma exigência do contrato de financiamento PAC RIACHO</t>
+          <t>Programa Água Doce - RIMC</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -6644,19 +6657,19 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Montes Claros</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>CONTAGEM</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE MONTES CLAROS</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>193263</v>
+        <v>0</v>
       </c>
       <c r="R103" t="n">
-        <v>0</v>
+        <v>4547000</v>
       </c>
     </row>
     <row r="104">
@@ -6686,7 +6699,7 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Programa Água Doce - RIMC</t>
+          <t>Programa Água Doce - RITO</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -6701,12 +6714,12 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>Região Intermediária de Montes Claros</t>
+          <t>Região Intermediária de Teófilo Otoni</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE MONTES CLAROS</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE TEÓFILO OTONI</t>
         </is>
       </c>
       <c r="Q104" t="n">
@@ -6718,37 +6731,37 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>1371</v>
+        <v>1451</v>
       </c>
       <c r="B105" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="C105" t="n">
-        <v>511</v>
+        <v>421</v>
       </c>
       <c r="D105" t="n">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="E105" t="n">
-        <v>4118</v>
+        <v>1048</v>
       </c>
       <c r="F105" t="n">
         <v>1</v>
       </c>
       <c r="G105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H105" t="n">
         <v>104</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Programa Água Doce - RITO</t>
+          <t>Construção de uma unidade prisional de segurança média com aproximadamente 800 (oitocentas) vagas.</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>PARALISADO</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -6758,19 +6771,19 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>Região Intermediária de Teófilo Otoni</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE TEÓFILO OTONI</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>0</v>
+        <v>904245</v>
       </c>
       <c r="R105" t="n">
-        <v>4547000</v>
+        <v>44308050</v>
       </c>
     </row>
     <row r="106">
@@ -6781,13 +6794,13 @@
         <v>6</v>
       </c>
       <c r="C106" t="n">
-        <v>421</v>
+        <v>243</v>
       </c>
       <c r="D106" t="n">
-        <v>130</v>
+        <v>146</v>
       </c>
       <c r="E106" t="n">
-        <v>1048</v>
+        <v>4441</v>
       </c>
       <c r="F106" t="n">
         <v>1</v>
@@ -6800,7 +6813,7 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Construção de uma unidade prisional de segurança média com aproximadamente 800 (oitocentas) vagas.</t>
+          <t>Construção e implementação de modelos alternativos de prestação da Medida Socioeducativa de Privação de Liberdade no Estado de Minas Gerais.</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -6815,19 +6828,19 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>904245</v>
+        <v>6999284</v>
       </c>
       <c r="R106" t="n">
-        <v>44308050</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -6877,11 +6890,11 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>BETIM</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>6999284</v>
+        <v>651694</v>
       </c>
       <c r="R107" t="n">
         <v>0</v>
@@ -6929,12 +6942,12 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Varginha</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>BETIM</t>
+          <t>ALFENAS</t>
         </is>
       </c>
       <c r="Q108" t="n">
@@ -6986,16 +6999,16 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>Região Intermediária de Varginha</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>ALFENAS</t>
+          <t>CONTAGEM</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>651694</v>
+        <v>1472757</v>
       </c>
       <c r="R109" t="n">
         <v>0</v>
@@ -7043,16 +7056,16 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Uberaba</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>CONTAGEM</t>
+          <t>ARAXÁ</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>1472757</v>
+        <v>651694</v>
       </c>
       <c r="R110" t="n">
         <v>0</v>
@@ -7100,16 +7113,16 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberaba</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>ARAXÁ</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>651694</v>
+        <v>18572878</v>
       </c>
       <c r="R111" t="n">
         <v>0</v>
@@ -7117,37 +7130,37 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>1451</v>
+        <v>1501</v>
       </c>
       <c r="B112" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C112" t="n">
-        <v>243</v>
+        <v>122</v>
       </c>
       <c r="D112" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E112" t="n">
-        <v>4441</v>
+        <v>4476</v>
       </c>
       <c r="F112" t="n">
         <v>1</v>
       </c>
       <c r="G112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H112" t="n">
         <v>111</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>Construção e implementação de modelos alternativos de prestação da Medida Socioeducativa de Privação de Liberdade no Estado de Minas Gerais.</t>
+          <t>REDIMENSIONAMENTO DE REDE ELÉTRICA (NRPMSO`S) - Garantir a segurança elétrica para implementação de novos equipamentos</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>PARALISADO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -7157,16 +7170,16 @@
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>18572878</v>
+        <v>270000</v>
       </c>
       <c r="R112" t="n">
         <v>0</v>
@@ -7183,10 +7196,10 @@
         <v>122</v>
       </c>
       <c r="D113" t="n">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="E113" t="n">
-        <v>4476</v>
+        <v>4465</v>
       </c>
       <c r="F113" t="n">
         <v>1</v>
@@ -7199,7 +7212,7 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>REDIMENSIONAMENTO DE REDE ELÉTRICA (NRPMSO`S) - Garantir a segurança elétrica para implementação de novos equipamentos</t>
+          <t>Construção de um abrigo de Resíduos Sólidos e guaritas de segurança externa na CAMG</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -7223,7 +7236,7 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>270000</v>
+        <v>1100000</v>
       </c>
       <c r="R113" t="n">
         <v>0</v>
@@ -7256,7 +7269,7 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>Construção de um abrigo de Resíduos Sólidos e guaritas de segurança externa na CAMG</t>
+          <t xml:space="preserve">Execução do projeto de reutilização da água da purga </t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -7280,7 +7293,7 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>1100000</v>
+        <v>624000</v>
       </c>
       <c r="R114" t="n">
         <v>0</v>
@@ -7313,7 +7326,7 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Execução do projeto de reutilização da água da purga </t>
+          <t>Projeto de modernização da alimentação elétrica emergencial dos elevadores</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -7337,7 +7350,7 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>624000</v>
+        <v>210000</v>
       </c>
       <c r="R115" t="n">
         <v>0</v>
@@ -7370,7 +7383,7 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>Projeto de modernização da alimentação elétrica emergencial dos elevadores</t>
+          <t>Programa de monitoramento e responsabilidade técnica das barragens da Cidade Administrativa</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -7394,7 +7407,7 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>210000</v>
+        <v>150000</v>
       </c>
       <c r="R116" t="n">
         <v>0</v>
@@ -7427,7 +7440,7 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>Programa de monitoramento e responsabilidade técnica das barragens da Cidade Administrativa</t>
+          <t>Impermeabilização das coberturas do prédio Alterosa e reforço estrutural do estacionamento do Alterosas</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -7451,7 +7464,7 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>150000</v>
+        <v>3918408</v>
       </c>
       <c r="R117" t="n">
         <v>0</v>
@@ -7468,10 +7481,10 @@
         <v>122</v>
       </c>
       <c r="D118" t="n">
-        <v>156</v>
+        <v>705</v>
       </c>
       <c r="E118" t="n">
-        <v>4465</v>
+        <v>2500</v>
       </c>
       <c r="F118" t="n">
         <v>1</v>
@@ -7484,7 +7497,7 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Impermeabilização das coberturas do prédio Alterosa e reforço estrutural do estacionamento do Alterosas</t>
+          <t>Projeto AVCB para o antigo prédio do IOF na av. Augusto de Lima</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -7492,9 +7505,17 @@
           <t>INICIANDO</t>
         </is>
       </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M118" t="n">
+        <v>1</v>
+      </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O118" t="inlineStr">
@@ -7508,7 +7529,7 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>3918408</v>
+        <v>282000</v>
       </c>
       <c r="R118" t="n">
         <v>0</v>
@@ -7516,19 +7537,19 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>1501</v>
+        <v>1511</v>
       </c>
       <c r="B119" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C119" t="n">
-        <v>122</v>
+        <v>181</v>
       </c>
       <c r="D119" t="n">
-        <v>705</v>
+        <v>32</v>
       </c>
       <c r="E119" t="n">
-        <v>2500</v>
+        <v>1006</v>
       </c>
       <c r="F119" t="n">
         <v>1</v>
@@ -7541,7 +7562,7 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>Projeto AVCB para o antigo prédio do IOF na av. Augusto de Lima</t>
+          <t xml:space="preserve">1ª Fase da Execução da Obra de Reformas e Adaptações da Antiga Cadeia Pública de Teofilo Otoni onde será instalada a Nova Delegacia Especializada no Atendimento a Mulher da DRPC de Teofilo Otoni. </t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -7549,34 +7570,26 @@
           <t>INICIANDO</t>
         </is>
       </c>
-      <c r="L119" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M119" t="n">
-        <v>1</v>
-      </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>282000</v>
+        <v>0</v>
       </c>
       <c r="R119" t="n">
-        <v>0</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="120">
@@ -7593,7 +7606,7 @@
         <v>32</v>
       </c>
       <c r="E120" t="n">
-        <v>1006</v>
+        <v>4063</v>
       </c>
       <c r="F120" t="n">
         <v>1</v>
@@ -7606,7 +7619,7 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t xml:space="preserve">1ª Fase da Execução da Obra de Reformas e Adaptações da Antiga Cadeia Pública de Teofilo Otoni onde será instalada a Nova Delegacia Especializada no Atendimento a Mulher da DRPC de Teofilo Otoni. </t>
+          <t>Construção do Complexo que irá abrigar o Núcleo Integrado de Perícias</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -7621,36 +7634,36 @@
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="R120" t="n">
-        <v>1000000</v>
+        <v>19850000</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>1511</v>
+        <v>1541</v>
       </c>
       <c r="B121" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C121" t="n">
-        <v>181</v>
+        <v>122</v>
       </c>
       <c r="D121" t="n">
-        <v>32</v>
+        <v>705</v>
       </c>
       <c r="E121" t="n">
-        <v>4063</v>
+        <v>2500</v>
       </c>
       <c r="F121" t="n">
         <v>1</v>
@@ -7663,12 +7676,12 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>Construção do Complexo que irá abrigar o Núcleo Integrado de Perícias</t>
+          <t>REFORMA DA ESCOLA DE SAÚDE PÚBLICA DO MUNICÍPIO DE BELO HORIZONTE</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -7683,31 +7696,31 @@
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BELO HORIZONTE</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>150000</v>
+        <v>2896100</v>
       </c>
       <c r="R121" t="n">
-        <v>19850000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>1541</v>
+        <v>2011</v>
       </c>
       <c r="B122" t="n">
         <v>10</v>
       </c>
       <c r="C122" t="n">
-        <v>122</v>
+        <v>302</v>
       </c>
       <c r="D122" t="n">
-        <v>705</v>
+        <v>88</v>
       </c>
       <c r="E122" t="n">
-        <v>2500</v>
+        <v>4231</v>
       </c>
       <c r="F122" t="n">
         <v>1</v>
@@ -7718,14 +7731,17 @@
       <c r="H122" t="n">
         <v>121</v>
       </c>
+      <c r="I122" t="n">
+        <v>12871</v>
+      </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>REFORMA DA ESCOLA DE SAÚDE PÚBLICA DO MUNICÍPIO DE BELO HORIZONTE</t>
+          <t xml:space="preserve">EXECUCAO DE OBRAS POR CONTRATO DE BENS PATRIMONIAVEIS adequação do HGIP para obtenção do AVCB                       </t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -7744,10 +7760,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>2896100</v>
+        <v>0</v>
       </c>
       <c r="R122" t="n">
-        <v>0</v>
+        <v>2000000</v>
       </c>
     </row>
     <row r="123">
@@ -7776,11 +7792,11 @@
         <v>122</v>
       </c>
       <c r="I123" t="n">
-        <v>12871</v>
+        <v>9999</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t xml:space="preserve">EXECUCAO DE OBRAS POR CONTRATO DE BENS PATRIMONIAVEIS adequação do HGIP para obtenção do AVCB                       </t>
+          <t xml:space="preserve">Reforma da Endoscopia - HGIP </t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -7807,7 +7823,7 @@
         <v>0</v>
       </c>
       <c r="R123" t="n">
-        <v>2000000</v>
+        <v>1600000</v>
       </c>
     </row>
     <row r="124">
@@ -7818,13 +7834,13 @@
         <v>10</v>
       </c>
       <c r="C124" t="n">
-        <v>302</v>
+        <v>122</v>
       </c>
       <c r="D124" t="n">
-        <v>88</v>
+        <v>705</v>
       </c>
       <c r="E124" t="n">
-        <v>4231</v>
+        <v>2500</v>
       </c>
       <c r="F124" t="n">
         <v>1</v>
@@ -7836,11 +7852,11 @@
         <v>123</v>
       </c>
       <c r="I124" t="n">
-        <v>9999</v>
+        <v>12690</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reforma da Endoscopia - HGIP </t>
+          <t>Apoio à GELENG, no atendimento às demandas de serviços de reforma e manutenção nas unidades.</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -7867,24 +7883,24 @@
         <v>0</v>
       </c>
       <c r="R124" t="n">
-        <v>1600000</v>
+        <v>2200000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>2011</v>
+        <v>2101</v>
       </c>
       <c r="B125" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C125" t="n">
-        <v>122</v>
+        <v>541</v>
       </c>
       <c r="D125" t="n">
-        <v>705</v>
+        <v>31</v>
       </c>
       <c r="E125" t="n">
-        <v>2500</v>
+        <v>4058</v>
       </c>
       <c r="F125" t="n">
         <v>1</v>
@@ -7895,12 +7911,9 @@
       <c r="H125" t="n">
         <v>124</v>
       </c>
-      <c r="I125" t="n">
-        <v>12690</v>
-      </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>Apoio à GELENG, no atendimento às demandas de serviços de reforma e manutenção nas unidades.</t>
+          <t>Construção do Cetras de Governador Valadares</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -7908,26 +7921,34 @@
           <t>INICIANDO</t>
         </is>
       </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M125" t="n">
+        <v>1</v>
+      </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>0</v>
+        <v>350000</v>
       </c>
       <c r="R125" t="n">
-        <v>2200000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -7944,7 +7965,7 @@
         <v>31</v>
       </c>
       <c r="E126" t="n">
-        <v>4058</v>
+        <v>4059</v>
       </c>
       <c r="F126" t="n">
         <v>1</v>
@@ -7957,7 +7978,7 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>Construção do Cetras de Governador Valadares</t>
+          <t>APA Parque Cataguás</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -7989,7 +8010,7 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>350000</v>
+        <v>1000000</v>
       </c>
       <c r="R126" t="n">
         <v>0</v>
@@ -7997,19 +8018,19 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>2101</v>
+        <v>2151</v>
       </c>
       <c r="B127" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C127" t="n">
-        <v>541</v>
+        <v>572</v>
       </c>
       <c r="D127" t="n">
-        <v>31</v>
+        <v>75</v>
       </c>
       <c r="E127" t="n">
-        <v>4059</v>
+        <v>1023</v>
       </c>
       <c r="F127" t="n">
         <v>1</v>
@@ -8022,7 +8043,7 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>APA Parque Cataguás</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA ELABORAÇÃO DE ESTUDOS TÉCNICOS, LEVANTAMENTOS TOPOGRÁFICOS, SONDAGENS, ESTUDOS AMBIENTAIS, PROJETOS DE ARQUITETURA E ENGENHARIA, ORÇAMENTOS, MEMORIAIS DESCRITIVOS E AFINS</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -8030,31 +8051,23 @@
           <t>INICIANDO</t>
         </is>
       </c>
-      <c r="L127" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M127" t="n">
-        <v>1</v>
-      </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>IBIRITÉ</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>1000000</v>
+        <v>200000</v>
       </c>
       <c r="R127" t="n">
         <v>0</v>
@@ -8068,13 +8081,13 @@
         <v>12</v>
       </c>
       <c r="C128" t="n">
-        <v>572</v>
+        <v>122</v>
       </c>
       <c r="D128" t="n">
-        <v>75</v>
+        <v>705</v>
       </c>
       <c r="E128" t="n">
-        <v>1023</v>
+        <v>2500</v>
       </c>
       <c r="F128" t="n">
         <v>1</v>
@@ -8087,7 +8100,7 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA ELABORAÇÃO DE ESTUDOS TÉCNICOS, LEVANTAMENTOS TOPOGRÁFICOS, SONDAGENS, ESTUDOS AMBIENTAIS, PROJETOS DE ARQUITETURA E ENGENHARIA, ORÇAMENTOS, MEMORIAIS DESCRITIVOS E AFINS</t>
+          <t>CONTRATAÇÃO DO CONSÓRCIO PGM / SINAURB CIDERSU (PGM CONSTRUÇÕES E EMPREENDIMENTOS LTDA E SINAURB SERVIÇOS E EMPREENDIMENTOS LTDA) PRESTAÇÃO DE SERVIÇOS COMUNS E CONTÍNUOS DE ENGENHARIA, SOB DEMANDA, DESTINADOS À MANUTENÇÃO PREDIAL, CONSERVAÇÃO E EXEC</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -8111,7 +8124,7 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>200000</v>
+        <v>1500000</v>
       </c>
       <c r="R128" t="n">
         <v>0</v>
@@ -8119,19 +8132,19 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>2151</v>
+        <v>2161</v>
       </c>
       <c r="B129" t="n">
         <v>12</v>
       </c>
       <c r="C129" t="n">
-        <v>122</v>
+        <v>242</v>
       </c>
       <c r="D129" t="n">
-        <v>705</v>
+        <v>5</v>
       </c>
       <c r="E129" t="n">
-        <v>2500</v>
+        <v>1030</v>
       </c>
       <c r="F129" t="n">
         <v>1</v>
@@ -8144,12 +8157,12 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DO CONSÓRCIO PGM / SINAURB CIDERSU (PGM CONSTRUÇÕES E EMPREENDIMENTOS LTDA E SINAURB SERVIÇOS E EMPREENDIMENTOS LTDA) PRESTAÇÃO DE SERVIÇOS COMUNS E CONTÍNUOS DE ENGENHARIA, SOB DEMANDA, DESTINADOS À MANUTENÇÃO PREDIAL, CONSERVAÇÃO E EXEC</t>
+          <t>Projeto para melhoria de acessibilidade nas unidades da FUCAM</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>PARALISADO</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -8159,16 +8172,16 @@
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Montes Claros</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>IBIRITÉ</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE MONTES CLAROS</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>1500000</v>
+        <v>14000</v>
       </c>
       <c r="R129" t="n">
         <v>0</v>
@@ -8216,16 +8229,16 @@
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>Região Intermediária de Montes Claros</t>
+          <t>Região Intermediária de Patos de Minas</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE MONTES CLAROS</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE PATOS DE MINAS</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>14000</v>
+        <v>3000</v>
       </c>
       <c r="R130" t="n">
         <v>0</v>
@@ -8273,12 +8286,12 @@
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>Região Intermediária de Patos de Minas</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE PATOS DE MINAS</t>
+          <t>ESMERALDAS</t>
         </is>
       </c>
       <c r="Q131" t="n">
@@ -8290,19 +8303,19 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>2161</v>
+        <v>2261</v>
       </c>
       <c r="B132" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C132" t="n">
-        <v>242</v>
+        <v>303</v>
       </c>
       <c r="D132" t="n">
-        <v>5</v>
+        <v>154</v>
       </c>
       <c r="E132" t="n">
-        <v>1030</v>
+        <v>4460</v>
       </c>
       <c r="F132" t="n">
         <v>1</v>
@@ -8313,14 +8326,17 @@
       <c r="H132" t="n">
         <v>131</v>
       </c>
+      <c r="I132" t="n">
+        <v>12502</v>
+      </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>Projeto para melhoria de acessibilidade nas unidades da FUCAM</t>
+          <t>Execução de Obras da nova sede da Divisão de Controle de Qualidade.</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>PARALISADO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -8335,11 +8351,11 @@
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>ESMERALDAS</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>3000</v>
+        <v>500000</v>
       </c>
       <c r="R132" t="n">
         <v>0</v>
@@ -8353,13 +8369,13 @@
         <v>10</v>
       </c>
       <c r="C133" t="n">
-        <v>303</v>
+        <v>122</v>
       </c>
       <c r="D133" t="n">
-        <v>154</v>
+        <v>705</v>
       </c>
       <c r="E133" t="n">
-        <v>4460</v>
+        <v>2500</v>
       </c>
       <c r="F133" t="n">
         <v>1</v>
@@ -8371,11 +8387,11 @@
         <v>132</v>
       </c>
       <c r="I133" t="n">
-        <v>12502</v>
+        <v>12500</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>Execução de Obras da nova sede da Divisão de Controle de Qualidade.</t>
+          <t>Novo Prédio Administrativo da FUNED em Steel Frame (Unidade IV)</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -8399,7 +8415,7 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>500000</v>
+        <v>10535000</v>
       </c>
       <c r="R133" t="n">
         <v>0</v>
@@ -8430,12 +8446,9 @@
       <c r="H134" t="n">
         <v>133</v>
       </c>
-      <c r="I134" t="n">
-        <v>12500</v>
-      </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>Novo Prédio Administrativo da FUNED em Steel Frame (Unidade IV)</t>
+          <t>Obras de adequação estrutural do refeitório para atendimento às exigências da Vigilância Sanitária Municipal.</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -8459,7 +8472,7 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>10535000</v>
+        <v>500000</v>
       </c>
       <c r="R134" t="n">
         <v>0</v>
@@ -8467,19 +8480,19 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>2261</v>
+        <v>2301</v>
       </c>
       <c r="B135" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="C135" t="n">
-        <v>122</v>
+        <v>782</v>
       </c>
       <c r="D135" t="n">
-        <v>705</v>
+        <v>81</v>
       </c>
       <c r="E135" t="n">
-        <v>2500</v>
+        <v>4268</v>
       </c>
       <c r="F135" t="n">
         <v>1</v>
@@ -8492,7 +8505,7 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>Obras de adequação estrutural do refeitório para atendimento às exigências da Vigilância Sanitária Municipal.</t>
+          <t>REABILITAÇÃO DA MG-010 (CONCEIÇÃO DO MATO DENTRO A SERRO)</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -8507,19 +8520,19 @@
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="R135" t="n">
-        <v>0</v>
+        <v>5000000</v>
       </c>
     </row>
     <row r="136">
@@ -8549,7 +8562,7 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>REABILITAÇÃO DA MG-010 (CONCEIÇÃO DO MATO DENTRO A SERRO)</t>
+          <t>REABILITAÇÃO DA MG-129 (OURO PRETO A OURO BRANCO)</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -8606,7 +8619,7 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>REABILITAÇÃO DA MG-129 (OURO PRETO A OURO BRANCO)</t>
+          <t>RESTAURAÇÃO RODOVIA MG-010, TRECHO CONCEIÇÃO DO MATO DENTRO - SERRO (DISTRITO DE MATO GROSSO) E RECOMPOSIÇÃO DE TALUDE ERODIDO</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -8633,7 +8646,7 @@
         <v>0</v>
       </c>
       <c r="R137" t="n">
-        <v>5000000</v>
+        <v>10000000</v>
       </c>
     </row>
     <row r="138">
@@ -8663,7 +8676,7 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO RODOVIA MG-010, TRECHO CONCEIÇÃO DO MATO DENTRO - SERRO (DISTRITO DE MATO GROSSO) E RECOMPOSIÇÃO DE TALUDE ERODIDO</t>
+          <t>ARCOS - CORUMBÁ - RODOVIA: MG-170 (ENTR BR-354 - AGRIMIG)</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -8687,10 +8700,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>0</v>
+        <v>9792000</v>
       </c>
       <c r="R138" t="n">
-        <v>10000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139">
@@ -8720,7 +8733,7 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>ARCOS - CORUMBÁ - RODOVIA: MG-170 (ENTR BR-354 - AGRIMIG)</t>
+          <t>MG-129 - OURO PRETO A OURO BRANCO</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -8744,7 +8757,7 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>9792000</v>
+        <v>1000000</v>
       </c>
       <c r="R139" t="n">
         <v>0</v>
@@ -8777,7 +8790,7 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>MG-129 - OURO PRETO A OURO BRANCO</t>
+          <t>RECUPERAÇÃO DE EROSÃO EM TALUDE DE CORTE NA RODOVIA MGC-354, KM 167,8, TRECHO: RIBEIRÃO DA MATA - AV MARABÁ (PATOS DE MINAS)</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -8801,7 +8814,7 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>1000000</v>
+        <v>143000</v>
       </c>
       <c r="R140" t="n">
         <v>0</v>
@@ -8834,7 +8847,7 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>RECUPERAÇÃO DE EROSÃO EM TALUDE DE CORTE NA RODOVIA MGC-354, KM 167,8, TRECHO: RIBEIRÃO DA MATA - AV MARABÁ (PATOS DE MINAS)</t>
+          <t>RESTAURAÇÃO DA INTERSEÇÃO NA RODOVIA MGC-354, KM 150,9, TRECHO: TRAVESSIA URBANA DE PRESIDENTE OLEGÁRIO</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -8858,7 +8871,7 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>143000</v>
+        <v>5876140</v>
       </c>
       <c r="R141" t="n">
         <v>0</v>
@@ -8891,7 +8904,7 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO DA INTERSEÇÃO NA RODOVIA MGC-354, KM 150,9, TRECHO: TRAVESSIA URBANA DE PRESIDENTE OLEGÁRIO</t>
+          <t>RESTAURAÇÃO DA INTERSEÇÃO NA RODOVIA MGC-354, KM 176,2, TRECHO: AV MARABÁ (PATOS DE MINAS) - ENTR BR 365</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -8915,7 +8928,7 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>5876140</v>
+        <v>1132500</v>
       </c>
       <c r="R142" t="n">
         <v>0</v>
@@ -8948,7 +8961,7 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO DA INTERSEÇÃO NA RODOVIA MGC-354, KM 176,2, TRECHO: AV MARABÁ (PATOS DE MINAS) - ENTR BR 365</t>
+          <t>RESTAURAÇÃO E 3ª FAIXA, TRECHO ENTR. BR-354 (CAXAMBÚ) - ENTR. BR-381 (PALMELA DISTRITO DE CAMPANHA), NA MGC-267</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -8972,7 +8985,7 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>1132500</v>
+        <v>1000000</v>
       </c>
       <c r="R143" t="n">
         <v>0</v>
@@ -9005,7 +9018,7 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO E 3ª FAIXA, TRECHO ENTR. BR-354 (CAXAMBÚ) - ENTR. BR-381 (PALMELA DISTRITO DE CAMPANHA), NA MGC-267</t>
+          <t>RESTAURAÇÃO E AUMENTO DE CAPACIDADE (3ª FAIXA) DO TRECHO SERRA DO SALITRE - SALITRE DE MINAS, NA MG-230</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -9029,7 +9042,7 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>1000000</v>
+        <v>34710000</v>
       </c>
       <c r="R144" t="n">
         <v>0</v>
@@ -9062,7 +9075,7 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO E AUMENTO DE CAPACIDADE (3ª FAIXA) DO TRECHO SERRA DO SALITRE - SALITRE DE MINAS, NA MG-230</t>
+          <t>RESTAURAÇÃO E AUMENTO DE CAPACIDADE DO TRECHO MG-344 (ENTR. P/ CÁSSIA) - DIVISA MG/SP, NA MG-444, EXT. 23,9 KM</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -9086,7 +9099,7 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>34710000</v>
+        <v>59000000</v>
       </c>
       <c r="R145" t="n">
         <v>0</v>
@@ -9119,7 +9132,7 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO E AUMENTO DE CAPACIDADE DO TRECHO MG-344 (ENTR. P/ CÁSSIA) - DIVISA MG/SP, NA MG-444, EXT. 23,9 KM</t>
+          <t>RESTAURAÇÃO E AUMENTO DE CAPACIDADE DO TRECHO PARÁ DE MINAS - PAPAGAIOS (3ª FAIXA) - LOTE 1</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -9143,7 +9156,7 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>59000000</v>
+        <v>1000000</v>
       </c>
       <c r="R146" t="n">
         <v>0</v>
@@ -9176,7 +9189,7 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO E AUMENTO DE CAPACIDADE DO TRECHO PARÁ DE MINAS - PAPAGAIOS (3ª FAIXA) - LOTE 1</t>
+          <t>RESTAURAÇÃO E AUMENTO DE CAPACIDADE DO TRECHO: UNAÍ A GARAPUAVA</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -9233,7 +9246,7 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO E AUMENTO DE CAPACIDADE DO TRECHO: UNAÍ A GARAPUAVA</t>
+          <t>RESTAURAÇÃO TIMÓTEO - ENTR. LMG-760 (CAVA GRANDE), NA MG-425</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
@@ -9257,7 +9270,7 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>1000000</v>
+        <v>200000</v>
       </c>
       <c r="R148" t="n">
         <v>0</v>
@@ -9290,7 +9303,7 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO TIMÓTEO - ENTR. LMG-760 (CAVA GRANDE), NA MG-425</t>
+          <t>RESTAURAÇÃO TRECHO ENTR. LMG764 (P/ MATUTINA) - SÃO GOTARDO, NA MG- 235 - 3ª FAIXA</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
@@ -9314,7 +9327,7 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>200000</v>
+        <v>1000000</v>
       </c>
       <c r="R149" t="n">
         <v>0</v>
@@ -9347,7 +9360,7 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO TRECHO ENTR. LMG764 (P/ MATUTINA) - SÃO GOTARDO, NA MG- 235 - 3ª FAIXA</t>
+          <t>RESTAURAÇÃO TRECHO ENTR. MGC-120 (B) (DONA EUZÉBIA) - ENTR. MGC-265, NA MG-285</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -9371,7 +9384,7 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>1000000</v>
+        <v>30980000</v>
       </c>
       <c r="R150" t="n">
         <v>0</v>
@@ -9404,7 +9417,7 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO TRECHO ENTR. MGC-120 (B) (DONA EUZÉBIA) - ENTR. MGC-265, NA MG-285</t>
+          <t>RESTAURAÇÃO TRECHO ENTR. MGC-265/MG-452 (P/ PAIVA) - ENTR. BR-040, NA MG-448</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
@@ -9428,7 +9441,7 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>30980000</v>
+        <v>25655000</v>
       </c>
       <c r="R151" t="n">
         <v>0</v>
@@ -9461,7 +9474,7 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO TRECHO ENTR. MGC-265/MG-452 (P/ PAIVA) - ENTR. BR-040, NA MG-448</t>
+          <t>RESTAURAÇÃO TRECHO PIRAÚBA (ENTR. MG-285) - PAIVA (ENTR. MG-488/MG-455), NA MG-265 E 3ª FAIXA</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -9485,7 +9498,7 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>25655000</v>
+        <v>66560000</v>
       </c>
       <c r="R152" t="n">
         <v>0</v>
@@ -9518,7 +9531,7 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO TRECHO PIRAÚBA (ENTR. MG-285) - PAIVA (ENTR. MG-488/MG-455), NA MG-265 E 3ª FAIXA</t>
+          <t>RESTAURAÇÃO TRECHO SÃO GOTARDO - ENTR. BR-354 (P/ PATOS DE MINAS), NA MG-235</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
@@ -9542,7 +9555,7 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>66560000</v>
+        <v>1000000</v>
       </c>
       <c r="R153" t="n">
         <v>0</v>
@@ -9575,7 +9588,7 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO TRECHO SÃO GOTARDO - ENTR. BR-354 (P/ PATOS DE MINAS), NA MG-235</t>
+          <t>RESTAURAÇÃO TRÊS PONTAS - VARGINHA, NA MG-167</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
@@ -9599,7 +9612,7 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>1000000</v>
+        <v>25464500</v>
       </c>
       <c r="R154" t="n">
         <v>0</v>
@@ -9619,7 +9632,7 @@
         <v>81</v>
       </c>
       <c r="E155" t="n">
-        <v>4268</v>
+        <v>4272</v>
       </c>
       <c r="F155" t="n">
         <v>1</v>
@@ -9632,7 +9645,7 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO TRÊS PONTAS - VARGINHA, NA MG-167</t>
+          <t>BDCC 3X3 CÓRREGO CAVALO, TRECHO ENTR. BR-040 - PORTO DIAMANTE</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
@@ -9656,7 +9669,7 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>25464500</v>
+        <v>100000</v>
       </c>
       <c r="R155" t="n">
         <v>0</v>
@@ -9689,7 +9702,7 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>BDCC 3X3 CÓRREGO CAVALO, TRECHO ENTR. BR-040 - PORTO DIAMANTE</t>
+          <t>COMPLEMENTAÇÃO DA CONSTRUÇÃO DA PONTE SOBRE O RIO SÃO FRANCISCO, PINTÓPOLIS</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
@@ -9713,7 +9726,7 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>100000</v>
+        <v>24000000</v>
       </c>
       <c r="R156" t="n">
         <v>0</v>
@@ -9746,7 +9759,7 @@
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>COMPLEMENTAÇÃO DA CONSTRUÇÃO DA PONTE SOBRE O RIO SÃO FRANCISCO, PINTÓPOLIS</t>
+          <t>ENCABEÇAMENTO E PONTE CÓRREGO SÃO BARTOLOMEU E ENCABEÇAMENTO CÓRREGO BARBADINHO, TRECHO CANABRAVA (JOÃO PINHEIRO) - ENTR. MG-181, NA LMG-698</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
@@ -9770,7 +9783,7 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>24000000</v>
+        <v>252000</v>
       </c>
       <c r="R157" t="n">
         <v>0</v>
@@ -9803,7 +9816,7 @@
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>ENCABEÇAMENTO E PONTE CÓRREGO SÃO BARTOLOMEU E ENCABEÇAMENTO CÓRREGO BARBADINHO, TRECHO CANABRAVA (JOÃO PINHEIRO) - ENTR. MG-181, NA LMG-698</t>
+          <t>ENCABEÇAMENTO E PONTE SOBRE CÓRREGO AMENDOIM, NO TRECHO RIACHINHO - GUARAPUAVA (UNAÍ), NA LMG-638</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
@@ -9827,7 +9840,7 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>252000</v>
+        <v>319200</v>
       </c>
       <c r="R158" t="n">
         <v>0</v>
@@ -9860,7 +9873,7 @@
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>ENCABEÇAMENTO E PONTE SOBRE CÓRREGO AMENDOIM, NO TRECHO RIACHINHO - GUARAPUAVA (UNAÍ), NA LMG-638</t>
+          <t>ENCABEÇAMENTO E PONTE SOBRE CÓRREGO BOI PRETO, NO TRECHO RIACHINHO - GUARAPUAVA (UNAÍ), NA LMG-638</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
@@ -9884,7 +9897,7 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>319200</v>
+        <v>495600</v>
       </c>
       <c r="R159" t="n">
         <v>0</v>
@@ -9917,7 +9930,7 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>ENCABEÇAMENTO E PONTE SOBRE CÓRREGO BOI PRETO, NO TRECHO RIACHINHO - GUARAPUAVA (UNAÍ), NA LMG-638</t>
+          <t>ENCABEÇAMENTO E PONTE SOBRE O CÓRREGO DAS LAJES, TRECHO ENTR. MGC-479 (SERRA DAS ARARAS) - ENTR. MG-402, NA LMG-622</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
@@ -9941,7 +9954,7 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>495600</v>
+        <v>679000</v>
       </c>
       <c r="R160" t="n">
         <v>0</v>
@@ -9974,7 +9987,7 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>ENCABEÇAMENTO E PONTE SOBRE O CÓRREGO DAS LAJES, TRECHO ENTR. MGC-479 (SERRA DAS ARARAS) - ENTR. MG-402, NA LMG-622</t>
+          <t>ENCABEÇAMENTO E PONTE SOBRE O RIO SANTO INÁCIO, TRECHO ENTR. MG-188 (COROMANDEL) - DISTRITO DE VEREDA, NA LMG-747</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
@@ -9998,7 +10011,7 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>679000</v>
+        <v>440000</v>
       </c>
       <c r="R161" t="n">
         <v>0</v>
@@ -10031,7 +10044,7 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>ENCABEÇAMENTO E PONTE SOBRE O RIO SANTO INÁCIO, TRECHO ENTR. MG-188 (COROMANDEL) - DISTRITO DE VEREDA, NA LMG-747</t>
+          <t>ENCABEÇAMENTO E PONTE SOBRE O RIO SÃO JOÃO, TRECHO IGARATINGA - ENTR. MG-252, NA MG-430 (SEMI-INTEGRADA)</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
@@ -10055,7 +10068,7 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>440000</v>
+        <v>14920000</v>
       </c>
       <c r="R162" t="n">
         <v>0</v>
@@ -10088,7 +10101,7 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>ENCABEÇAMENTO E PONTE SOBRE O RIO SÃO JOÃO, TRECHO IGARATINGA - ENTR. MG-252, NA MG-430 (SEMI-INTEGRADA)</t>
+          <t>ENCABEÇAMENTO E PONTE SOBRE O RIO SERRA BRANCA, TRECHO PAI PEDRO - CATUTI, NA MGC-122</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
@@ -10112,7 +10125,7 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>14920000</v>
+        <v>8798400</v>
       </c>
       <c r="R163" t="n">
         <v>0</v>
@@ -10145,7 +10158,7 @@
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>ENCABEÇAMENTO E PONTE SOBRE O RIO SERRA BRANCA, TRECHO PAI PEDRO - CATUTI, NA MGC-122</t>
+          <t>ENCABEÇAMENTOS E PONTES SOBRE CÓRREGO VEREDINHA E RIBEIRÃO MARQUES, NO TRECHO RIACHINHO - GUARAPUAVA (UNAÍ), NA LMG-638</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
@@ -10169,7 +10182,7 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>8798400</v>
+        <v>369600</v>
       </c>
       <c r="R164" t="n">
         <v>0</v>
@@ -10202,7 +10215,7 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>ENCABEÇAMENTOS E PONTES SOBRE CÓRREGO VEREDINHA E RIBEIRÃO MARQUES, NO TRECHO RIACHINHO - GUARAPUAVA (UNAÍ), NA LMG-638</t>
+          <t>LMG-722 (ROCHINHA A LAGAMAR, PONTE SOBRE O RIO PARANAÍBA)</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
@@ -10226,7 +10239,7 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>369600</v>
+        <v>1000000</v>
       </c>
       <c r="R165" t="n">
         <v>0</v>
@@ -10259,7 +10272,7 @@
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>LMG-722 (ROCHINHA A LAGAMAR, PONTE SOBRE O RIO PARANAÍBA)</t>
+          <t>MGC-267 (CORDISLÂNDIA A CARVALHÓPOLIS, PONTE SOBRE O RIO SAPUCAÍ -  LOTE 01)</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
@@ -10283,7 +10296,7 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>1000000</v>
+        <v>1203643</v>
       </c>
       <c r="R166" t="n">
         <v>0</v>
@@ -10316,7 +10329,7 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>MGC-267 (CORDISLÂNDIA A CARVALHÓPOLIS, PONTE SOBRE O RIO SAPUCAÍ -  LOTE 01)</t>
+          <t>OLHOS D´AGUA DO OESTE A SANTA LUZIA DA SERRA - CÓRREGO SÃO BARTOLOMEU</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
@@ -10340,7 +10353,7 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>1203643</v>
+        <v>730000</v>
       </c>
       <c r="R167" t="n">
         <v>0</v>
@@ -10373,7 +10386,7 @@
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>OLHOS D´AGUA DO OESTE A SANTA LUZIA DA SERRA - CÓRREGO SÃO BARTOLOMEU</t>
+          <t>PASSARELA MG-010 (CIDADE ADMINISTRATIVA)</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
@@ -10397,7 +10410,7 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>730000</v>
+        <v>66619</v>
       </c>
       <c r="R168" t="n">
         <v>0</v>
@@ -10430,7 +10443,7 @@
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>PASSARELA MG-010 (CIDADE ADMINISTRATIVA)</t>
+          <t>PONTE CÓRREGO PERUAÇU, TRECHO CÔNEGO MARINHO - MIRAVÂNIA (RESERVA XACRIABÁ)</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
@@ -10454,7 +10467,7 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>66619</v>
+        <v>901000</v>
       </c>
       <c r="R169" t="n">
         <v>0</v>
@@ -10487,7 +10500,7 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>PONTE CÓRREGO PERUAÇU, TRECHO CÔNEGO MARINHO - MIRAVÂNIA (RESERVA XACRIABÁ)</t>
+          <t>PONTE CÓRREGO RIBEIRÃO, TRECHO ENTR. BR-040 - PORTO DIAMANTE</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
@@ -10511,7 +10524,7 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>901000</v>
+        <v>100000</v>
       </c>
       <c r="R170" t="n">
         <v>0</v>
@@ -10544,7 +10557,7 @@
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>PONTE CÓRREGO RIBEIRÃO, TRECHO ENTR. BR-040 - PORTO DIAMANTE</t>
+          <t>PONTE SOBRE O EXTRAVASOR DA CEMIG, TRECHO JANUÁRIA - RIO PARDO - PANDEIROS, NA MGC-479</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
@@ -10568,7 +10581,7 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>100000</v>
+        <v>170000</v>
       </c>
       <c r="R171" t="n">
         <v>0</v>
@@ -10601,7 +10614,7 @@
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>PONTE SOBRE O EXTRAVASOR DA CEMIG, TRECHO JANUÁRIA - RIO PARDO - PANDEIROS, NA MGC-479</t>
+          <t>PONTE SOBRE O RIBEIRÃO MATA BOI NA RODOVIA MG-414, TRECHO ARAGUARI (DISTRITO DE AMANHECE) - DIVISA MG/GO</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
@@ -10625,7 +10638,7 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>170000</v>
+        <v>2940000</v>
       </c>
       <c r="R172" t="n">
         <v>0</v>
@@ -10658,7 +10671,7 @@
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>PONTE SOBRE O RIBEIRÃO MATA BOI NA RODOVIA MG-414, TRECHO ARAGUARI (DISTRITO DE AMANHECE) - DIVISA MG/GO</t>
+          <t>PONTE SOBRE O RIBEIRÃO PANDEIROS, TRECHO JANUÁRIA - RIO PARDO - PANDEIROS, NA MGC-479</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
@@ -10682,7 +10695,7 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>2940000</v>
+        <v>810000</v>
       </c>
       <c r="R173" t="n">
         <v>0</v>
@@ -10715,7 +10728,7 @@
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>PONTE SOBRE O RIBEIRÃO PANDEIROS, TRECHO JANUÁRIA - RIO PARDO - PANDEIROS, NA MGC-479</t>
+          <t>PONTE SOBRE O RIO ARAGUARI (TROCA DOS APARELHOS DE DO 1º E 5º VÃOS), TRECHO ENTR. MG-190 - ZELÂNDIA (USINA SANTA JULIANA), DIMENSÕES 130,00X12,20M, RODOVIA AMG-0730</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
@@ -10739,7 +10752,7 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>810000</v>
+        <v>542000</v>
       </c>
       <c r="R174" t="n">
         <v>0</v>
@@ -10772,7 +10785,7 @@
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>PONTE SOBRE O RIO ARAGUARI (TROCA DOS APARELHOS DE DO 1º E 5º VÃOS), TRECHO ENTR. MG-190 - ZELÂNDIA (USINA SANTA JULIANA), DIMENSÕES 130,00X12,20M, RODOVIA AMG-0730</t>
+          <t>PONTE SOBRE O RIO CORRENTE -  MG-460, NO TRECHO DE MUNHOZ - TOLEDO ( E SEMI-INTEGRADA)</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
@@ -10796,7 +10809,7 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>542000</v>
+        <v>2163814</v>
       </c>
       <c r="R175" t="n">
         <v>0</v>
@@ -10829,7 +10842,7 @@
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>PONTE SOBRE O RIO CORRENTE -  MG-460, NO TRECHO DE MUNHOZ - TOLEDO ( E SEMI-INTEGRADA)</t>
+          <t>PONTE SOBRE O RIO SÃO FRANCISCO - ENTR. MGC-135 (MANGA) ¿ PORTO DE MATIAS CARDOSO, NA RODOVIA MG-401</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
@@ -10853,7 +10866,7 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>2163814</v>
+        <v>25000000</v>
       </c>
       <c r="R176" t="n">
         <v>0</v>
@@ -10886,7 +10899,7 @@
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>PONTE SOBRE O RIO SÃO FRANCISCO - ENTR. MGC-135 (MANGA) ¿ PORTO DE MATIAS CARDOSO, NA RODOVIA MG-401</t>
+          <t>PONTES SOBRE OS RIOS SUAÇUI PEQUENO I E II, TRECHO PEÇANHA - COROACI, NA MG-314</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
@@ -10910,7 +10923,7 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>25000000</v>
+        <v>500000</v>
       </c>
       <c r="R177" t="n">
         <v>0</v>
@@ -10943,7 +10956,7 @@
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>PONTES SOBRE OS RIOS SUAÇUI PEQUENO I E II, TRECHO PEÇANHA - COROACI, NA MG-314</t>
+          <t>RECUPERAÇÃO DA PONTE S/ O RIO JEQUITINHONHA- DIAMANTINA - COUTO MAGALHÃES.</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
@@ -10967,7 +10980,7 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>500000</v>
+        <v>1382535</v>
       </c>
       <c r="R178" t="n">
         <v>0</v>
@@ -11000,7 +11013,7 @@
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>RECUPERAÇÃO DA PONTE S/ O RIO JEQUITINHONHA- DIAMANTINA - COUTO MAGALHÃES.</t>
+          <t>RECUPERAÇÃO ESTRUTURAL DA PONTE SOBRE O RIO PARACATU, TRECHO JOÃO PINHEIRO - BRASÍLÂNDIA DE MINAS, NA MG-181</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
@@ -11024,7 +11037,7 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>1382535</v>
+        <v>1000000</v>
       </c>
       <c r="R179" t="n">
         <v>0</v>
@@ -11057,7 +11070,7 @@
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>RECUPERAÇÃO ESTRUTURAL DA PONTE SOBRE O RIO PARACATU, TRECHO JOÃO PINHEIRO - BRASÍLÂNDIA DE MINAS, NA MG-181</t>
+          <t>RECUPERAÇÃO ESTRUTURAL DA PONTE SOBRE O RIO PARACATU, TRECHO JOÃO PINHEIRO (ENTR. MG-408) - BRASÍLÂNDIA DE MINAS, NA MG-181</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
@@ -11081,7 +11094,7 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>1000000</v>
+        <v>900000</v>
       </c>
       <c r="R180" t="n">
         <v>0</v>
@@ -11114,7 +11127,7 @@
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>RECUPERAÇÃO ESTRUTURAL DA PONTE SOBRE O RIO PARACATU, TRECHO JOÃO PINHEIRO (ENTR. MG-408) - BRASÍLÂNDIA DE MINAS, NA MG-181</t>
+          <t>REFORÇO DA FUNDAÇÃO DA PONTE SOBRE O RIBEIRÃO DAS ARARAS I, TRECHO GUANHÃES - SÃO PEDRO DO SUAÇUÍ, NA CMG-120</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
@@ -11138,7 +11151,7 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>900000</v>
+        <v>168000</v>
       </c>
       <c r="R181" t="n">
         <v>0</v>
@@ -11171,7 +11184,7 @@
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>REFORÇO DA FUNDAÇÃO DA PONTE SOBRE O RIBEIRÃO DAS ARARAS I, TRECHO GUANHÃES - SÃO PEDRO DO SUAÇUÍ, NA CMG-120</t>
+          <t>REFORÇO DA FUNDAÇÃO DA PONTE SOBRE O RIBEIRÃO MACAÚBAS, TRECHO SANTA LUZIA - JABOTICATUBAS, MG-020</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
@@ -11195,7 +11208,7 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>168000</v>
+        <v>249000</v>
       </c>
       <c r="R182" t="n">
         <v>0</v>
@@ -11228,7 +11241,7 @@
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>REFORÇO DA FUNDAÇÃO DA PONTE SOBRE O RIBEIRÃO MACAÚBAS, TRECHO SANTA LUZIA - JABOTICATUBAS, MG-020</t>
+          <t>REFORÇO DA FUNDAÇÃO DO VIADUTO II NA PISTA DIREITA DA INTERSEÇÃO 3 (ACESSO AO INHOTIM, ESTACA 138)</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
@@ -11252,7 +11265,7 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>249000</v>
+        <v>705000</v>
       </c>
       <c r="R183" t="n">
         <v>0</v>
@@ -11285,7 +11298,7 @@
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>REFORÇO DA FUNDAÇÃO DO VIADUTO II NA PISTA DIREITA DA INTERSEÇÃO 3 (ACESSO AO INHOTIM, ESTACA 138)</t>
+          <t>REFORÇO DE FUNDAÇÃO CÓRREGO DOIDOS, TRECHO SÃO FRANCISCO DE PAULA - ENTR. BR-354</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
@@ -11309,7 +11322,7 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>705000</v>
+        <v>58800</v>
       </c>
       <c r="R184" t="n">
         <v>0</v>
@@ -11342,7 +11355,7 @@
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>REFORÇO DE FUNDAÇÃO CÓRREGO DOIDOS, TRECHO SÃO FRANCISCO DE PAULA - ENTR. BR-354</t>
+          <t>REFORÇO NA FUNDAÇÃO DA PONTE SOBRE O RIO VERMELHO, TRECHO SANTA BÁRBARA - CATAS ALTAS, NA MG-129</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
@@ -11366,7 +11379,7 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>58800</v>
+        <v>725000</v>
       </c>
       <c r="R185" t="n">
         <v>0</v>
@@ -11386,7 +11399,7 @@
         <v>81</v>
       </c>
       <c r="E186" t="n">
-        <v>4272</v>
+        <v>4275</v>
       </c>
       <c r="F186" t="n">
         <v>1</v>
@@ -11399,7 +11412,7 @@
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>REFORÇO NA FUNDAÇÃO DA PONTE SOBRE O RIO VERMELHO, TRECHO SANTA BÁRBARA - CATAS ALTAS, NA MG-129</t>
+          <t>PAVIMENTAÇÃO MG-326 (PONTE NOVA A BARRA LONGA)</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
@@ -11423,10 +11436,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>725000</v>
+        <v>0</v>
       </c>
       <c r="R186" t="n">
-        <v>0</v>
+        <v>82286728</v>
       </c>
     </row>
     <row r="187">
@@ -11456,7 +11469,7 @@
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>PAVIMENTAÇÃO MG-326 (PONTE NOVA A BARRA LONGA)</t>
+          <t>PAVIMENTAÇÃO DA MG-314 (ENTR. MG-416 (PEÇANHA) A LMG-744 (COROACI) ENTR. VIRGOLÂNDIA)</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
@@ -11483,7 +11496,7 @@
         <v>0</v>
       </c>
       <c r="R187" t="n">
-        <v>82286728</v>
+        <v>22137718</v>
       </c>
     </row>
     <row r="188">
@@ -11513,7 +11526,7 @@
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>PAVIMENTAÇÃO DA MG-314 (ENTR. MG-416 (PEÇANHA) A LMG-744 (COROACI) ENTR. VIRGOLÂNDIA)</t>
+          <t>PAVIMENTAÇÃO DA RODOVIA MUNICIPAL (SANTA RITA DO ITUETO A ENTR. BR-259 (RESPLENDOR))</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
@@ -11540,7 +11553,7 @@
         <v>0</v>
       </c>
       <c r="R188" t="n">
-        <v>22137718</v>
+        <v>21757581</v>
       </c>
     </row>
     <row r="189">
@@ -11570,7 +11583,7 @@
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>PAVIMENTAÇÃO DA RODOVIA MUNICIPAL (SANTA RITA DO ITUETO A ENTR. BR-259 (RESPLENDOR))</t>
+          <t>RODOVIA MG-010, TRECHO CONCEIÇÃO DO MATO DENTRO - SERRO (DISTRITO DE MATO GROSSO), COM EXTENSÃO DE 21,80 KM</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
@@ -11597,7 +11610,7 @@
         <v>0</v>
       </c>
       <c r="R189" t="n">
-        <v>21757581</v>
+        <v>8036364</v>
       </c>
     </row>
     <row r="190">
@@ -11627,7 +11640,7 @@
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>RODOVIA MG-010, TRECHO CONCEIÇÃO DO MATO DENTRO - SERRO (DISTRITO DE MATO GROSSO), COM EXTENSÃO DE 21,80 KM</t>
+          <t>TRECHO ENTRº LMG-690 (PARACATU) - ENTRº ENTRE RIBEIROS (DISTRITO) - ENTRº MG-181 (ESTACA 1250 A 2000)</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
@@ -11654,7 +11667,7 @@
         <v>0</v>
       </c>
       <c r="R190" t="n">
-        <v>8036364</v>
+        <v>14063636</v>
       </c>
     </row>
     <row r="191">
@@ -11684,7 +11697,7 @@
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>TRECHO ENTRº LMG-690 (PARACATU) - ENTRº ENTRE RIBEIROS (DISTRITO) - ENTRº MG-181 (ESTACA 1250 A 2000)</t>
+          <t>RODOVIA MG-10 - TRECHO CONCEIÇÃO DO MATO DENTRO - SERRO (DISTRITO DE MATO GROSSO), COM EXTENSÃO DE 22,50 KM</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
@@ -11711,7 +11724,7 @@
         <v>0</v>
       </c>
       <c r="R191" t="n">
-        <v>14063636</v>
+        <v>8100000</v>
       </c>
     </row>
     <row r="192">
@@ -11741,7 +11754,7 @@
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>RODOVIA MG-10 - TRECHO CONCEIÇÃO DO MATO DENTRO - SERRO (DISTRITO DE MATO GROSSO), COM EXTENSÃO DE 22,50 KM</t>
+          <t>MELHORAMENTO E PAVIMENTAÇÃO DO CONTORNO DE ANDRADAS</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
@@ -11768,7 +11781,7 @@
         <v>0</v>
       </c>
       <c r="R192" t="n">
-        <v>8100000</v>
+        <v>4804860</v>
       </c>
     </row>
     <row r="193">
@@ -11798,7 +11811,7 @@
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>MELHORAMENTO E PAVIMENTAÇÃO DO CONTORNO DE ANDRADAS</t>
+          <t>EMPREENDIMENTO EM DEFINIÇÃO JUNTO AO BANCO DO BRASIL - CONTRATO DE FINANCIAMENTO Nº 20/00020-0 (PDMG)</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
@@ -11825,7 +11838,7 @@
         <v>0</v>
       </c>
       <c r="R193" t="n">
-        <v>4804860</v>
+        <v>6000001</v>
       </c>
     </row>
     <row r="194">
@@ -11855,7 +11868,7 @@
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>EMPREENDIMENTO EM DEFINIÇÃO JUNTO AO BANCO DO BRASIL - CONTRATO DE FINANCIAMENTO Nº 20/00020-0 (PDMG)</t>
+          <t>COMPLEMENTAÇÃO LMG-680, TRECHO PARACATU (ENTR. LMG-690) - ENTR. ENTRE RIBEIROS - ENTR. MG-181 - (LOTE 1), SEGMENTO 1 (0 A 835), 16,70 KM E SEGMENTO 2 (835 A 1250), 8,30 KM</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
@@ -11879,10 +11892,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>0</v>
+        <v>11326937</v>
       </c>
       <c r="R194" t="n">
-        <v>6000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="195">
@@ -11912,7 +11925,7 @@
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>COMPLEMENTAÇÃO LMG-680, TRECHO PARACATU (ENTR. LMG-690) - ENTR. ENTRE RIBEIROS - ENTR. MG-181 - (LOTE 1), SEGMENTO 1 (0 A 835), 16,70 KM E SEGMENTO 2 (835 A 1250), 8,30 KM</t>
+          <t>COMPLEMENTAÇÃO LMG-680, TRECHO PARACATU (ENTR. LMG-690) - ENTR. ENTRE RIBEIROS - ENTR. MG-181 - ESTACA 2550 A 3281</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
@@ -11936,7 +11949,7 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>11326937</v>
+        <v>19000000</v>
       </c>
       <c r="R195" t="n">
         <v>0</v>
@@ -11969,7 +11982,7 @@
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>COMPLEMENTAÇÃO LMG-680, TRECHO PARACATU (ENTR. LMG-690) - ENTR. ENTRE RIBEIROS - ENTR. MG-181 - ESTACA 2550 A 3281</t>
+          <t>COMPLEMENTO S JANUÁRIA - PANDEIROS, NA RODOVIA MGC-479</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
@@ -11993,7 +12006,7 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>19000000</v>
+        <v>74941120</v>
       </c>
       <c r="R196" t="n">
         <v>0</v>
@@ -12026,7 +12039,7 @@
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>COMPLEMENTO S JANUÁRIA - PANDEIROS, NA RODOVIA MGC-479</t>
+          <t>CONTORNO DE ANDRADAS (COMPLEMENTAÇÃO) - LOTE 01</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
@@ -12050,7 +12063,7 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>74941120</v>
+        <v>38460000</v>
       </c>
       <c r="R197" t="n">
         <v>0</v>
@@ -12083,7 +12096,7 @@
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>CONTORNO DE ANDRADAS (COMPLEMENTAÇÃO) - LOTE 01</t>
+          <t>ENTR. MG-181 (BRASILÂNDIA DE MINAS) - ENTR. BR-365 (BURITIZEIRO), NA MG-408 - LOTE 01</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
@@ -12107,7 +12120,7 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>38460000</v>
+        <v>1000000</v>
       </c>
       <c r="R198" t="n">
         <v>0</v>
@@ -12140,7 +12153,7 @@
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>ENTR. MG-181 (BRASILÂNDIA DE MINAS) - ENTR. BR-365 (BURITIZEIRO), NA MG-408 - LOTE 01</t>
+          <t>IBERTIOGA - PIEDADE DO RIO GRANDE, NA RODOVIA MG-338</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
@@ -12164,7 +12177,7 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>1000000</v>
+        <v>7000000</v>
       </c>
       <c r="R199" t="n">
         <v>0</v>
@@ -12197,7 +12210,7 @@
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>IBERTIOGA - PIEDADE DO RIO GRANDE, NA RODOVIA MG-338</t>
+          <t>INTERSEÇÃO DE ACESSO A COUTO DE MAGALHÃES DE MINAS, NA MGC-367</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
@@ -12221,7 +12234,7 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>7000000</v>
+        <v>1000000</v>
       </c>
       <c r="R200" t="n">
         <v>0</v>
@@ -12254,7 +12267,7 @@
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>INTERSEÇÃO DE ACESSO A COUTO DE MAGALHÃES DE MINAS, NA MGC-367</t>
+          <t>ITAPAGIPE - ENTR. BR-364 (CAMPINA VERDE), RODOVIA MGC-154</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
@@ -12278,7 +12291,7 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>1000000</v>
+        <v>6121131</v>
       </c>
       <c r="R201" t="n">
         <v>0</v>
@@ -12311,7 +12324,7 @@
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>ITAPAGIPE - ENTR. BR-364 (CAMPINA VERDE), RODOVIA MGC-154</t>
+          <t>MG-631 - SÃO JOÃO DA PONTE A CAPITÃO ENÉAS</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
@@ -12335,7 +12348,7 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>6121131</v>
+        <v>1000000</v>
       </c>
       <c r="R202" t="n">
         <v>0</v>
@@ -12368,7 +12381,7 @@
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>MG-631 - SÃO JOÃO DA PONTE A CAPITÃO ENÉAS</t>
+          <t>MELHORAMENTO E PAVIMENTAÇÃO DA RODOVIA LMG-706, SEGMENTO 01: ENTR. BR-040 - VARIANTE (PONTE RIO ESCURO); SEGMENTO 02: VAZAMOR - VAZANTE; SEGMENTO 03: CONTORNO DE VAZANTE - ENTR. BR-354</t>
         </is>
       </c>
       <c r="K203" t="inlineStr">
@@ -12425,7 +12438,7 @@
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>MELHORAMENTO E PAVIMENTAÇÃO DA RODOVIA LMG-706, SEGMENTO 01: ENTR. BR-040 - VARIANTE (PONTE RIO ESCURO); SEGMENTO 02: VAZAMOR - VAZANTE; SEGMENTO 03: CONTORNO DE VAZANTE - ENTR. BR-354</t>
+          <t>ACESSO AO PRESÍDIO DE ITURAMA</t>
         </is>
       </c>
       <c r="K204" t="inlineStr">
@@ -12482,7 +12495,7 @@
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>ACESSO AO PRESÍDIO DE ITURAMA</t>
+          <t>MONTE CARMELO (ENTR. MG-190) - ENTR. LMG-742 (CHAPADA DE MINAS P/ GRUPIARA), NA LMG-746 - LOTE 01 9,50 KM</t>
         </is>
       </c>
       <c r="K205" t="inlineStr">
@@ -12539,7 +12552,7 @@
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>MONTE CARMELO (ENTR. MG-190) - ENTR. LMG-742 (CHAPADA DE MINAS P/ GRUPIARA), NA LMG-746 - LOTE 01 9,50 KM</t>
+          <t>MONTE CARMELO A CHAPADA DE MINAS - LOTE 2</t>
         </is>
       </c>
       <c r="K206" t="inlineStr">
@@ -12596,7 +12609,7 @@
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>MONTE CARMELO A CHAPADA DE MINAS - LOTE 2</t>
+          <t>NATALÂNDIA - ENTR. BR-251, NA LMG-622</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
@@ -12653,7 +12666,7 @@
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>NATALÂNDIA - ENTR. BR-251, NA LMG-622</t>
+          <t>PEÇANHA (ENTR. MG-416) - LMG-744 (COROACI), NA MG-314</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
@@ -12677,7 +12690,7 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>1000000</v>
+        <v>431808</v>
       </c>
       <c r="R208" t="n">
         <v>0</v>
@@ -12710,7 +12723,7 @@
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>PEÇANHA (ENTR. MG-416) - LMG-744 (COROACI), NA MG-314</t>
+          <t>PEDRA AZUL (ENTR. MG-105) - DISTRITO DE PEDRA GRANDE - ALMENARA, MG-251/MG-406, LOTE 01 35 KM</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
@@ -12734,7 +12747,7 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>431808</v>
+        <v>1000000</v>
       </c>
       <c r="R209" t="n">
         <v>0</v>
@@ -12767,7 +12780,7 @@
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>PEDRA AZUL (ENTR. MG-105) - DISTRITO DE PEDRA GRANDE - ALMENARA, MG-251/MG-406, LOTE 01 35 KM</t>
+          <t>PEDRA BONITA - ENTR. BR-116 E INTERSEÇÃO ENTR. BR-116 (COMPLEMENTAÇÃO), RODOVIA LMG-840</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
@@ -12824,7 +12837,7 @@
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>PEDRA BONITA - ENTR. BR-116 E INTERSEÇÃO ENTR. BR-116 (COMPLEMENTAÇÃO), RODOVIA LMG-840</t>
+          <t>PRESIDENTE OLEGÁRIO - GALENA, NA LMG-726</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
@@ -12881,7 +12894,7 @@
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>PRESIDENTE OLEGÁRIO - GALENA, NA LMG-726</t>
+          <t>SANTA RITA DO ITUETO - ENTR. BR-259 (RESPLENDOR) (COMPLEMENTAÇÃO), MUNICIPAL AMG-2320</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
@@ -12905,7 +12918,7 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>1000000</v>
+        <v>14356788</v>
       </c>
       <c r="R212" t="n">
         <v>0</v>
@@ -12938,7 +12951,7 @@
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>SANTA RITA DO ITUETO - ENTR. BR-259 (RESPLENDOR) (COMPLEMENTAÇÃO), MUNICIPAL AMG-2320</t>
+          <t>SÃO DOMINGOS DO PRATA - DOM SILVÉRIO, NA MGC-120</t>
         </is>
       </c>
       <c r="K213" t="inlineStr">
@@ -12962,7 +12975,7 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>14356788</v>
+        <v>100000</v>
       </c>
       <c r="R213" t="n">
         <v>0</v>
@@ -12995,7 +13008,7 @@
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>SÃO DOMINGOS DO PRATA - DOM SILVÉRIO, NA MGC-120</t>
+          <t>UNAÍ (ENTR. BR-251) - PARACATU (ENTR. BR-040) (ESTRADA DO MUNDO NOVO), NA LMG-658 - LOTE 01</t>
         </is>
       </c>
       <c r="K214" t="inlineStr">
@@ -13019,7 +13032,7 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>100000</v>
+        <v>1000000</v>
       </c>
       <c r="R214" t="n">
         <v>0</v>
@@ -13052,7 +13065,7 @@
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>UNAÍ (ENTR. BR-251) - PARACATU (ENTR. BR-040) (ESTRADA DO MUNDO NOVO), NA LMG-658 - LOTE 01</t>
+          <t>ARAÇAÍ - SETE LAGOAS, RODOVIA MUNICIPAL</t>
         </is>
       </c>
       <c r="K215" t="inlineStr">
@@ -13076,7 +13089,7 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>1000000</v>
+        <v>35359852</v>
       </c>
       <c r="R215" t="n">
         <v>0</v>
@@ -13109,7 +13122,7 @@
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>ARAÇAÍ - SETE LAGOAS, RODOVIA MUNICIPAL</t>
+          <t>ARAGUARI (DISTRITO DE AMANHECE) - DIVISA MG/GO, NA MG-414</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
@@ -13133,7 +13146,7 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>35359852</v>
+        <v>29030000</v>
       </c>
       <c r="R216" t="n">
         <v>0</v>
@@ -13166,7 +13179,7 @@
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>ARAGUARI (DISTRITO DE AMANHECE) - DIVISA MG/GO, NA MG-414</t>
+          <t>CAMPO VERDE (DISTRITO E NOVORIZONTE) - FRUTA DE LEITE, NA LMG-626 (LOTE 01 TSD)</t>
         </is>
       </c>
       <c r="K217" t="inlineStr">
@@ -13190,7 +13203,7 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>29030000</v>
+        <v>1000000</v>
       </c>
       <c r="R217" t="n">
         <v>0</v>
@@ -13223,7 +13236,7 @@
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>CAMPO VERDE (DISTRITO E NOVORIZONTE) - FRUTA DE LEITE, NA LMG-626 (LOTE 01 TSD)</t>
+          <t>JABOTICATUBAS - LAGOA SANTA, RODOVIA MUNICIPAL - LOTE 01</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
@@ -13247,7 +13260,7 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>1000000</v>
+        <v>3541727</v>
       </c>
       <c r="R218" t="n">
         <v>0</v>
@@ -13280,7 +13293,7 @@
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>JABOTICATUBAS - LAGOA SANTA, RODOVIA MUNICIPAL - LOTE 01</t>
+          <t xml:space="preserve">LMG-629 (RIO PARDO DE MINAS A ENTRº LMG-635) - LOTE 2 </t>
         </is>
       </c>
       <c r="K219" t="inlineStr">
@@ -13304,7 +13317,7 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>3541727</v>
+        <v>31280000</v>
       </c>
       <c r="R219" t="n">
         <v>0</v>
@@ -13324,7 +13337,7 @@
         <v>81</v>
       </c>
       <c r="E220" t="n">
-        <v>4275</v>
+        <v>4287</v>
       </c>
       <c r="F220" t="n">
         <v>1</v>
@@ -13337,7 +13350,7 @@
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t xml:space="preserve">LMG-629 (RIO PARDO DE MINAS A ENTRº LMG-635) - LOTE 2 </t>
+          <t>Empreendimentos do Acordo Judicial do Rio Doce</t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
@@ -13361,7 +13374,7 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>31280000</v>
+        <v>1000</v>
       </c>
       <c r="R220" t="n">
         <v>0</v>
@@ -13381,7 +13394,7 @@
         <v>81</v>
       </c>
       <c r="E221" t="n">
-        <v>4287</v>
+        <v>4289</v>
       </c>
       <c r="F221" t="n">
         <v>1</v>
@@ -13394,7 +13407,7 @@
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>Empreendimentos do Acordo Judicial do Rio Doce</t>
+          <t>Empreendimentos do Acordo Judicial de Brumadinho</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
@@ -13438,7 +13451,7 @@
         <v>81</v>
       </c>
       <c r="E222" t="n">
-        <v>4289</v>
+        <v>4293</v>
       </c>
       <c r="F222" t="n">
         <v>1</v>
@@ -13451,7 +13464,7 @@
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>Empreendimentos do Acordo Judicial de Brumadinho</t>
+          <t>PROGRAMA DE MICRORREVESTIMENTO ASFÁLTICO</t>
         </is>
       </c>
       <c r="K222" t="inlineStr">
@@ -13475,7 +13488,7 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>1000</v>
+        <v>10000000</v>
       </c>
       <c r="R222" t="n">
         <v>0</v>
@@ -13508,7 +13521,7 @@
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>PROGRAMA DE MICRORREVESTIMENTO ASFÁLTICO</t>
+          <t>REALINHAMENTO DE PREÇOS DO FORNECIMENTO DO MATERIAL BETUMINOSO</t>
         </is>
       </c>
       <c r="K223" t="inlineStr">
@@ -13532,7 +13545,7 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>10000000</v>
+        <v>1406178</v>
       </c>
       <c r="R223" t="n">
         <v>0</v>
@@ -13565,7 +13578,7 @@
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>REALINHAMENTO DE PREÇOS DO FORNECIMENTO DO MATERIAL BETUMINOSO</t>
+          <t>04ª URG BARBACENA</t>
         </is>
       </c>
       <c r="K224" t="inlineStr">
@@ -13589,10 +13602,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>1406178</v>
+        <v>0</v>
       </c>
       <c r="R224" t="n">
-        <v>0</v>
+        <v>12870000</v>
       </c>
     </row>
     <row r="225">
@@ -13622,7 +13635,7 @@
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>04ª URG BARBACENA</t>
+          <t>20ª URG FORMIGA</t>
         </is>
       </c>
       <c r="K225" t="inlineStr">
@@ -13679,7 +13692,7 @@
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>20ª URG FORMIGA</t>
+          <t>28ª URG TEÓFILO OTONI</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
@@ -13706,7 +13719,7 @@
         <v>0</v>
       </c>
       <c r="R226" t="n">
-        <v>12870000</v>
+        <v>9575065</v>
       </c>
     </row>
     <row r="227">
@@ -13736,7 +13749,7 @@
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>28ª URG TEÓFILO OTONI</t>
+          <t>30ª URG JUIZ DE FORA</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
@@ -13763,7 +13776,7 @@
         <v>0</v>
       </c>
       <c r="R227" t="n">
-        <v>9575065</v>
+        <v>12375000</v>
       </c>
     </row>
     <row r="228">
@@ -13793,7 +13806,7 @@
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>30ª URG JUIZ DE FORA</t>
+          <t>01ª URG BELO HORIZONTE - SUL</t>
         </is>
       </c>
       <c r="K228" t="inlineStr">
@@ -13820,7 +13833,7 @@
         <v>0</v>
       </c>
       <c r="R228" t="n">
-        <v>12375000</v>
+        <v>14850000</v>
       </c>
     </row>
     <row r="229">
@@ -13850,7 +13863,7 @@
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>01ª URG BELO HORIZONTE - SUL</t>
+          <t>01ª URG BELO HORIZONTE - NORTE</t>
         </is>
       </c>
       <c r="K229" t="inlineStr">
@@ -13907,7 +13920,7 @@
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>01ª URG BELO HORIZONTE - NORTE</t>
+          <t>31ª URG ITUIUTABA</t>
         </is>
       </c>
       <c r="K230" t="inlineStr">
@@ -13934,7 +13947,7 @@
         <v>0</v>
       </c>
       <c r="R230" t="n">
-        <v>14850000</v>
+        <v>9900000</v>
       </c>
     </row>
     <row r="231">
@@ -13964,7 +13977,7 @@
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>31ª URG ITUIUTABA</t>
+          <t>CONSERVAÇÃO DA MALHA VIÁRIA DAS 40ª URG`S</t>
         </is>
       </c>
       <c r="K231" t="inlineStr">
@@ -13988,10 +14001,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>0</v>
+        <v>654124898</v>
       </c>
       <c r="R231" t="n">
-        <v>9900000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="232">
@@ -14021,7 +14034,7 @@
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>CONSERVAÇÃO DA MALHA VIÁRIA DAS 40ª URG`S</t>
+          <t>CONTRATAÇÃO DE EMPRESA PARA EXECUÇÃO DE SERVIÇOS DE NATUREZA CONTÍNUA DE SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, EM REGIME DE EMPREITADA POR PREÇO UNITÁRIO, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE</t>
         </is>
       </c>
       <c r="K232" t="inlineStr">
@@ -14045,7 +14058,7 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>654124898</v>
+        <v>30767861</v>
       </c>
       <c r="R232" t="n">
         <v>0</v>
@@ -14078,7 +14091,7 @@
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA PARA EXECUÇÃO DE SERVIÇOS DE NATUREZA CONTÍNUA DE SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, EM REGIME DE EMPREITADA POR PREÇO UNITÁRIO, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE</t>
+          <t>MANUTENÇÃO LINHA VERDE E COMPLEXO CIDADE ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="K233" t="inlineStr">
@@ -14102,7 +14115,7 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>30767861</v>
+        <v>19976964</v>
       </c>
       <c r="R233" t="n">
         <v>0</v>
@@ -14135,7 +14148,7 @@
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO LINHA VERDE E COMPLEXO CIDADE ADMINISTRATIVA</t>
+          <t>SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE-OBRA ESPECIALIZADA - LOTE 1</t>
         </is>
       </c>
       <c r="K234" t="inlineStr">
@@ -14159,7 +14172,7 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>19976964</v>
+        <v>12895888</v>
       </c>
       <c r="R234" t="n">
         <v>0</v>
@@ -14192,7 +14205,7 @@
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE-OBRA ESPECIALIZADA - LOTE 1</t>
+          <t>SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE-OBRA ESPECIALIZADA - LOTE 2</t>
         </is>
       </c>
       <c r="K235" t="inlineStr">
@@ -14216,7 +14229,7 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>12895888</v>
+        <v>11846334</v>
       </c>
       <c r="R235" t="n">
         <v>0</v>
@@ -14249,7 +14262,7 @@
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE-OBRA ESPECIALIZADA - LOTE 2</t>
+          <t>SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE-OBRA ESPECIALIZADA - LOTE 3</t>
         </is>
       </c>
       <c r="K236" t="inlineStr">
@@ -14273,7 +14286,7 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>11846334</v>
+        <v>15201174</v>
       </c>
       <c r="R236" t="n">
         <v>0</v>
@@ -14306,7 +14319,7 @@
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE-OBRA ESPECIALIZADA - LOTE 3</t>
+          <t>SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE-OBRA ESPECIALIZADA - LOTE 4</t>
         </is>
       </c>
       <c r="K237" t="inlineStr">
@@ -14330,7 +14343,7 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>15201174</v>
+        <v>12921920</v>
       </c>
       <c r="R237" t="n">
         <v>0</v>
@@ -14350,7 +14363,7 @@
         <v>81</v>
       </c>
       <c r="E238" t="n">
-        <v>4293</v>
+        <v>4385</v>
       </c>
       <c r="F238" t="n">
         <v>1</v>
@@ -14363,7 +14376,7 @@
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE-OBRA ESPECIALIZADA - LOTE 4</t>
+          <t>RECUPERAÇÃO FUNCIONAL MG-232 (BRAÚNAS (DIV. 40ª/ 2ª) - IPATINGA)</t>
         </is>
       </c>
       <c r="K238" t="inlineStr">
@@ -14387,7 +14400,7 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>12921920</v>
+        <v>6382601</v>
       </c>
       <c r="R238" t="n">
         <v>0</v>
@@ -14420,7 +14433,7 @@
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>RECUPERAÇÃO FUNCIONAL MG-232 (BRAÚNAS (DIV. 40ª/ 2ª) - IPATINGA)</t>
+          <t>RECUPERAÇÃO FUNCIONAL MGC-259 ( SABINÓPOLIS - SERRO, GUANHÃES - SABINÓPOLIS E ALVORADA MINAS - SERRO) *</t>
         </is>
       </c>
       <c r="K239" t="inlineStr">
@@ -14444,7 +14457,7 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>6382601</v>
+        <v>30000000</v>
       </c>
       <c r="R239" t="n">
         <v>0</v>
@@ -14477,7 +14490,7 @@
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>RECUPERAÇÃO FUNCIONAL MGC-259 ( SABINÓPOLIS - SERRO, GUANHÃES - SABINÓPOLIS E ALVORADA MINAS - SERRO) *</t>
+          <t>RECUPERAÇÃO FUNCIONAL MGC-455 (PIRAJUBA - ENTRº BR-364 (PLANURA)</t>
         </is>
       </c>
       <c r="K240" t="inlineStr">
@@ -14501,7 +14514,7 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>30000000</v>
+        <v>4000000</v>
       </c>
       <c r="R240" t="n">
         <v>0</v>
@@ -14518,10 +14531,10 @@
         <v>782</v>
       </c>
       <c r="D241" t="n">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="E241" t="n">
-        <v>4385</v>
+        <v>4280</v>
       </c>
       <c r="F241" t="n">
         <v>1</v>
@@ -14534,7 +14547,7 @@
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>RECUPERAÇÃO FUNCIONAL MGC-455 (PIRAJUBA - ENTRº BR-364 (PLANURA)</t>
+          <t>PONTO CRÍTICO: ENTRº BR-040 (BARREIRA DOTRIUNFO) - ENTRº MG-353 (GOIANÁ)</t>
         </is>
       </c>
       <c r="K241" t="inlineStr">
@@ -14591,7 +14604,7 @@
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>PONTO CRÍTICO: ENTRº BR-040 (BARREIRA DOTRIUNFO) - ENTRº MG-353 (GOIANÁ)</t>
+          <t>PONTO CRÍTICO: ENTRº MGC-265 (RIO POMBA) - PONTE RIO POMBA</t>
         </is>
       </c>
       <c r="K242" t="inlineStr">
@@ -14615,7 +14628,7 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>4000000</v>
+        <v>470000</v>
       </c>
       <c r="R242" t="n">
         <v>0</v>
@@ -14648,7 +14661,7 @@
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>PONTO CRÍTICO: ENTRº MGC-265 (RIO POMBA) - PONTE RIO POMBA</t>
+          <t>PONTO CRÍTICO: ENTRº P/ MARIA DA FÉ - INÍCIO DO PERÍMETRO URBANO DE ITAJUBÁ (2  PONTOS)</t>
         </is>
       </c>
       <c r="K243" t="inlineStr">
@@ -14672,7 +14685,7 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>470000</v>
+        <v>4000000</v>
       </c>
       <c r="R243" t="n">
         <v>0</v>
@@ -14705,7 +14718,7 @@
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>PONTO CRÍTICO: ENTRº P/ MARIA DA FÉ - INÍCIO DO PERÍMETRO URBANO DE ITAJUBÁ (2  PONTOS)</t>
+          <t>PONTO CRÍTICO: PALMÓPOLIS - RIO DO PRADO (6 PONTOS)/ PONTE SOBRE O RIBEIRÃO JOSÉ FERREIRA (1 PONTO)</t>
         </is>
       </c>
       <c r="K244" t="inlineStr">
@@ -14729,7 +14742,7 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>4000000</v>
+        <v>1000000</v>
       </c>
       <c r="R244" t="n">
         <v>0</v>
@@ -14762,7 +14775,7 @@
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>PONTO CRÍTICO: PALMÓPOLIS - RIO DO PRADO (6 PONTOS)/ PONTE SOBRE O RIBEIRÃO JOSÉ FERREIRA (1 PONTO)</t>
+          <t>PONTO CRÍTICO: RODEIRO - ENTRº MG-285</t>
         </is>
       </c>
       <c r="K245" t="inlineStr">
@@ -14786,7 +14799,7 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>1000000</v>
+        <v>420000</v>
       </c>
       <c r="R245" t="n">
         <v>0</v>
@@ -14819,7 +14832,7 @@
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>PONTO CRÍTICO: RODEIRO - ENTRº MG-285</t>
+          <t>PONTO CRÍTICO: SABARÁ-CAETÉ (3 PONTOS)</t>
         </is>
       </c>
       <c r="K246" t="inlineStr">
@@ -14843,7 +14856,7 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>420000</v>
+        <v>790000</v>
       </c>
       <c r="R246" t="n">
         <v>0</v>
@@ -14851,19 +14864,19 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>2301</v>
+        <v>2311</v>
       </c>
       <c r="B247" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C247" t="n">
-        <v>782</v>
+        <v>363</v>
       </c>
       <c r="D247" t="n">
-        <v>139</v>
+        <v>7</v>
       </c>
       <c r="E247" t="n">
-        <v>4280</v>
+        <v>4006</v>
       </c>
       <c r="F247" t="n">
         <v>1</v>
@@ -14876,31 +14889,39 @@
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>PONTO CRÍTICO: SABARÁ-CAETÉ (3 PONTOS)</t>
+          <t>Construção da escola do Brasil Profissionalizado no município de Unaí-MG</t>
         </is>
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
-        </is>
+          <t>PARALISADO</t>
+        </is>
+      </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>METRO QUADRADO</t>
+        </is>
+      </c>
+      <c r="M247" t="n">
+        <v>5000</v>
       </c>
       <c r="N247" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O247" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Patos de Minas</t>
         </is>
       </c>
       <c r="P247" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>UNAÍ</t>
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>790000</v>
+        <v>5000000</v>
       </c>
       <c r="R247" t="n">
         <v>0</v>
@@ -14908,19 +14929,19 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>2311</v>
+        <v>2321</v>
       </c>
       <c r="B248" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C248" t="n">
-        <v>363</v>
+        <v>302</v>
       </c>
       <c r="D248" t="n">
-        <v>7</v>
+        <v>87</v>
       </c>
       <c r="E248" t="n">
-        <v>4006</v>
+        <v>4222</v>
       </c>
       <c r="F248" t="n">
         <v>1</v>
@@ -14933,39 +14954,31 @@
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>Construção da escola do Brasil Profissionalizado no município de Unaí-MG</t>
+          <t xml:space="preserve">Projetos em unidade diversas </t>
         </is>
       </c>
       <c r="K248" t="inlineStr">
         <is>
-          <t>PARALISADO</t>
-        </is>
-      </c>
-      <c r="L248" t="inlineStr">
-        <is>
-          <t>METRO QUADRADO</t>
-        </is>
-      </c>
-      <c r="M248" t="n">
-        <v>5000</v>
+          <t>EXECUÇÃO</t>
+        </is>
       </c>
       <c r="N248" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="O248" t="inlineStr">
         <is>
-          <t>Região Intermediária de Patos de Minas</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P248" t="inlineStr">
         <is>
-          <t>UNAÍ</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>5000000</v>
+        <v>800291</v>
       </c>
       <c r="R248" t="n">
         <v>0</v>
@@ -15018,11 +15031,11 @@
       </c>
       <c r="P249" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>BETIM</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>800291</v>
+        <v>174673</v>
       </c>
       <c r="R249" t="n">
         <v>0</v>
@@ -15053,14 +15066,17 @@
       <c r="H250" t="n">
         <v>249</v>
       </c>
+      <c r="I250" t="n">
+        <v>11877</v>
+      </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Projetos em unidade diversas </t>
+          <t>Contrato a obra de reforma e ampliação</t>
         </is>
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -15070,16 +15086,16 @@
       </c>
       <c r="O250" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Barbacena</t>
         </is>
       </c>
       <c r="P250" t="inlineStr">
         <is>
-          <t>BETIM</t>
+          <t>SÃO JOÃO DEL REI</t>
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>174673</v>
+        <v>1088908</v>
       </c>
       <c r="R250" t="n">
         <v>0</v>
@@ -15087,19 +15103,19 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>2321</v>
+        <v>2361</v>
       </c>
       <c r="B251" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="C251" t="n">
-        <v>302</v>
+        <v>846</v>
       </c>
       <c r="D251" t="n">
-        <v>87</v>
+        <v>705</v>
       </c>
       <c r="E251" t="n">
-        <v>4222</v>
+        <v>7004</v>
       </c>
       <c r="F251" t="n">
         <v>1</v>
@@ -15110,12 +15126,9 @@
       <c r="H251" t="n">
         <v>250</v>
       </c>
-      <c r="I251" t="n">
-        <v>11877</v>
-      </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>Contrato a obra de reforma e ampliação</t>
+          <t>Possível adequação da sede</t>
         </is>
       </c>
       <c r="K251" t="inlineStr">
@@ -15127,22 +15140,6 @@
         <is>
           <t>Não</t>
         </is>
-      </c>
-      <c r="O251" t="inlineStr">
-        <is>
-          <t>Região Intermediária de Barbacena</t>
-        </is>
-      </c>
-      <c r="P251" t="inlineStr">
-        <is>
-          <t>SÃO JOÃO DEL REI</t>
-        </is>
-      </c>
-      <c r="Q251" t="n">
-        <v>1088908</v>
-      </c>
-      <c r="R251" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="252">
@@ -15150,16 +15147,16 @@
         <v>2361</v>
       </c>
       <c r="B252" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C252" t="n">
-        <v>846</v>
+        <v>274</v>
       </c>
       <c r="D252" t="n">
-        <v>705</v>
+        <v>766</v>
       </c>
       <c r="E252" t="n">
-        <v>7004</v>
+        <v>2113</v>
       </c>
       <c r="F252" t="n">
         <v>1</v>
@@ -15197,10 +15194,10 @@
         <v>274</v>
       </c>
       <c r="D253" t="n">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="E253" t="n">
-        <v>2113</v>
+        <v>2114</v>
       </c>
       <c r="F253" t="n">
         <v>1</v>
@@ -15213,7 +15210,7 @@
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>Possível adequação da sede</t>
+          <t>Possível obras de adequação da sede.</t>
         </is>
       </c>
       <c r="K253" t="inlineStr">
@@ -15225,23 +15222,39 @@
         <is>
           <t>Não</t>
         </is>
+      </c>
+      <c r="O253" t="inlineStr">
+        <is>
+          <t>Região Intermediária de Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="P253" t="inlineStr">
+        <is>
+          <t>BELO HORIZONTE</t>
+        </is>
+      </c>
+      <c r="Q253" t="n">
+        <v>0</v>
+      </c>
+      <c r="R253" t="n">
+        <v>2754406</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>2361</v>
+        <v>2371</v>
       </c>
       <c r="B254" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C254" t="n">
-        <v>274</v>
+        <v>609</v>
       </c>
       <c r="D254" t="n">
-        <v>767</v>
+        <v>78</v>
       </c>
       <c r="E254" t="n">
-        <v>2114</v>
+        <v>4238</v>
       </c>
       <c r="F254" t="n">
         <v>1</v>
@@ -15254,7 +15267,7 @@
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>Possível obras de adequação da sede.</t>
+          <t>Reestruturação física e ampliação do Laboratório de Química Agropecuária do Instituto Mineiro de Agropecuária - IMA</t>
         </is>
       </c>
       <c r="K254" t="inlineStr">
@@ -15278,27 +15291,27 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>0</v>
+        <v>8311374</v>
       </c>
       <c r="R254" t="n">
-        <v>2754406</v>
+        <v>0</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>2371</v>
+        <v>2421</v>
       </c>
       <c r="B255" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="C255" t="n">
-        <v>609</v>
+        <v>544</v>
       </c>
       <c r="D255" t="n">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="E255" t="n">
-        <v>4238</v>
+        <v>1016</v>
       </c>
       <c r="F255" t="n">
         <v>1</v>
@@ -15311,7 +15324,7 @@
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>Reestruturação física e ampliação do Laboratório de Química Agropecuária do Instituto Mineiro de Agropecuária - IMA</t>
+          <t>Perfuração de Sistemas de Abastecimento de Agua conforme demanda dos municípios atendidos pelo IDENE</t>
         </is>
       </c>
       <c r="K255" t="inlineStr">
@@ -15326,16 +15339,16 @@
       </c>
       <c r="O255" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Montes Claros</t>
         </is>
       </c>
       <c r="P255" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>MONTES CLAROS</t>
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>8311374</v>
+        <v>477508</v>
       </c>
       <c r="R255" t="n">
         <v>0</v>
@@ -15343,19 +15356,19 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>2421</v>
+        <v>3051</v>
       </c>
       <c r="B256" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C256" t="n">
-        <v>544</v>
+        <v>364</v>
       </c>
       <c r="D256" t="n">
-        <v>101</v>
+        <v>15</v>
       </c>
       <c r="E256" t="n">
-        <v>1016</v>
+        <v>4016</v>
       </c>
       <c r="F256" t="n">
         <v>1</v>
@@ -15368,7 +15381,7 @@
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>Perfuração de Sistemas de Abastecimento de Agua conforme demanda dos municípios atendidos pelo IDENE</t>
+          <t>Instalações do curso de Agropecuária de Precisão, com 1.070 m² de área total, além de 5 unidades de tratamento de águas residuárias.</t>
         </is>
       </c>
       <c r="K256" t="inlineStr">
@@ -15383,16 +15396,16 @@
       </c>
       <c r="O256" t="inlineStr">
         <is>
-          <t>Região Intermediária de Montes Claros</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P256" t="inlineStr">
         <is>
-          <t>MONTES CLAROS</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>477508</v>
+        <v>4825656</v>
       </c>
       <c r="R256" t="n">
         <v>0</v>
@@ -15425,7 +15438,7 @@
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>Instalações do curso de Agropecuária de Precisão, com 1.070 m² de área total, além de 5 unidades de tratamento de águas residuárias.</t>
+          <t>Construção de novas instalações no Instituto Tecnológico de Agropecuária de Pitangui - ITAP, totalizando 3.214 m², para salas de aula, plantas-piloto de produção e laboratórios de apoio.</t>
         </is>
       </c>
       <c r="K257" t="inlineStr">
@@ -15449,7 +15462,7 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>4825656</v>
+        <v>12649000</v>
       </c>
       <c r="R257" t="n">
         <v>0</v>
@@ -15482,7 +15495,7 @@
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>Construção de novas instalações no Instituto Tecnológico de Agropecuária de Pitangui - ITAP, totalizando 3.214 m², para salas de aula, plantas-piloto de produção e laboratórios de apoio.</t>
+          <t xml:space="preserve">Reforma do edifício histórico do Instituto de Laticínios Cândido Tostes, localizado no município dde juiz de Fora. </t>
         </is>
       </c>
       <c r="K258" t="inlineStr">
@@ -15506,7 +15519,7 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>12649000</v>
+        <v>3715000</v>
       </c>
       <c r="R258" t="n">
         <v>0</v>
@@ -15517,16 +15530,16 @@
         <v>3051</v>
       </c>
       <c r="B259" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C259" t="n">
-        <v>364</v>
+        <v>571</v>
       </c>
       <c r="D259" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E259" t="n">
-        <v>4016</v>
+        <v>4018</v>
       </c>
       <c r="F259" t="n">
         <v>1</v>
@@ -15539,7 +15552,7 @@
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reforma do edifício histórico do Instituto de Laticínios Cândido Tostes, localizado no município dde juiz de Fora. </t>
+          <t>Melhoria na infraestrutura das unidades de pesquisa.</t>
         </is>
       </c>
       <c r="K259" t="inlineStr">
@@ -15563,27 +15576,27 @@
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>3715000</v>
+        <v>0</v>
       </c>
       <c r="R259" t="n">
-        <v>0</v>
+        <v>250000</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>3051</v>
+        <v>4031</v>
       </c>
       <c r="B260" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="C260" t="n">
-        <v>571</v>
+        <v>61</v>
       </c>
       <c r="D260" t="n">
-        <v>16</v>
+        <v>706</v>
       </c>
       <c r="E260" t="n">
-        <v>4018</v>
+        <v>2091</v>
       </c>
       <c r="F260" t="n">
         <v>1</v>
@@ -15594,36 +15607,47 @@
       <c r="H260" t="n">
         <v>259</v>
       </c>
+      <c r="I260" t="n">
+        <v>12054</v>
+      </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>Melhoria na infraestrutura das unidades de pesquisa.</t>
+          <t xml:space="preserve"> Construção do novo prédio do Fórum da Comarca de Betim/MG</t>
         </is>
       </c>
       <c r="K260" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
-        </is>
+          <t>EXECUÇÃO</t>
+        </is>
+      </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M260" t="n">
+        <v>1</v>
       </c>
       <c r="N260" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O260" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P260" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>BETIM</t>
         </is>
       </c>
       <c r="Q260" t="n">
         <v>0</v>
       </c>
       <c r="R260" t="n">
-        <v>250000</v>
+        <v>11016496</v>
       </c>
     </row>
     <row r="261">
@@ -15652,11 +15676,11 @@
         <v>260</v>
       </c>
       <c r="I261" t="n">
-        <v>12054</v>
+        <v>12806</v>
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Construção do novo prédio do Fórum da Comarca de Betim/MG</t>
+          <t>Campo Belo/MG - Construção do novo Fórum da Comarca de Campo Belo</t>
         </is>
       </c>
       <c r="K261" t="inlineStr">
@@ -15679,19 +15703,19 @@
       </c>
       <c r="O261" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Varginha</t>
         </is>
       </c>
       <c r="P261" t="inlineStr">
         <is>
-          <t>BETIM</t>
+          <t>CAMPO BELO</t>
         </is>
       </c>
       <c r="Q261" t="n">
         <v>0</v>
       </c>
       <c r="R261" t="n">
-        <v>11016496</v>
+        <v>19994210</v>
       </c>
     </row>
     <row r="262">
@@ -15720,11 +15744,11 @@
         <v>261</v>
       </c>
       <c r="I262" t="n">
-        <v>12806</v>
+        <v>12638</v>
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>Campo Belo/MG - Construção do novo Fórum da Comarca de Campo Belo</t>
+          <t>Obra de construção do novo Fórum da Comarca de Carangola.</t>
         </is>
       </c>
       <c r="K262" t="inlineStr">
@@ -15747,19 +15771,19 @@
       </c>
       <c r="O262" t="inlineStr">
         <is>
-          <t>Região Intermediária de Varginha</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P262" t="inlineStr">
         <is>
-          <t>CAMPO BELO</t>
+          <t>CARANGOLA</t>
         </is>
       </c>
       <c r="Q262" t="n">
         <v>0</v>
       </c>
       <c r="R262" t="n">
-        <v>19994210</v>
+        <v>12843388</v>
       </c>
     </row>
     <row r="263">
@@ -15788,11 +15812,11 @@
         <v>262</v>
       </c>
       <c r="I263" t="n">
-        <v>12638</v>
+        <v>12400</v>
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>Obra de construção do novo Fórum da Comarca de Carangola.</t>
+          <t xml:space="preserve"> Contrato a execução da obra de reforma e ampliação do Fórum da Comarca de Ipatinga/MG</t>
         </is>
       </c>
       <c r="K263" t="inlineStr">
@@ -15815,19 +15839,19 @@
       </c>
       <c r="O263" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Ipatinga</t>
         </is>
       </c>
       <c r="P263" t="inlineStr">
         <is>
-          <t>CARANGOLA</t>
+          <t>IPATINGA</t>
         </is>
       </c>
       <c r="Q263" t="n">
         <v>0</v>
       </c>
       <c r="R263" t="n">
-        <v>12843388</v>
+        <v>18849069</v>
       </c>
     </row>
     <row r="264">
@@ -15856,11 +15880,11 @@
         <v>263</v>
       </c>
       <c r="I264" t="n">
-        <v>12400</v>
+        <v>12288</v>
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Contrato a execução da obra de reforma e ampliação do Fórum da Comarca de Ipatinga/MG</t>
+          <t xml:space="preserve"> Reforma e Ampliação do Fórum da Comarca de Monte Belo/MG</t>
         </is>
       </c>
       <c r="K264" t="inlineStr">
@@ -15883,19 +15907,19 @@
       </c>
       <c r="O264" t="inlineStr">
         <is>
-          <t>Região Intermediária de Ipatinga</t>
+          <t>Região Intermediária de Varginha</t>
         </is>
       </c>
       <c r="P264" t="inlineStr">
         <is>
-          <t>IPATINGA</t>
+          <t>MONTE BELO</t>
         </is>
       </c>
       <c r="Q264" t="n">
         <v>0</v>
       </c>
       <c r="R264" t="n">
-        <v>18849069</v>
+        <v>1950000</v>
       </c>
     </row>
     <row r="265">
@@ -15924,11 +15948,11 @@
         <v>264</v>
       </c>
       <c r="I265" t="n">
-        <v>12288</v>
+        <v>12816</v>
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Reforma e Ampliação do Fórum da Comarca de Monte Belo/MG</t>
+          <t>Obra de construção do novo Fórum da Comarca de Pirapora/MG</t>
         </is>
       </c>
       <c r="K265" t="inlineStr">
@@ -15951,19 +15975,19 @@
       </c>
       <c r="O265" t="inlineStr">
         <is>
-          <t>Região Intermediária de Varginha</t>
+          <t>Região Intermediária de Montes Claros</t>
         </is>
       </c>
       <c r="P265" t="inlineStr">
         <is>
-          <t>MONTE BELO</t>
+          <t>PIRAPORA</t>
         </is>
       </c>
       <c r="Q265" t="n">
         <v>0</v>
       </c>
       <c r="R265" t="n">
-        <v>1950000</v>
+        <v>22776109</v>
       </c>
     </row>
     <row r="266">
@@ -15992,11 +16016,11 @@
         <v>265</v>
       </c>
       <c r="I266" t="n">
-        <v>12816</v>
+        <v>12781</v>
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>Obra de construção do novo Fórum da Comarca de Pirapora/MG</t>
+          <t>Construção do novo fórum da Comarca de São Gonçalo do Sapucaí/MG</t>
         </is>
       </c>
       <c r="K266" t="inlineStr">
@@ -16019,19 +16043,19 @@
       </c>
       <c r="O266" t="inlineStr">
         <is>
-          <t>Região Intermediária de Montes Claros</t>
+          <t>Região Intermediária de Varginha</t>
         </is>
       </c>
       <c r="P266" t="inlineStr">
         <is>
-          <t>PIRAPORA</t>
+          <t>SÃO GONÇALO DO SAPUCAÍ</t>
         </is>
       </c>
       <c r="Q266" t="n">
         <v>0</v>
       </c>
       <c r="R266" t="n">
-        <v>22776109</v>
+        <v>14670005</v>
       </c>
     </row>
     <row r="267">
@@ -16060,11 +16084,11 @@
         <v>266</v>
       </c>
       <c r="I267" t="n">
-        <v>12781</v>
+        <v>12799</v>
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>Construção do novo fórum da Comarca de São Gonçalo do Sapucaí/MG</t>
+          <t xml:space="preserve">Construção do novo Fórum da Comarca de Timóteo/MG </t>
         </is>
       </c>
       <c r="K267" t="inlineStr">
@@ -16087,19 +16111,19 @@
       </c>
       <c r="O267" t="inlineStr">
         <is>
-          <t>Região Intermediária de Varginha</t>
+          <t>Região Intermediária de Ipatinga</t>
         </is>
       </c>
       <c r="P267" t="inlineStr">
         <is>
-          <t>SÃO GONÇALO DO SAPUCAÍ</t>
+          <t>TIMÓTEO</t>
         </is>
       </c>
       <c r="Q267" t="n">
         <v>0</v>
       </c>
       <c r="R267" t="n">
-        <v>14670005</v>
+        <v>19506288</v>
       </c>
     </row>
     <row r="268">
@@ -16128,16 +16152,16 @@
         <v>267</v>
       </c>
       <c r="I268" t="n">
-        <v>12799</v>
+        <v>12833</v>
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t xml:space="preserve">Construção do novo Fórum da Comarca de Timóteo/MG </t>
+          <t>Obra de construção do novo Fórum da Comarca de Rio Novo.</t>
         </is>
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
@@ -16155,19 +16179,19 @@
       </c>
       <c r="O268" t="inlineStr">
         <is>
-          <t>Região Intermediária de Ipatinga</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P268" t="inlineStr">
         <is>
-          <t>TIMÓTEO</t>
+          <t>RIO NOVO</t>
         </is>
       </c>
       <c r="Q268" t="n">
         <v>0</v>
       </c>
       <c r="R268" t="n">
-        <v>19506288</v>
+        <v>4976096</v>
       </c>
     </row>
     <row r="269">
@@ -16196,11 +16220,11 @@
         <v>268</v>
       </c>
       <c r="I269" t="n">
-        <v>12833</v>
+        <v>12629</v>
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>Obra de construção do novo Fórum da Comarca de Rio Novo.</t>
+          <t>Obra de construção do novo Fórum da Comarca de Luz.</t>
         </is>
       </c>
       <c r="K269" t="inlineStr">
@@ -16223,19 +16247,19 @@
       </c>
       <c r="O269" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Divinópolis</t>
         </is>
       </c>
       <c r="P269" t="inlineStr">
         <is>
-          <t>RIO NOVO</t>
+          <t>LUZ</t>
         </is>
       </c>
       <c r="Q269" t="n">
         <v>0</v>
       </c>
       <c r="R269" t="n">
-        <v>4976096</v>
+        <v>7654409</v>
       </c>
     </row>
     <row r="270">
@@ -16264,16 +16288,16 @@
         <v>269</v>
       </c>
       <c r="I270" t="n">
-        <v>12629</v>
+        <v>12607</v>
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>Obra de construção do novo Fórum da Comarca de Luz.</t>
+          <t>Reforma e ampliação do Fórum da Comarca de Sete Lagoas/MG.</t>
         </is>
       </c>
       <c r="K270" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
@@ -16291,19 +16315,19 @@
       </c>
       <c r="O270" t="inlineStr">
         <is>
-          <t>Região Intermediária de Divinópolis</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P270" t="inlineStr">
         <is>
-          <t>LUZ</t>
+          <t>SETE LAGOAS</t>
         </is>
       </c>
       <c r="Q270" t="n">
         <v>0</v>
       </c>
       <c r="R270" t="n">
-        <v>7654409</v>
+        <v>32235085</v>
       </c>
     </row>
     <row r="271">
@@ -16332,11 +16356,11 @@
         <v>270</v>
       </c>
       <c r="I271" t="n">
-        <v>12607</v>
+        <v>12639</v>
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>Reforma e ampliação do Fórum da Comarca de Sete Lagoas/MG.</t>
+          <t>Obra de construção do novo Fórum da Comarca de Três Pontas</t>
         </is>
       </c>
       <c r="K271" t="inlineStr">
@@ -16359,19 +16383,19 @@
       </c>
       <c r="O271" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Varginha</t>
         </is>
       </c>
       <c r="P271" t="inlineStr">
         <is>
-          <t>SETE LAGOAS</t>
+          <t>TRÊS PONTAS</t>
         </is>
       </c>
       <c r="Q271" t="n">
         <v>0</v>
       </c>
       <c r="R271" t="n">
-        <v>32235085</v>
+        <v>9489687</v>
       </c>
     </row>
     <row r="272">
@@ -16400,16 +16424,16 @@
         <v>271</v>
       </c>
       <c r="I272" t="n">
-        <v>12639</v>
+        <v>11547</v>
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>Obra de construção do novo Fórum da Comarca de Três Pontas</t>
+          <t>RETOMADA DA OBRA DE CONSTRUÇÃO DO NOVO PRÉDIO DO FÓRUM DA COMARCA DE ITAJUBÁ/MG</t>
         </is>
       </c>
       <c r="K272" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
@@ -16427,19 +16451,19 @@
       </c>
       <c r="O272" t="inlineStr">
         <is>
-          <t>Região Intermediária de Varginha</t>
+          <t>Região Intermediária de Pouso Alegre</t>
         </is>
       </c>
       <c r="P272" t="inlineStr">
         <is>
-          <t>TRÊS PONTAS</t>
+          <t>ITAJUBÁ</t>
         </is>
       </c>
       <c r="Q272" t="n">
         <v>0</v>
       </c>
       <c r="R272" t="n">
-        <v>9489687</v>
+        <v>9366263</v>
       </c>
     </row>
     <row r="273">
@@ -16468,11 +16492,11 @@
         <v>272</v>
       </c>
       <c r="I273" t="n">
-        <v>11547</v>
+        <v>12856</v>
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>RETOMADA DA OBRA DE CONSTRUÇÃO DO NOVO PRÉDIO DO FÓRUM DA COMARCA DE ITAJUBÁ/MG</t>
+          <t>Retomada da obra de construção do novo Fórum da Comarca de Poços de Caldas.</t>
         </is>
       </c>
       <c r="K273" t="inlineStr">
@@ -16500,14 +16524,14 @@
       </c>
       <c r="P273" t="inlineStr">
         <is>
-          <t>ITAJUBÁ</t>
+          <t>POÇOS DE CALDAS</t>
         </is>
       </c>
       <c r="Q273" t="n">
         <v>0</v>
       </c>
       <c r="R273" t="n">
-        <v>9366263</v>
+        <v>11009635</v>
       </c>
     </row>
     <row r="274">
@@ -16536,11 +16560,11 @@
         <v>273</v>
       </c>
       <c r="I274" t="n">
-        <v>12856</v>
+        <v>12344</v>
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>Retomada da obra de construção do novo Fórum da Comarca de Poços de Caldas.</t>
+          <t>Construção do novo prédio do Fórum da Comarca de Camanducaia/MG</t>
         </is>
       </c>
       <c r="K274" t="inlineStr">
@@ -16568,14 +16592,14 @@
       </c>
       <c r="P274" t="inlineStr">
         <is>
-          <t>POÇOS DE CALDAS</t>
+          <t>CAMANDUCAIA</t>
         </is>
       </c>
       <c r="Q274" t="n">
         <v>0</v>
       </c>
       <c r="R274" t="n">
-        <v>11009635</v>
+        <v>4627222</v>
       </c>
     </row>
     <row r="275">
@@ -16603,12 +16627,9 @@
       <c r="H275" t="n">
         <v>274</v>
       </c>
-      <c r="I275" t="n">
-        <v>12344</v>
-      </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t>Construção do novo prédio do Fórum da Comarca de Camanducaia/MG</t>
+          <t>Obra de construção do novo Fórum da Comarca de São João do Paraíso</t>
         </is>
       </c>
       <c r="K275" t="inlineStr">
@@ -16631,19 +16652,19 @@
       </c>
       <c r="O275" t="inlineStr">
         <is>
-          <t>Região Intermediária de Pouso Alegre</t>
+          <t>Região Intermediária de Montes Claros</t>
         </is>
       </c>
       <c r="P275" t="inlineStr">
         <is>
-          <t>CAMANDUCAIA</t>
+          <t>SÃO JOÃO DO PARAÍSO</t>
         </is>
       </c>
       <c r="Q275" t="n">
         <v>0</v>
       </c>
       <c r="R275" t="n">
-        <v>4627222</v>
+        <v>7290196</v>
       </c>
     </row>
     <row r="276">
@@ -16673,7 +16694,7 @@
       </c>
       <c r="J276" t="inlineStr">
         <is>
-          <t>Obra de construção do novo Fórum da Comarca de São João do Paraíso</t>
+          <t>Implantação do Fórum Digital no município de Brasilândia de Minas</t>
         </is>
       </c>
       <c r="K276" t="inlineStr">
@@ -16696,19 +16717,19 @@
       </c>
       <c r="O276" t="inlineStr">
         <is>
-          <t>Região Intermediária de Montes Claros</t>
+          <t>Região Intermediária de Patos de Minas</t>
         </is>
       </c>
       <c r="P276" t="inlineStr">
         <is>
-          <t>SÃO JOÃO DO PARAÍSO</t>
+          <t>BRASILÂNDIA DE MINAS</t>
         </is>
       </c>
       <c r="Q276" t="n">
         <v>0</v>
       </c>
       <c r="R276" t="n">
-        <v>7290196</v>
+        <v>1373680</v>
       </c>
     </row>
     <row r="277">
@@ -16738,7 +16759,7 @@
       </c>
       <c r="J277" t="inlineStr">
         <is>
-          <t>Implantação do Fórum Digital no município de Brasilândia de Minas</t>
+          <t>Implantação do Fórum Digital no município de São Gonçalo do Abaeté</t>
         </is>
       </c>
       <c r="K277" t="inlineStr">
@@ -16766,7 +16787,7 @@
       </c>
       <c r="P277" t="inlineStr">
         <is>
-          <t>BRASILÂNDIA DE MINAS</t>
+          <t>SÃO GONÇALO DO ABAETÉ</t>
         </is>
       </c>
       <c r="Q277" t="n">
@@ -16803,7 +16824,7 @@
       </c>
       <c r="J278" t="inlineStr">
         <is>
-          <t>Implantação do Fórum Digital no município de São Gonçalo do Abaeté</t>
+          <t>Implantação do Fórum Digital no município de Ponto Chique</t>
         </is>
       </c>
       <c r="K278" t="inlineStr">
@@ -16826,19 +16847,19 @@
       </c>
       <c r="O278" t="inlineStr">
         <is>
-          <t>Região Intermediária de Patos de Minas</t>
+          <t>Região Intermediária de Montes Claros</t>
         </is>
       </c>
       <c r="P278" t="inlineStr">
         <is>
-          <t>SÃO GONÇALO DO ABAETÉ</t>
+          <t>PONTO CHIQUE</t>
         </is>
       </c>
       <c r="Q278" t="n">
         <v>0</v>
       </c>
       <c r="R278" t="n">
-        <v>1373680</v>
+        <v>1760000</v>
       </c>
     </row>
     <row r="279">
@@ -16866,14 +16887,17 @@
       <c r="H279" t="n">
         <v>278</v>
       </c>
+      <c r="I279" t="n">
+        <v>12627</v>
+      </c>
       <c r="J279" t="inlineStr">
         <is>
-          <t>Implantação do Fórum Digital no município de Ponto Chique</t>
+          <t>Execução da 4ª (quarta) parcela da reforma parcial do Edifício-Sede do TRIBUNAL.</t>
         </is>
       </c>
       <c r="K279" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L279" t="inlineStr">
@@ -16891,19 +16915,19 @@
       </c>
       <c r="O279" t="inlineStr">
         <is>
-          <t>Região Intermediária de Montes Claros</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P279" t="inlineStr">
         <is>
-          <t>PONTO CHIQUE</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q279" t="n">
         <v>0</v>
       </c>
       <c r="R279" t="n">
-        <v>1760000</v>
+        <v>38084213</v>
       </c>
     </row>
     <row r="280">
@@ -16932,11 +16956,11 @@
         <v>279</v>
       </c>
       <c r="I280" t="n">
-        <v>12627</v>
+        <v>12146</v>
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>Execução da 4ª (quarta) parcela da reforma parcial do Edifício-Sede do TRIBUNAL.</t>
+          <t>Reforma geral do Fórum Lafayette, em Belo Horizonte/MG</t>
         </is>
       </c>
       <c r="K280" t="inlineStr">
@@ -16971,7 +16995,7 @@
         <v>0</v>
       </c>
       <c r="R280" t="n">
-        <v>38084213</v>
+        <v>135013067</v>
       </c>
     </row>
     <row r="281">
@@ -17000,11 +17024,11 @@
         <v>280</v>
       </c>
       <c r="I281" t="n">
-        <v>12146</v>
+        <v>12703</v>
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>Reforma geral do Fórum Lafayette, em Belo Horizonte/MG</t>
+          <t>Cincão - Reforma parcial para adequações da estrutura física dos Armazéns 6, 7 e 8, Galpão 2, Arquivo Central e Permanente</t>
         </is>
       </c>
       <c r="K281" t="inlineStr">
@@ -17039,7 +17063,7 @@
         <v>0</v>
       </c>
       <c r="R281" t="n">
-        <v>135013067</v>
+        <v>1052449</v>
       </c>
     </row>
     <row r="282">
@@ -17067,17 +17091,14 @@
       <c r="H282" t="n">
         <v>281</v>
       </c>
-      <c r="I282" t="n">
-        <v>12703</v>
-      </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>Cincão - Reforma parcial para adequações da estrutura física dos Armazéns 6, 7 e 8, Galpão 2, Arquivo Central e Permanente</t>
+          <t>Obra de construção do novo Fórum da Comarca de Monte Alegre de Minas</t>
         </is>
       </c>
       <c r="K282" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L282" t="inlineStr">
@@ -17095,36 +17116,36 @@
       </c>
       <c r="O282" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Uberlândia</t>
         </is>
       </c>
       <c r="P282" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>MONTE ALEGRE DE MINAS</t>
         </is>
       </c>
       <c r="Q282" t="n">
         <v>0</v>
       </c>
       <c r="R282" t="n">
-        <v>1052449</v>
+        <v>6139672</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>4031</v>
+        <v>5011</v>
       </c>
       <c r="B283" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C283" t="n">
-        <v>61</v>
+        <v>122</v>
       </c>
       <c r="D283" t="n">
-        <v>706</v>
+        <v>133</v>
       </c>
       <c r="E283" t="n">
-        <v>2091</v>
+        <v>3017</v>
       </c>
       <c r="F283" t="n">
         <v>1</v>
@@ -17137,7 +17158,7 @@
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>Obra de construção do novo Fórum da Comarca de Monte Alegre de Minas</t>
+          <t>CENTRO DE CULTURA PRESIDENTE ITAMAR FRANCO</t>
         </is>
       </c>
       <c r="K283" t="inlineStr">
@@ -17145,51 +17166,43 @@
           <t>INICIANDO</t>
         </is>
       </c>
-      <c r="L283" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M283" t="n">
-        <v>1</v>
-      </c>
       <c r="N283" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="O283" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberlândia</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P283" t="inlineStr">
         <is>
-          <t>MONTE ALEGRE DE MINAS</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q283" t="n">
         <v>0</v>
       </c>
       <c r="R283" t="n">
-        <v>6139672</v>
+        <v>800000</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>5011</v>
+        <v>5031</v>
       </c>
       <c r="B284" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="C284" t="n">
-        <v>122</v>
+        <v>572</v>
       </c>
       <c r="D284" t="n">
         <v>133</v>
       </c>
       <c r="E284" t="n">
-        <v>3017</v>
+        <v>3015</v>
       </c>
       <c r="F284" t="n">
         <v>1</v>
@@ -17202,7 +17215,7 @@
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>CENTRO DE CULTURA PRESIDENTE ITAMAR FRANCO</t>
+          <t>BALNEÁRIO ÁGUAS SANTAS - TIRADENTES/MG | BARREIO DE ARAXÁ</t>
         </is>
       </c>
       <c r="K284" t="inlineStr">
@@ -17229,24 +17242,24 @@
         <v>0</v>
       </c>
       <c r="R284" t="n">
-        <v>800000</v>
+        <v>4782988</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>5031</v>
+        <v>5141</v>
       </c>
       <c r="B285" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="C285" t="n">
-        <v>572</v>
+        <v>126</v>
       </c>
       <c r="D285" t="n">
-        <v>133</v>
+        <v>30</v>
       </c>
       <c r="E285" t="n">
-        <v>3015</v>
+        <v>6006</v>
       </c>
       <c r="F285" t="n">
         <v>1</v>
@@ -17259,7 +17272,7 @@
       </c>
       <c r="J285" t="inlineStr">
         <is>
-          <t>BALNEÁRIO ÁGUAS SANTAS - TIRADENTES/MG | BARREIO DE ARAXÁ</t>
+          <t>ELABORAÇÃO E EXECUÇÃO DE PROJETOS RELACIONADOS À REFORMA, MODERNIZAÇÃO E ADEQUAÇÃO DAS INSTALAÇÕES PREDIAIS DA COMPANHIA.</t>
         </is>
       </c>
       <c r="K285" t="inlineStr">
@@ -17286,24 +17299,24 @@
         <v>0</v>
       </c>
       <c r="R285" t="n">
-        <v>4782988</v>
+        <v>16317109</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>5141</v>
+        <v>5251</v>
       </c>
       <c r="B286" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C286" t="n">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D286" t="n">
-        <v>30</v>
+        <v>133</v>
       </c>
       <c r="E286" t="n">
-        <v>6006</v>
+        <v>3018</v>
       </c>
       <c r="F286" t="n">
         <v>1</v>
@@ -17316,12 +17329,12 @@
       </c>
       <c r="J286" t="inlineStr">
         <is>
-          <t>ELABORAÇÃO E EXECUÇÃO DE PROJETOS RELACIONADOS À REFORMA, MODERNIZAÇÃO E ADEQUAÇÃO DAS INSTALAÇÕES PREDIAIS DA COMPANHIA.</t>
+          <t>Projeto de Expansão</t>
         </is>
       </c>
       <c r="K286" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
@@ -17331,36 +17344,36 @@
       </c>
       <c r="O286" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P286" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q286" t="n">
         <v>0</v>
       </c>
       <c r="R286" t="n">
-        <v>16317109</v>
+        <v>457766318</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>5251</v>
+        <v>5391</v>
       </c>
       <c r="B287" t="n">
         <v>25</v>
       </c>
       <c r="C287" t="n">
-        <v>121</v>
+        <v>752</v>
       </c>
       <c r="D287" t="n">
-        <v>133</v>
+        <v>92</v>
       </c>
       <c r="E287" t="n">
-        <v>3018</v>
+        <v>3004</v>
       </c>
       <c r="F287" t="n">
         <v>1</v>
@@ -17373,12 +17386,12 @@
       </c>
       <c r="J287" t="inlineStr">
         <is>
-          <t>Projeto de Expansão</t>
+          <t xml:space="preserve">Expansão e Aquisição do Sistema de Transmissão </t>
         </is>
       </c>
       <c r="K287" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="N287" t="inlineStr">
@@ -17393,14 +17406,14 @@
       </c>
       <c r="P287" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q287" t="n">
         <v>0</v>
       </c>
       <c r="R287" t="n">
-        <v>457766318</v>
+        <v>92004926</v>
       </c>
     </row>
     <row r="288">
@@ -17445,19 +17458,19 @@
       </c>
       <c r="O288" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Montes Claros</t>
         </is>
       </c>
       <c r="P288" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BELO HORIZONTE</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE MONTES CLAROS</t>
         </is>
       </c>
       <c r="Q288" t="n">
         <v>0</v>
       </c>
       <c r="R288" t="n">
-        <v>92004926</v>
+        <v>10705994</v>
       </c>
     </row>
     <row r="289">
@@ -17502,19 +17515,19 @@
       </c>
       <c r="O289" t="inlineStr">
         <is>
-          <t>Região Intermediária de Montes Claros</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P289" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE MONTES CLAROS</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE JUÍZ DE FORA</t>
         </is>
       </c>
       <c r="Q289" t="n">
         <v>0</v>
       </c>
       <c r="R289" t="n">
-        <v>10705994</v>
+        <v>10464844</v>
       </c>
     </row>
     <row r="290">
@@ -17559,19 +17572,19 @@
       </c>
       <c r="O290" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Uberlândia</t>
         </is>
       </c>
       <c r="P290" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE JUÍZ DE FORA</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERLÂNDIA</t>
         </is>
       </c>
       <c r="Q290" t="n">
         <v>0</v>
       </c>
       <c r="R290" t="n">
-        <v>10464844</v>
+        <v>2098278</v>
       </c>
     </row>
     <row r="291">
@@ -17616,19 +17629,19 @@
       </c>
       <c r="O291" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberlândia</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P291" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERLÂNDIA</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q291" t="n">
         <v>0</v>
       </c>
       <c r="R291" t="n">
-        <v>2098278</v>
+        <v>96721858</v>
       </c>
     </row>
     <row r="292">
@@ -17673,19 +17686,19 @@
       </c>
       <c r="O292" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Uberaba</t>
         </is>
       </c>
       <c r="P292" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERABA</t>
         </is>
       </c>
       <c r="Q292" t="n">
         <v>0</v>
       </c>
       <c r="R292" t="n">
-        <v>96721858</v>
+        <v>16415074</v>
       </c>
     </row>
     <row r="293">
@@ -17730,19 +17743,19 @@
       </c>
       <c r="O293" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberaba</t>
+          <t>Região Intermediária de Ipatinga</t>
         </is>
       </c>
       <c r="P293" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERABA</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE IPATINGA</t>
         </is>
       </c>
       <c r="Q293" t="n">
         <v>0</v>
       </c>
       <c r="R293" t="n">
-        <v>16415074</v>
+        <v>1</v>
       </c>
     </row>
     <row r="294">
@@ -17759,7 +17772,7 @@
         <v>92</v>
       </c>
       <c r="E294" t="n">
-        <v>3004</v>
+        <v>3005</v>
       </c>
       <c r="F294" t="n">
         <v>1</v>
@@ -17772,7 +17785,7 @@
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t xml:space="preserve">Expansão e Aquisição do Sistema de Transmissão </t>
+          <t>Reformas de Subestações e Linhas de Transmissão</t>
         </is>
       </c>
       <c r="K294" t="inlineStr">
@@ -17787,19 +17800,19 @@
       </c>
       <c r="O294" t="inlineStr">
         <is>
-          <t>Região Intermediária de Ipatinga</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P294" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE IPATINGA</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q294" t="n">
         <v>0</v>
       </c>
       <c r="R294" t="n">
-        <v>1</v>
+        <v>126817302</v>
       </c>
     </row>
     <row r="295">
@@ -17844,19 +17857,19 @@
       </c>
       <c r="O295" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Montes Claros</t>
         </is>
       </c>
       <c r="P295" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BELO HORIZONTE</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE MONTES CLAROS</t>
         </is>
       </c>
       <c r="Q295" t="n">
         <v>0</v>
       </c>
       <c r="R295" t="n">
-        <v>126817302</v>
+        <v>16058991</v>
       </c>
     </row>
     <row r="296">
@@ -17901,19 +17914,19 @@
       </c>
       <c r="O296" t="inlineStr">
         <is>
-          <t>Região Intermediária de Montes Claros</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P296" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE MONTES CLAROS</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE JUÍZ DE FORA</t>
         </is>
       </c>
       <c r="Q296" t="n">
         <v>0</v>
       </c>
       <c r="R296" t="n">
-        <v>16058991</v>
+        <v>65795530</v>
       </c>
     </row>
     <row r="297">
@@ -17958,19 +17971,19 @@
       </c>
       <c r="O297" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Uberlândia</t>
         </is>
       </c>
       <c r="P297" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE JUÍZ DE FORA</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERLÂNDIA</t>
         </is>
       </c>
       <c r="Q297" t="n">
         <v>0</v>
       </c>
       <c r="R297" t="n">
-        <v>65795530</v>
+        <v>44156794</v>
       </c>
     </row>
     <row r="298">
@@ -18015,19 +18028,19 @@
       </c>
       <c r="O298" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberlândia</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P298" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERLÂNDIA</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q298" t="n">
         <v>0</v>
       </c>
       <c r="R298" t="n">
-        <v>44156794</v>
+        <v>140716908</v>
       </c>
     </row>
     <row r="299">
@@ -18072,19 +18085,19 @@
       </c>
       <c r="O299" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Ipatinga</t>
         </is>
       </c>
       <c r="P299" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE IPATINGA</t>
         </is>
       </c>
       <c r="Q299" t="n">
         <v>0</v>
       </c>
       <c r="R299" t="n">
-        <v>140716908</v>
+        <v>8715687</v>
       </c>
     </row>
     <row r="300">
@@ -18129,19 +18142,19 @@
       </c>
       <c r="O300" t="inlineStr">
         <is>
-          <t>Região Intermediária de Ipatinga</t>
+          <t>Região Intermediária de Uberaba</t>
         </is>
       </c>
       <c r="P300" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE IPATINGA</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERABA</t>
         </is>
       </c>
       <c r="Q300" t="n">
         <v>0</v>
       </c>
       <c r="R300" t="n">
-        <v>8715687</v>
+        <v>24622611</v>
       </c>
     </row>
     <row r="301">
@@ -18155,10 +18168,10 @@
         <v>752</v>
       </c>
       <c r="D301" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E301" t="n">
-        <v>3005</v>
+        <v>3001</v>
       </c>
       <c r="F301" t="n">
         <v>1</v>
@@ -18171,7 +18184,7 @@
       </c>
       <c r="J301" t="inlineStr">
         <is>
-          <t>Reformas de Subestações e Linhas de Transmissão</t>
+          <t>Expansão do Sistema de Geração</t>
         </is>
       </c>
       <c r="K301" t="inlineStr">
@@ -18186,75 +18199,18 @@
       </c>
       <c r="O301" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberaba</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P301" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERABA</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q301" t="n">
         <v>0</v>
       </c>
       <c r="R301" t="n">
-        <v>24622611</v>
-      </c>
-    </row>
-    <row r="302">
-      <c r="A302" t="n">
-        <v>5391</v>
-      </c>
-      <c r="B302" t="n">
-        <v>25</v>
-      </c>
-      <c r="C302" t="n">
-        <v>752</v>
-      </c>
-      <c r="D302" t="n">
-        <v>94</v>
-      </c>
-      <c r="E302" t="n">
-        <v>3001</v>
-      </c>
-      <c r="F302" t="n">
-        <v>1</v>
-      </c>
-      <c r="G302" t="n">
-        <v>0</v>
-      </c>
-      <c r="H302" t="n">
-        <v>301</v>
-      </c>
-      <c r="J302" t="inlineStr">
-        <is>
-          <t>Expansão do Sistema de Geração</t>
-        </is>
-      </c>
-      <c r="K302" t="inlineStr">
-        <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="N302" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="O302" t="inlineStr">
-        <is>
-          <t>Estadual</t>
-        </is>
-      </c>
-      <c r="P302" t="inlineStr">
-        <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
-        </is>
-      </c>
-      <c r="Q302" t="n">
-        <v>0</v>
-      </c>
-      <c r="R302" t="n">
         <v>1</v>
       </c>
     </row>

--- a/bancos/SISOR/BASE_DETALHAMENTO_OBRAS.xlsx
+++ b/bancos/SISOR/BASE_DETALHAMENTO_OBRAS.xlsx
@@ -8676,7 +8676,7 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>ARCOS - CORUMBÁ - RODOVIA: MG-170 (ENTR BR-354 - AGRIMIG)</t>
+          <t>MG-129 - OURO PRETO A OURO BRANCO</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -8700,7 +8700,7 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>9792000</v>
+        <v>1000000</v>
       </c>
       <c r="R138" t="n">
         <v>0</v>
@@ -8733,7 +8733,7 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>MG-129 - OURO PRETO A OURO BRANCO</t>
+          <t>RECUPERAÇÃO DE EROSÃO EM TALUDE DE CORTE NA RODOVIA MGC-354, KM 167,8, TRECHO: RIBEIRÃO DA MATA - AV MARABÁ (PATOS DE MINAS)</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -8757,7 +8757,7 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>1000000</v>
+        <v>143000</v>
       </c>
       <c r="R139" t="n">
         <v>0</v>
@@ -8790,7 +8790,7 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>RECUPERAÇÃO DE EROSÃO EM TALUDE DE CORTE NA RODOVIA MGC-354, KM 167,8, TRECHO: RIBEIRÃO DA MATA - AV MARABÁ (PATOS DE MINAS)</t>
+          <t>RESTAURAÇÃO DA INTERSEÇÃO NA RODOVIA MGC-354, KM 150,9, TRECHO: TRAVESSIA URBANA DE PRESIDENTE OLEGÁRIO</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -8814,7 +8814,7 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>143000</v>
+        <v>5876140</v>
       </c>
       <c r="R140" t="n">
         <v>0</v>
@@ -8847,7 +8847,7 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO DA INTERSEÇÃO NA RODOVIA MGC-354, KM 150,9, TRECHO: TRAVESSIA URBANA DE PRESIDENTE OLEGÁRIO</t>
+          <t>RESTAURAÇÃO DA INTERSEÇÃO NA RODOVIA MGC-354, KM 176,2, TRECHO: AV MARABÁ (PATOS DE MINAS) - ENTR BR 365</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -8871,7 +8871,7 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>5876140</v>
+        <v>1132500</v>
       </c>
       <c r="R141" t="n">
         <v>0</v>
@@ -8904,7 +8904,7 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO DA INTERSEÇÃO NA RODOVIA MGC-354, KM 176,2, TRECHO: AV MARABÁ (PATOS DE MINAS) - ENTR BR 365</t>
+          <t>RESTAURAÇÃO E AUMENTO DE CAPACIDADE (3ª FAIXA) DO TRECHO SERRA DO SALITRE - SALITRE DE MINAS, NA MG-230</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -8928,7 +8928,7 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>1132500</v>
+        <v>34710000</v>
       </c>
       <c r="R142" t="n">
         <v>0</v>
@@ -8961,7 +8961,7 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO E 3ª FAIXA, TRECHO ENTR. BR-354 (CAXAMBÚ) - ENTR. BR-381 (PALMELA DISTRITO DE CAMPANHA), NA MGC-267</t>
+          <t>RESTAURAÇÃO E AUMENTO DE CAPACIDADE DO TRECHO MG-344 (ENTR. P/ CÁSSIA) - DIVISA MG/SP, NA MG-444, EXT. 23,9 KM</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -8985,7 +8985,7 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>1000000</v>
+        <v>59000000</v>
       </c>
       <c r="R143" t="n">
         <v>0</v>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO E AUMENTO DE CAPACIDADE (3ª FAIXA) DO TRECHO SERRA DO SALITRE - SALITRE DE MINAS, NA MG-230</t>
+          <t>RESTAURAÇÃO E AUMENTO DE CAPACIDADE DO TRECHO PARÁ DE MINAS - PAPAGAIOS (3ª FAIXA) - LOTE 1</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -9042,7 +9042,7 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>34710000</v>
+        <v>1000000</v>
       </c>
       <c r="R144" t="n">
         <v>0</v>
@@ -9075,7 +9075,7 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO E AUMENTO DE CAPACIDADE DO TRECHO MG-344 (ENTR. P/ CÁSSIA) - DIVISA MG/SP, NA MG-444, EXT. 23,9 KM</t>
+          <t>RESTAURAÇÃO TIMÓTEO - ENTR. LMG-760 (CAVA GRANDE), NA MG-425</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -9099,7 +9099,7 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>59000000</v>
+        <v>200000</v>
       </c>
       <c r="R145" t="n">
         <v>0</v>
@@ -9132,7 +9132,7 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO E AUMENTO DE CAPACIDADE DO TRECHO PARÁ DE MINAS - PAPAGAIOS (3ª FAIXA) - LOTE 1</t>
+          <t>RESTAURAÇÃO TRECHO ENTR. MGC-120 (B) (DONA EUZÉBIA) - ENTR. MGC-265, NA MG-285</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -9156,7 +9156,7 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>1000000</v>
+        <v>30980000</v>
       </c>
       <c r="R146" t="n">
         <v>0</v>
@@ -9189,7 +9189,7 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO E AUMENTO DE CAPACIDADE DO TRECHO: UNAÍ A GARAPUAVA</t>
+          <t>RESTAURAÇÃO TRECHO ENTR. MGC-265/MG-452 (P/ PAIVA) - ENTR. BR-040, NA MG-448</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -9213,7 +9213,7 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>1000000</v>
+        <v>25655000</v>
       </c>
       <c r="R147" t="n">
         <v>0</v>
@@ -9246,7 +9246,7 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO TIMÓTEO - ENTR. LMG-760 (CAVA GRANDE), NA MG-425</t>
+          <t>RESTAURAÇÃO TRECHO PIRAÚBA (ENTR. MG-285) - PAIVA (ENTR. MG-488/MG-455), NA MG-265 E 3ª FAIXA</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
@@ -9270,7 +9270,7 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>200000</v>
+        <v>66560000</v>
       </c>
       <c r="R148" t="n">
         <v>0</v>
@@ -9303,7 +9303,7 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO TRECHO ENTR. LMG764 (P/ MATUTINA) - SÃO GOTARDO, NA MG- 235 - 3ª FAIXA</t>
+          <t>RESTAURAÇÃO TRÊS PONTAS - VARGINHA, NA MG-167</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
@@ -9327,7 +9327,7 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>1000000</v>
+        <v>25464500</v>
       </c>
       <c r="R149" t="n">
         <v>0</v>
@@ -9347,7 +9347,7 @@
         <v>81</v>
       </c>
       <c r="E150" t="n">
-        <v>4268</v>
+        <v>4272</v>
       </c>
       <c r="F150" t="n">
         <v>1</v>
@@ -9360,7 +9360,7 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO TRECHO ENTR. MGC-120 (B) (DONA EUZÉBIA) - ENTR. MGC-265, NA MG-285</t>
+          <t>COMPLEMENTAÇÃO DA CONSTRUÇÃO DA PONTE SOBRE O RIO SÃO FRANCISCO, PINTÓPOLIS</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -9384,7 +9384,7 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>30980000</v>
+        <v>1202905</v>
       </c>
       <c r="R150" t="n">
         <v>0</v>
@@ -9404,7 +9404,7 @@
         <v>81</v>
       </c>
       <c r="E151" t="n">
-        <v>4268</v>
+        <v>4272</v>
       </c>
       <c r="F151" t="n">
         <v>1</v>
@@ -9417,7 +9417,7 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO TRECHO ENTR. MGC-265/MG-452 (P/ PAIVA) - ENTR. BR-040, NA MG-448</t>
+          <t>ENCABEÇAMENTO E PONTE SOBRE O CÓRREGO DAS LAJES, TRECHO ENTR. MGC-479 (SERRA DAS ARARAS) - ENTR. MG-402, NA LMG-622</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
@@ -9441,7 +9441,7 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>25655000</v>
+        <v>1000000</v>
       </c>
       <c r="R151" t="n">
         <v>0</v>
@@ -9461,7 +9461,7 @@
         <v>81</v>
       </c>
       <c r="E152" t="n">
-        <v>4268</v>
+        <v>4272</v>
       </c>
       <c r="F152" t="n">
         <v>1</v>
@@ -9474,7 +9474,7 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO TRECHO PIRAÚBA (ENTR. MG-285) - PAIVA (ENTR. MG-488/MG-455), NA MG-265 E 3ª FAIXA</t>
+          <t>ENCABEÇAMENTO E PONTE SOBRE O RIO SÃO JOÃO, TRECHO IGARATINGA - ENTR. MG-252, NA MG-430 (SEMI-INTEGRADA)</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -9498,7 +9498,7 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>66560000</v>
+        <v>14920000</v>
       </c>
       <c r="R152" t="n">
         <v>0</v>
@@ -9518,7 +9518,7 @@
         <v>81</v>
       </c>
       <c r="E153" t="n">
-        <v>4268</v>
+        <v>4272</v>
       </c>
       <c r="F153" t="n">
         <v>1</v>
@@ -9531,7 +9531,7 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO TRECHO SÃO GOTARDO - ENTR. BR-354 (P/ PATOS DE MINAS), NA MG-235</t>
+          <t>ENCABEÇAMENTO E PONTE SOBRE O RIO SERRA BRANCA, TRECHO PAI PEDRO - CATUTI, NA MGC-122</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
@@ -9555,7 +9555,7 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>1000000</v>
+        <v>8798400</v>
       </c>
       <c r="R153" t="n">
         <v>0</v>
@@ -9575,7 +9575,7 @@
         <v>81</v>
       </c>
       <c r="E154" t="n">
-        <v>4268</v>
+        <v>4272</v>
       </c>
       <c r="F154" t="n">
         <v>1</v>
@@ -9588,7 +9588,7 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO TRÊS PONTAS - VARGINHA, NA MG-167</t>
+          <t>LMG-722 (ROCHINHA A LAGAMAR, PONTE SOBRE O RIO PARANAÍBA)</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
@@ -9612,7 +9612,7 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>25464500</v>
+        <v>1000000</v>
       </c>
       <c r="R154" t="n">
         <v>0</v>
@@ -9645,7 +9645,7 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>BDCC 3X3 CÓRREGO CAVALO, TRECHO ENTR. BR-040 - PORTO DIAMANTE</t>
+          <t>MGC-267 (CORDISLÂNDIA A CARVALHÓPOLIS, PONTE SOBRE O RIO SAPUCAÍ -  LOTE 01)</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
@@ -9669,7 +9669,7 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>100000</v>
+        <v>1203643</v>
       </c>
       <c r="R155" t="n">
         <v>0</v>
@@ -9702,7 +9702,7 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>COMPLEMENTAÇÃO DA CONSTRUÇÃO DA PONTE SOBRE O RIO SÃO FRANCISCO, PINTÓPOLIS</t>
+          <t>PASSARELA MG-010 (CIDADE ADMINISTRATIVA)</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
@@ -9726,7 +9726,7 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>24000000</v>
+        <v>66620</v>
       </c>
       <c r="R156" t="n">
         <v>0</v>
@@ -9759,7 +9759,7 @@
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>ENCABEÇAMENTO E PONTE CÓRREGO SÃO BARTOLOMEU E ENCABEÇAMENTO CÓRREGO BARBADINHO, TRECHO CANABRAVA (JOÃO PINHEIRO) - ENTR. MG-181, NA LMG-698</t>
+          <t>PONTE SOBRE O EXTRAVASOR DA CEMIG, TRECHO JANUÁRIA - RIO PARDO - PANDEIROS, NA MGC-479</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
@@ -9783,7 +9783,7 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>252000</v>
+        <v>1000000</v>
       </c>
       <c r="R157" t="n">
         <v>0</v>
@@ -9816,7 +9816,7 @@
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>ENCABEÇAMENTO E PONTE SOBRE CÓRREGO AMENDOIM, NO TRECHO RIACHINHO - GUARAPUAVA (UNAÍ), NA LMG-638</t>
+          <t>PONTE SOBRE O RIBEIRÃO MATA BOI NA RODOVIA MG-414, TRECHO ARAGUARI (DISTRITO DE AMANHECE) - DIVISA MG/GO</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
@@ -9840,7 +9840,7 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>319200</v>
+        <v>2940000</v>
       </c>
       <c r="R158" t="n">
         <v>0</v>
@@ -9873,7 +9873,7 @@
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>ENCABEÇAMENTO E PONTE SOBRE CÓRREGO BOI PRETO, NO TRECHO RIACHINHO - GUARAPUAVA (UNAÍ), NA LMG-638</t>
+          <t>PONTE SOBRE O RIBEIRÃO PANDEIROS, TRECHO JANUÁRIA - RIO PARDO - PANDEIROS, NA MGC-479</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
@@ -9897,7 +9897,7 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>495600</v>
+        <v>1000000</v>
       </c>
       <c r="R159" t="n">
         <v>0</v>
@@ -9930,7 +9930,7 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>ENCABEÇAMENTO E PONTE SOBRE O CÓRREGO DAS LAJES, TRECHO ENTR. MGC-479 (SERRA DAS ARARAS) - ENTR. MG-402, NA LMG-622</t>
+          <t>PONTE SOBRE O RIO ARAGUARI (TROCA DOS APARELHOS DE DO 1º E 5º VÃOS), TRECHO ENTR. MG-190 - ZELÂNDIA (USINA SANTA JULIANA), DIMENSÕES 130,00X12,20M, RODOVIA AMG-0730</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
@@ -9954,7 +9954,7 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>679000</v>
+        <v>542000</v>
       </c>
       <c r="R160" t="n">
         <v>0</v>
@@ -9987,7 +9987,7 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>ENCABEÇAMENTO E PONTE SOBRE O RIO SANTO INÁCIO, TRECHO ENTR. MG-188 (COROMANDEL) - DISTRITO DE VEREDA, NA LMG-747</t>
+          <t>PONTE SOBRE O RIO CORRENTE -  MG-460, NO TRECHO DE MUNHOZ - TOLEDO ( E SEMI-INTEGRADA)</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
@@ -10011,7 +10011,7 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>440000</v>
+        <v>2163814</v>
       </c>
       <c r="R161" t="n">
         <v>0</v>
@@ -10044,7 +10044,7 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>ENCABEÇAMENTO E PONTE SOBRE O RIO SÃO JOÃO, TRECHO IGARATINGA - ENTR. MG-252, NA MG-430 (SEMI-INTEGRADA)</t>
+          <t>PONTE SOBRE O RIO SÃO FRANCISCO - ENTR. MGC-135 (MANGA) ¿ PORTO DE MATIAS CARDOSO, NA RODOVIA MG-401</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
@@ -10068,7 +10068,7 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>14920000</v>
+        <v>11974837</v>
       </c>
       <c r="R162" t="n">
         <v>0</v>
@@ -10101,7 +10101,7 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>ENCABEÇAMENTO E PONTE SOBRE O RIO SERRA BRANCA, TRECHO PAI PEDRO - CATUTI, NA MGC-122</t>
+          <t>RECUPERAÇÃO DA PONTE S/ O RIO JEQUITINHONHA- DIAMANTINA - COUTO MAGALHÃES.</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
@@ -10125,7 +10125,7 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>8798400</v>
+        <v>1382535</v>
       </c>
       <c r="R163" t="n">
         <v>0</v>
@@ -10145,7 +10145,7 @@
         <v>81</v>
       </c>
       <c r="E164" t="n">
-        <v>4272</v>
+        <v>4275</v>
       </c>
       <c r="F164" t="n">
         <v>1</v>
@@ -10158,7 +10158,7 @@
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>ENCABEÇAMENTOS E PONTES SOBRE CÓRREGO VEREDINHA E RIBEIRÃO MARQUES, NO TRECHO RIACHINHO - GUARAPUAVA (UNAÍ), NA LMG-638</t>
+          <t>ACESSO AO PRESÍDIO DE ITURAMA</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
@@ -10182,7 +10182,7 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>369600</v>
+        <v>1000000</v>
       </c>
       <c r="R164" t="n">
         <v>0</v>
@@ -10202,7 +10202,7 @@
         <v>81</v>
       </c>
       <c r="E165" t="n">
-        <v>4272</v>
+        <v>4275</v>
       </c>
       <c r="F165" t="n">
         <v>1</v>
@@ -10215,7 +10215,7 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>LMG-722 (ROCHINHA A LAGAMAR, PONTE SOBRE O RIO PARANAÍBA)</t>
+          <t>ARAÇAÍ - SETE LAGOAS, RODOVIA MUNICIPAL</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
@@ -10239,7 +10239,7 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>1000000</v>
+        <v>35359853</v>
       </c>
       <c r="R165" t="n">
         <v>0</v>
@@ -10259,7 +10259,7 @@
         <v>81</v>
       </c>
       <c r="E166" t="n">
-        <v>4272</v>
+        <v>4275</v>
       </c>
       <c r="F166" t="n">
         <v>1</v>
@@ -10272,7 +10272,7 @@
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>MGC-267 (CORDISLÂNDIA A CARVALHÓPOLIS, PONTE SOBRE O RIO SAPUCAÍ -  LOTE 01)</t>
+          <t>ARAGUARI (DISTRITO DE AMANHECE) - DIVISA MG/GO, NA MG-414</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
@@ -10296,7 +10296,7 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>1203643</v>
+        <v>13982612</v>
       </c>
       <c r="R166" t="n">
         <v>0</v>
@@ -10316,7 +10316,7 @@
         <v>81</v>
       </c>
       <c r="E167" t="n">
-        <v>4272</v>
+        <v>4275</v>
       </c>
       <c r="F167" t="n">
         <v>1</v>
@@ -10329,7 +10329,7 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>OLHOS D´AGUA DO OESTE A SANTA LUZIA DA SERRA - CÓRREGO SÃO BARTOLOMEU</t>
+          <t>CAMPO VERDE (DISTRITO E NOVORIZONTE) - FRUTA DE LEITE, NA LMG-626 (LOTE 01 TSD)</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
@@ -10353,7 +10353,7 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>730000</v>
+        <v>1000000</v>
       </c>
       <c r="R167" t="n">
         <v>0</v>
@@ -10373,7 +10373,7 @@
         <v>81</v>
       </c>
       <c r="E168" t="n">
-        <v>4272</v>
+        <v>4275</v>
       </c>
       <c r="F168" t="n">
         <v>1</v>
@@ -10386,7 +10386,7 @@
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>PASSARELA MG-010 (CIDADE ADMINISTRATIVA)</t>
+          <t>COMPLEMENTAÇÃO LMG-680, TRECHO PARACATU (ENTR. LMG-690) - ENTR. ENTRE RIBEIROS - ENTR. MG-181 - (LOTE 1), SEGMENTO 1 (0 A 835), 16,70 KM E SEGMENTO 2 (835 A 1250), 8,30 KM</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
@@ -10410,7 +10410,7 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>66619</v>
+        <v>10459632</v>
       </c>
       <c r="R168" t="n">
         <v>0</v>
@@ -10430,7 +10430,7 @@
         <v>81</v>
       </c>
       <c r="E169" t="n">
-        <v>4272</v>
+        <v>4275</v>
       </c>
       <c r="F169" t="n">
         <v>1</v>
@@ -10443,7 +10443,7 @@
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>PONTE CÓRREGO PERUAÇU, TRECHO CÔNEGO MARINHO - MIRAVÂNIA (RESERVA XACRIABÁ)</t>
+          <t>COMPLEMENTAÇÃO LMG-680, TRECHO PARACATU (ENTR. LMG-690) - ENTR. ENTRE RIBEIROS - ENTR. MG-181 - ESTACA 2550 A 3281</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
@@ -10467,7 +10467,7 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>901000</v>
+        <v>17000000</v>
       </c>
       <c r="R169" t="n">
         <v>0</v>
@@ -10487,7 +10487,7 @@
         <v>81</v>
       </c>
       <c r="E170" t="n">
-        <v>4272</v>
+        <v>4275</v>
       </c>
       <c r="F170" t="n">
         <v>1</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>PONTE CÓRREGO RIBEIRÃO, TRECHO ENTR. BR-040 - PORTO DIAMANTE</t>
+          <t>COMPLEMENTO S JANUÁRIA - PANDEIROS, NA RODOVIA MGC-479</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
@@ -10524,7 +10524,7 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>100000</v>
+        <v>74941121</v>
       </c>
       <c r="R170" t="n">
         <v>0</v>
@@ -10544,7 +10544,7 @@
         <v>81</v>
       </c>
       <c r="E171" t="n">
-        <v>4272</v>
+        <v>4275</v>
       </c>
       <c r="F171" t="n">
         <v>1</v>
@@ -10557,7 +10557,7 @@
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>PONTE SOBRE O EXTRAVASOR DA CEMIG, TRECHO JANUÁRIA - RIO PARDO - PANDEIROS, NA MGC-479</t>
+          <t>CONTORNO DE ANDRADAS (COMPLEMENTAÇÃO) - LOTE 01</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
@@ -10581,7 +10581,7 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>170000</v>
+        <v>38460000</v>
       </c>
       <c r="R171" t="n">
         <v>0</v>
@@ -10601,7 +10601,7 @@
         <v>81</v>
       </c>
       <c r="E172" t="n">
-        <v>4272</v>
+        <v>4275</v>
       </c>
       <c r="F172" t="n">
         <v>1</v>
@@ -10614,7 +10614,7 @@
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>PONTE SOBRE O RIBEIRÃO MATA BOI NA RODOVIA MG-414, TRECHO ARAGUARI (DISTRITO DE AMANHECE) - DIVISA MG/GO</t>
+          <t>ENTR. MG-181 (BRASILÂNDIA DE MINAS) - ENTR. BR-365 (BURITIZEIRO), NA MG-408 - LOTE 01</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
@@ -10638,7 +10638,7 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>2940000</v>
+        <v>1000000</v>
       </c>
       <c r="R172" t="n">
         <v>0</v>
@@ -10658,7 +10658,7 @@
         <v>81</v>
       </c>
       <c r="E173" t="n">
-        <v>4272</v>
+        <v>4275</v>
       </c>
       <c r="F173" t="n">
         <v>1</v>
@@ -10671,7 +10671,7 @@
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>PONTE SOBRE O RIBEIRÃO PANDEIROS, TRECHO JANUÁRIA - RIO PARDO - PANDEIROS, NA MGC-479</t>
+          <t>IBERTIOGA - PIEDADE DO RIO GRANDE, NA RODOVIA MG-338</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
@@ -10695,7 +10695,7 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>810000</v>
+        <v>7000000</v>
       </c>
       <c r="R173" t="n">
         <v>0</v>
@@ -10715,7 +10715,7 @@
         <v>81</v>
       </c>
       <c r="E174" t="n">
-        <v>4272</v>
+        <v>4275</v>
       </c>
       <c r="F174" t="n">
         <v>1</v>
@@ -10728,7 +10728,7 @@
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>PONTE SOBRE O RIO ARAGUARI (TROCA DOS APARELHOS DE DO 1º E 5º VÃOS), TRECHO ENTR. MG-190 - ZELÂNDIA (USINA SANTA JULIANA), DIMENSÕES 130,00X12,20M, RODOVIA AMG-0730</t>
+          <t>INTERSEÇÃO DE ACESSO A COUTO DE MAGALHÃES DE MINAS, NA MGC-367</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
@@ -10752,7 +10752,7 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>542000</v>
+        <v>1000000</v>
       </c>
       <c r="R174" t="n">
         <v>0</v>
@@ -10772,7 +10772,7 @@
         <v>81</v>
       </c>
       <c r="E175" t="n">
-        <v>4272</v>
+        <v>4275</v>
       </c>
       <c r="F175" t="n">
         <v>1</v>
@@ -10785,7 +10785,7 @@
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>PONTE SOBRE O RIO CORRENTE -  MG-460, NO TRECHO DE MUNHOZ - TOLEDO ( E SEMI-INTEGRADA)</t>
+          <t>PAVIMENTAÇÃO MG-326 (PONTE NOVA A BARRA LONGA)</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
@@ -10809,10 +10809,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>2163814</v>
+        <v>0</v>
       </c>
       <c r="R175" t="n">
-        <v>0</v>
+        <v>82286724</v>
       </c>
     </row>
     <row r="176">
@@ -10829,7 +10829,7 @@
         <v>81</v>
       </c>
       <c r="E176" t="n">
-        <v>4272</v>
+        <v>4275</v>
       </c>
       <c r="F176" t="n">
         <v>1</v>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>PONTE SOBRE O RIO SÃO FRANCISCO - ENTR. MGC-135 (MANGA) ¿ PORTO DE MATIAS CARDOSO, NA RODOVIA MG-401</t>
+          <t>PAVIMENTAÇÃO DA MG-314 (ENTR. MG-416 (PEÇANHA) A LMG-744 (COROACI) ENTR. VIRGOLÂNDIA)</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
@@ -10866,10 +10866,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>25000000</v>
+        <v>0</v>
       </c>
       <c r="R176" t="n">
-        <v>0</v>
+        <v>22137718</v>
       </c>
     </row>
     <row r="177">
@@ -10886,7 +10886,7 @@
         <v>81</v>
       </c>
       <c r="E177" t="n">
-        <v>4272</v>
+        <v>4275</v>
       </c>
       <c r="F177" t="n">
         <v>1</v>
@@ -10899,7 +10899,7 @@
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>PONTES SOBRE OS RIOS SUAÇUI PEQUENO I E II, TRECHO PEÇANHA - COROACI, NA MG-314</t>
+          <t>PAVIMENTAÇÃO DA RODOVIA MUNICIPAL (SANTA RITA DO ITUETO A ENTR. BR-259 (RESPLENDOR))</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
@@ -10923,10 +10923,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="R177" t="n">
-        <v>0</v>
+        <v>21757581</v>
       </c>
     </row>
     <row r="178">
@@ -10943,7 +10943,7 @@
         <v>81</v>
       </c>
       <c r="E178" t="n">
-        <v>4272</v>
+        <v>4275</v>
       </c>
       <c r="F178" t="n">
         <v>1</v>
@@ -10956,7 +10956,7 @@
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>RECUPERAÇÃO DA PONTE S/ O RIO JEQUITINHONHA- DIAMANTINA - COUTO MAGALHÃES.</t>
+          <t>RODOVIA MG-010, TRECHO CONCEIÇÃO DO MATO DENTRO - SERRO (DISTRITO DE MATO GROSSO), COM EXTENSÃO DE 21,80 KM</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
@@ -10980,10 +10980,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>1382535</v>
+        <v>0</v>
       </c>
       <c r="R178" t="n">
-        <v>0</v>
+        <v>8036364</v>
       </c>
     </row>
     <row r="179">
@@ -11000,7 +11000,7 @@
         <v>81</v>
       </c>
       <c r="E179" t="n">
-        <v>4272</v>
+        <v>4275</v>
       </c>
       <c r="F179" t="n">
         <v>1</v>
@@ -11013,7 +11013,7 @@
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>RECUPERAÇÃO ESTRUTURAL DA PONTE SOBRE O RIO PARACATU, TRECHO JOÃO PINHEIRO - BRASÍLÂNDIA DE MINAS, NA MG-181</t>
+          <t>TRECHO ENTRº LMG-690 (PARACATU) - ENTRº ENTRE RIBEIROS (DISTRITO) - ENTRº MG-181 (ESTACA 1250 A 2000)</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
@@ -11037,10 +11037,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="R179" t="n">
-        <v>0</v>
+        <v>14063636</v>
       </c>
     </row>
     <row r="180">
@@ -11057,7 +11057,7 @@
         <v>81</v>
       </c>
       <c r="E180" t="n">
-        <v>4272</v>
+        <v>4275</v>
       </c>
       <c r="F180" t="n">
         <v>1</v>
@@ -11070,7 +11070,7 @@
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>RECUPERAÇÃO ESTRUTURAL DA PONTE SOBRE O RIO PARACATU, TRECHO JOÃO PINHEIRO (ENTR. MG-408) - BRASÍLÂNDIA DE MINAS, NA MG-181</t>
+          <t>RODOVIA MG-10 - TRECHO CONCEIÇÃO DO MATO DENTRO - SERRO (DISTRITO DE MATO GROSSO), COM EXTENSÃO DE 22,50 KM</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
@@ -11094,10 +11094,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>900000</v>
+        <v>0</v>
       </c>
       <c r="R180" t="n">
-        <v>0</v>
+        <v>8100000</v>
       </c>
     </row>
     <row r="181">
@@ -11114,7 +11114,7 @@
         <v>81</v>
       </c>
       <c r="E181" t="n">
-        <v>4272</v>
+        <v>4275</v>
       </c>
       <c r="F181" t="n">
         <v>1</v>
@@ -11127,7 +11127,7 @@
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>REFORÇO DA FUNDAÇÃO DA PONTE SOBRE O RIBEIRÃO DAS ARARAS I, TRECHO GUANHÃES - SÃO PEDRO DO SUAÇUÍ, NA CMG-120</t>
+          <t>MELHORAMENTO E PAVIMENTAÇÃO DO CONTORNO DE ANDRADAS</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
@@ -11151,10 +11151,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>168000</v>
+        <v>0</v>
       </c>
       <c r="R181" t="n">
-        <v>0</v>
+        <v>4804860</v>
       </c>
     </row>
     <row r="182">
@@ -11171,7 +11171,7 @@
         <v>81</v>
       </c>
       <c r="E182" t="n">
-        <v>4272</v>
+        <v>4275</v>
       </c>
       <c r="F182" t="n">
         <v>1</v>
@@ -11184,7 +11184,7 @@
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>REFORÇO DA FUNDAÇÃO DA PONTE SOBRE O RIBEIRÃO MACAÚBAS, TRECHO SANTA LUZIA - JABOTICATUBAS, MG-020</t>
+          <t>EMPREENDIMENTO EM DEFINIÇÃO JUNTO AO BANCO DO BRASIL - CONTRATO DE FINANCIAMENTO Nº 20/00020-0 (PDMG)</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
@@ -11208,10 +11208,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>249000</v>
+        <v>0</v>
       </c>
       <c r="R182" t="n">
-        <v>0</v>
+        <v>6000001</v>
       </c>
     </row>
     <row r="183">
@@ -11228,7 +11228,7 @@
         <v>81</v>
       </c>
       <c r="E183" t="n">
-        <v>4272</v>
+        <v>4275</v>
       </c>
       <c r="F183" t="n">
         <v>1</v>
@@ -11241,7 +11241,7 @@
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>REFORÇO DA FUNDAÇÃO DO VIADUTO II NA PISTA DIREITA DA INTERSEÇÃO 3 (ACESSO AO INHOTIM, ESTACA 138)</t>
+          <t>SÃO DOMINGOS DO PRATA - DOM SILVÉRIO, NA MGC-120</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
@@ -11265,7 +11265,7 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>705000</v>
+        <v>100000</v>
       </c>
       <c r="R183" t="n">
         <v>0</v>
@@ -11285,7 +11285,7 @@
         <v>81</v>
       </c>
       <c r="E184" t="n">
-        <v>4272</v>
+        <v>4275</v>
       </c>
       <c r="F184" t="n">
         <v>1</v>
@@ -11298,7 +11298,7 @@
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>REFORÇO DE FUNDAÇÃO CÓRREGO DOIDOS, TRECHO SÃO FRANCISCO DE PAULA - ENTR. BR-354</t>
+          <t>ITAPAGIPE - ENTR. BR-364 (CAMPINA VERDE), RODOVIA MGC-154</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
@@ -11322,7 +11322,7 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>58800</v>
+        <v>6121132</v>
       </c>
       <c r="R184" t="n">
         <v>0</v>
@@ -11342,7 +11342,7 @@
         <v>81</v>
       </c>
       <c r="E185" t="n">
-        <v>4272</v>
+        <v>4275</v>
       </c>
       <c r="F185" t="n">
         <v>1</v>
@@ -11355,7 +11355,7 @@
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>REFORÇO NA FUNDAÇÃO DA PONTE SOBRE O RIO VERMELHO, TRECHO SANTA BÁRBARA - CATAS ALTAS, NA MG-129</t>
+          <t>JABOTICATUBAS - LAGOA SANTA, RODOVIA MUNICIPAL - LOTE 01</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
@@ -11379,7 +11379,7 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>725000</v>
+        <v>3541728</v>
       </c>
       <c r="R185" t="n">
         <v>0</v>
@@ -11412,7 +11412,7 @@
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>PAVIMENTAÇÃO MG-326 (PONTE NOVA A BARRA LONGA)</t>
+          <t>LMG-629 (RIO PARDO DE MINAS A ENTRº LMG-635) - LOTE 2</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
@@ -11436,10 +11436,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>0</v>
+        <v>22254062</v>
       </c>
       <c r="R186" t="n">
-        <v>82286728</v>
+        <v>0</v>
       </c>
     </row>
     <row r="187">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>PAVIMENTAÇÃO DA MG-314 (ENTR. MG-416 (PEÇANHA) A LMG-744 (COROACI) ENTR. VIRGOLÂNDIA)</t>
+          <t>MELHORAMENTO E PAVIMENTAÇÃO DA RODOVIA LMG-706, SEGMENTO 01: ENTR. BR-040 - VARIANTE (PONTE RIO ESCURO); SEGMENTO 02: VAZAMOR - VAZANTE; SEGMENTO 03: CONTORNO DE VAZANTE - ENTR. BR-354</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
@@ -11493,10 +11493,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="R187" t="n">
-        <v>22137718</v>
+        <v>0</v>
       </c>
     </row>
     <row r="188">
@@ -11526,7 +11526,7 @@
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>PAVIMENTAÇÃO DA RODOVIA MUNICIPAL (SANTA RITA DO ITUETO A ENTR. BR-259 (RESPLENDOR))</t>
+          <t>MONTE CARMELO (ENTR. MG-190) - ENTR. LMG-742 (CHAPADA DE MINAS P/ GRUPIARA), NA LMG-746 - LOTE 01 9,50 KM</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
@@ -11550,10 +11550,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="R188" t="n">
-        <v>21757581</v>
+        <v>0</v>
       </c>
     </row>
     <row r="189">
@@ -11583,7 +11583,7 @@
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>RODOVIA MG-010, TRECHO CONCEIÇÃO DO MATO DENTRO - SERRO (DISTRITO DE MATO GROSSO), COM EXTENSÃO DE 21,80 KM</t>
+          <t>PEÇANHA (ENTR. MG-416) - LMG-744 (COROACI), NA MG-314</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
@@ -11607,10 +11607,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>0</v>
+        <v>431809</v>
       </c>
       <c r="R189" t="n">
-        <v>8036364</v>
+        <v>0</v>
       </c>
     </row>
     <row r="190">
@@ -11640,7 +11640,7 @@
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>TRECHO ENTRº LMG-690 (PARACATU) - ENTRº ENTRE RIBEIROS (DISTRITO) - ENTRº MG-181 (ESTACA 1250 A 2000)</t>
+          <t>PEDRA BONITA - ENTR. BR-116 E INTERSEÇÃO ENTR. BR-116 (COMPLEMENTAÇÃO), RODOVIA LMG-840</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
@@ -11664,10 +11664,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="R190" t="n">
-        <v>14063636</v>
+        <v>0</v>
       </c>
     </row>
     <row r="191">
@@ -11697,7 +11697,7 @@
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>RODOVIA MG-10 - TRECHO CONCEIÇÃO DO MATO DENTRO - SERRO (DISTRITO DE MATO GROSSO), COM EXTENSÃO DE 22,50 KM</t>
+          <t>SANTA RITA DO ITUETO - ENTR. BR-259 (RESPLENDOR) (COMPLEMENTAÇÃO), MUNICIPAL AMG-2320</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
@@ -11721,10 +11721,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>0</v>
+        <v>14356790</v>
       </c>
       <c r="R191" t="n">
-        <v>8100000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="192">
@@ -11741,7 +11741,7 @@
         <v>81</v>
       </c>
       <c r="E192" t="n">
-        <v>4275</v>
+        <v>4287</v>
       </c>
       <c r="F192" t="n">
         <v>1</v>
@@ -11754,7 +11754,7 @@
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>MELHORAMENTO E PAVIMENTAÇÃO DO CONTORNO DE ANDRADAS</t>
+          <t>Empreendimentos do Acordo Judicial do Rio Doce</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
@@ -11778,10 +11778,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="R192" t="n">
-        <v>4804860</v>
+        <v>0</v>
       </c>
     </row>
     <row r="193">
@@ -11798,7 +11798,7 @@
         <v>81</v>
       </c>
       <c r="E193" t="n">
-        <v>4275</v>
+        <v>4289</v>
       </c>
       <c r="F193" t="n">
         <v>1</v>
@@ -11811,7 +11811,7 @@
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>EMPREENDIMENTO EM DEFINIÇÃO JUNTO AO BANCO DO BRASIL - CONTRATO DE FINANCIAMENTO Nº 20/00020-0 (PDMG)</t>
+          <t>Empreendimentos do Acordo Judicial de Brumadinho</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
@@ -11835,10 +11835,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="R193" t="n">
-        <v>6000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="194">
@@ -11855,7 +11855,7 @@
         <v>81</v>
       </c>
       <c r="E194" t="n">
-        <v>4275</v>
+        <v>4293</v>
       </c>
       <c r="F194" t="n">
         <v>1</v>
@@ -11868,7 +11868,7 @@
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>COMPLEMENTAÇÃO LMG-680, TRECHO PARACATU (ENTR. LMG-690) - ENTR. ENTRE RIBEIROS - ENTR. MG-181 - (LOTE 1), SEGMENTO 1 (0 A 835), 16,70 KM E SEGMENTO 2 (835 A 1250), 8,30 KM</t>
+          <t>04ª URG BARBACENA</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
@@ -11892,10 +11892,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>11326937</v>
+        <v>0</v>
       </c>
       <c r="R194" t="n">
-        <v>0</v>
+        <v>12870000</v>
       </c>
     </row>
     <row r="195">
@@ -11912,7 +11912,7 @@
         <v>81</v>
       </c>
       <c r="E195" t="n">
-        <v>4275</v>
+        <v>4293</v>
       </c>
       <c r="F195" t="n">
         <v>1</v>
@@ -11925,7 +11925,7 @@
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>COMPLEMENTAÇÃO LMG-680, TRECHO PARACATU (ENTR. LMG-690) - ENTR. ENTRE RIBEIROS - ENTR. MG-181 - ESTACA 2550 A 3281</t>
+          <t>20ª URG FORMIGA</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
@@ -11949,10 +11949,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>19000000</v>
+        <v>0</v>
       </c>
       <c r="R195" t="n">
-        <v>0</v>
+        <v>12870000</v>
       </c>
     </row>
     <row r="196">
@@ -11969,7 +11969,7 @@
         <v>81</v>
       </c>
       <c r="E196" t="n">
-        <v>4275</v>
+        <v>4293</v>
       </c>
       <c r="F196" t="n">
         <v>1</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>COMPLEMENTO S JANUÁRIA - PANDEIROS, NA RODOVIA MGC-479</t>
+          <t>28ª URG TEÓFILO OTONI</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
@@ -12006,10 +12006,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>74941120</v>
+        <v>0</v>
       </c>
       <c r="R196" t="n">
-        <v>0</v>
+        <v>9575065</v>
       </c>
     </row>
     <row r="197">
@@ -12026,7 +12026,7 @@
         <v>81</v>
       </c>
       <c r="E197" t="n">
-        <v>4275</v>
+        <v>4293</v>
       </c>
       <c r="F197" t="n">
         <v>1</v>
@@ -12039,7 +12039,7 @@
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>CONTORNO DE ANDRADAS (COMPLEMENTAÇÃO) - LOTE 01</t>
+          <t>30ª URG JUIZ DE FORA</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
@@ -12063,10 +12063,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>38460000</v>
+        <v>0</v>
       </c>
       <c r="R197" t="n">
-        <v>0</v>
+        <v>12375000</v>
       </c>
     </row>
     <row r="198">
@@ -12083,7 +12083,7 @@
         <v>81</v>
       </c>
       <c r="E198" t="n">
-        <v>4275</v>
+        <v>4293</v>
       </c>
       <c r="F198" t="n">
         <v>1</v>
@@ -12096,7 +12096,7 @@
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>ENTR. MG-181 (BRASILÂNDIA DE MINAS) - ENTR. BR-365 (BURITIZEIRO), NA MG-408 - LOTE 01</t>
+          <t>01ª URG BELO HORIZONTE - SUL</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
@@ -12120,10 +12120,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="R198" t="n">
-        <v>0</v>
+        <v>14850000</v>
       </c>
     </row>
     <row r="199">
@@ -12140,7 +12140,7 @@
         <v>81</v>
       </c>
       <c r="E199" t="n">
-        <v>4275</v>
+        <v>4293</v>
       </c>
       <c r="F199" t="n">
         <v>1</v>
@@ -12153,7 +12153,7 @@
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>IBERTIOGA - PIEDADE DO RIO GRANDE, NA RODOVIA MG-338</t>
+          <t>01ª URG BELO HORIZONTE - NORTE</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
@@ -12177,10 +12177,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>7000000</v>
+        <v>0</v>
       </c>
       <c r="R199" t="n">
-        <v>0</v>
+        <v>14850000</v>
       </c>
     </row>
     <row r="200">
@@ -12197,7 +12197,7 @@
         <v>81</v>
       </c>
       <c r="E200" t="n">
-        <v>4275</v>
+        <v>4293</v>
       </c>
       <c r="F200" t="n">
         <v>1</v>
@@ -12210,7 +12210,7 @@
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>INTERSEÇÃO DE ACESSO A COUTO DE MAGALHÃES DE MINAS, NA MGC-367</t>
+          <t>31ª URG ITUIUTABA</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
@@ -12234,10 +12234,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="R200" t="n">
-        <v>0</v>
+        <v>9900000</v>
       </c>
     </row>
     <row r="201">
@@ -12254,7 +12254,7 @@
         <v>81</v>
       </c>
       <c r="E201" t="n">
-        <v>4275</v>
+        <v>4293</v>
       </c>
       <c r="F201" t="n">
         <v>1</v>
@@ -12267,7 +12267,7 @@
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>ITAPAGIPE - ENTR. BR-364 (CAMPINA VERDE), RODOVIA MGC-154</t>
+          <t>PROGRAMA DE MICRORREVESTIMENTO ASFÁLTICO</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
@@ -12291,7 +12291,7 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>6121131</v>
+        <v>50000000</v>
       </c>
       <c r="R201" t="n">
         <v>0</v>
@@ -12311,7 +12311,7 @@
         <v>81</v>
       </c>
       <c r="E202" t="n">
-        <v>4275</v>
+        <v>4293</v>
       </c>
       <c r="F202" t="n">
         <v>1</v>
@@ -12324,7 +12324,7 @@
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>MG-631 - SÃO JOÃO DA PONTE A CAPITÃO ENÉAS</t>
+          <t>SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE-OBRA ESPECIALIZADA - LOTE 1</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
@@ -12348,7 +12348,7 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>1000000</v>
+        <v>8151612</v>
       </c>
       <c r="R202" t="n">
         <v>0</v>
@@ -12368,7 +12368,7 @@
         <v>81</v>
       </c>
       <c r="E203" t="n">
-        <v>4275</v>
+        <v>4293</v>
       </c>
       <c r="F203" t="n">
         <v>1</v>
@@ -12381,7 +12381,7 @@
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>MELHORAMENTO E PAVIMENTAÇÃO DA RODOVIA LMG-706, SEGMENTO 01: ENTR. BR-040 - VARIANTE (PONTE RIO ESCURO); SEGMENTO 02: VAZAMOR - VAZANTE; SEGMENTO 03: CONTORNO DE VAZANTE - ENTR. BR-354</t>
+          <t>SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE-OBRA ESPECIALIZADA - LOTE 2</t>
         </is>
       </c>
       <c r="K203" t="inlineStr">
@@ -12405,7 +12405,7 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>1000000</v>
+        <v>7488179</v>
       </c>
       <c r="R203" t="n">
         <v>0</v>
@@ -12425,7 +12425,7 @@
         <v>81</v>
       </c>
       <c r="E204" t="n">
-        <v>4275</v>
+        <v>4293</v>
       </c>
       <c r="F204" t="n">
         <v>1</v>
@@ -12438,7 +12438,7 @@
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>ACESSO AO PRESÍDIO DE ITURAMA</t>
+          <t>SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE-OBRA ESPECIALIZADA - LOTE 3</t>
         </is>
       </c>
       <c r="K204" t="inlineStr">
@@ -12462,7 +12462,7 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>1000000</v>
+        <v>9608804</v>
       </c>
       <c r="R204" t="n">
         <v>0</v>
@@ -12482,7 +12482,7 @@
         <v>81</v>
       </c>
       <c r="E205" t="n">
-        <v>4275</v>
+        <v>4293</v>
       </c>
       <c r="F205" t="n">
         <v>1</v>
@@ -12495,7 +12495,7 @@
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>MONTE CARMELO (ENTR. MG-190) - ENTR. LMG-742 (CHAPADA DE MINAS P/ GRUPIARA), NA LMG-746 - LOTE 01 9,50 KM</t>
+          <t>SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE-OBRA ESPECIALIZADA - LOTE 4</t>
         </is>
       </c>
       <c r="K205" t="inlineStr">
@@ -12519,7 +12519,7 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>1000000</v>
+        <v>8168067</v>
       </c>
       <c r="R205" t="n">
         <v>0</v>
@@ -12539,7 +12539,7 @@
         <v>81</v>
       </c>
       <c r="E206" t="n">
-        <v>4275</v>
+        <v>4293</v>
       </c>
       <c r="F206" t="n">
         <v>1</v>
@@ -12552,7 +12552,7 @@
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>MONTE CARMELO A CHAPADA DE MINAS - LOTE 2</t>
+          <t>CONSERVAÇÃO DA MALHA VIÁRIA DAS 40ª URG`S</t>
         </is>
       </c>
       <c r="K206" t="inlineStr">
@@ -12576,7 +12576,7 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>1000000</v>
+        <v>571386707</v>
       </c>
       <c r="R206" t="n">
         <v>0</v>
@@ -12596,7 +12596,7 @@
         <v>81</v>
       </c>
       <c r="E207" t="n">
-        <v>4275</v>
+        <v>4293</v>
       </c>
       <c r="F207" t="n">
         <v>1</v>
@@ -12609,7 +12609,7 @@
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>NATALÂNDIA - ENTR. BR-251, NA LMG-622</t>
+          <t>MANUTENÇÃO LINHA VERDE E COMPLEXO CIDADE ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
@@ -12633,7 +12633,7 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>1000000</v>
+        <v>15000000</v>
       </c>
       <c r="R207" t="n">
         <v>0</v>
@@ -12653,7 +12653,7 @@
         <v>81</v>
       </c>
       <c r="E208" t="n">
-        <v>4275</v>
+        <v>4293</v>
       </c>
       <c r="F208" t="n">
         <v>1</v>
@@ -12666,7 +12666,7 @@
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>PEÇANHA (ENTR. MG-416) - LMG-744 (COROACI), NA MG-314</t>
+          <t>REALINHAMENTO DE PREÇOS DO FORNECIMENTO DO MATERIAL BETUMINOSO</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
@@ -12690,7 +12690,7 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>431808</v>
+        <v>1406178</v>
       </c>
       <c r="R208" t="n">
         <v>0</v>
@@ -12710,7 +12710,7 @@
         <v>81</v>
       </c>
       <c r="E209" t="n">
-        <v>4275</v>
+        <v>4293</v>
       </c>
       <c r="F209" t="n">
         <v>1</v>
@@ -12723,7 +12723,7 @@
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>PEDRA AZUL (ENTR. MG-105) - DISTRITO DE PEDRA GRANDE - ALMENARA, MG-251/MG-406, LOTE 01 35 KM</t>
+          <t>CONTRATAÇÃO DE EMPRESA PARA EXECUÇÃO DE SERVIÇOS DE NATUREZA CONTÍNUA DE SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, EM REGIME DE EMPREITADA POR PREÇO UNITÁRIO, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
@@ -12747,7 +12747,7 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>1000000</v>
+        <v>19448656</v>
       </c>
       <c r="R209" t="n">
         <v>0</v>
@@ -12767,7 +12767,7 @@
         <v>81</v>
       </c>
       <c r="E210" t="n">
-        <v>4275</v>
+        <v>4385</v>
       </c>
       <c r="F210" t="n">
         <v>1</v>
@@ -12780,7 +12780,7 @@
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>PEDRA BONITA - ENTR. BR-116 E INTERSEÇÃO ENTR. BR-116 (COMPLEMENTAÇÃO), RODOVIA LMG-840</t>
+          <t>RECUPERAÇÃO FUNCIONAL MG-232 (BRAÚNAS (DIV. 40ª/ 2ª) - IPATINGA)</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
@@ -12824,7 +12824,7 @@
         <v>81</v>
       </c>
       <c r="E211" t="n">
-        <v>4275</v>
+        <v>4385</v>
       </c>
       <c r="F211" t="n">
         <v>1</v>
@@ -12837,7 +12837,7 @@
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>PRESIDENTE OLEGÁRIO - GALENA, NA LMG-726</t>
+          <t>RECUPERAÇÃO FUNCIONAL MGC-259 ( SABINÓPOLIS - SERRO, GUANHÃES - SABINÓPOLIS E ALVORADA MINAS - SERRO) *</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
@@ -12861,7 +12861,7 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>1000000</v>
+        <v>30000000</v>
       </c>
       <c r="R211" t="n">
         <v>0</v>
@@ -12881,7 +12881,7 @@
         <v>81</v>
       </c>
       <c r="E212" t="n">
-        <v>4275</v>
+        <v>4385</v>
       </c>
       <c r="F212" t="n">
         <v>1</v>
@@ -12894,7 +12894,7 @@
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>SANTA RITA DO ITUETO - ENTR. BR-259 (RESPLENDOR) (COMPLEMENTAÇÃO), MUNICIPAL AMG-2320</t>
+          <t>RECUPERAÇÃO FUNCIONAL MGC-455 (PIRAJUBA - ENTRº BR-364 (PLANURA)</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
@@ -12918,7 +12918,7 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>14356788</v>
+        <v>1000000</v>
       </c>
       <c r="R212" t="n">
         <v>0</v>
@@ -12935,10 +12935,10 @@
         <v>782</v>
       </c>
       <c r="D213" t="n">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="E213" t="n">
-        <v>4275</v>
+        <v>4280</v>
       </c>
       <c r="F213" t="n">
         <v>1</v>
@@ -12951,7 +12951,7 @@
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>SÃO DOMINGOS DO PRATA - DOM SILVÉRIO, NA MGC-120</t>
+          <t>PONTO CRÍTICO: ENTRº BR-040 (BARREIRA DOTRIUNFO) - ENTRº MG-353 (GOIANÁ)</t>
         </is>
       </c>
       <c r="K213" t="inlineStr">
@@ -12975,7 +12975,7 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>100000</v>
+        <v>4000000</v>
       </c>
       <c r="R213" t="n">
         <v>0</v>
@@ -12992,10 +12992,10 @@
         <v>782</v>
       </c>
       <c r="D214" t="n">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="E214" t="n">
-        <v>4275</v>
+        <v>4280</v>
       </c>
       <c r="F214" t="n">
         <v>1</v>
@@ -13008,7 +13008,7 @@
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>UNAÍ (ENTR. BR-251) - PARACATU (ENTR. BR-040) (ESTRADA DO MUNDO NOVO), NA LMG-658 - LOTE 01</t>
+          <t>PONTO CRÍTICO: ENTRº P/ MARIA DA FÉ - INÍCIO DO PERÍMETRO URBANO DE ITAJUBÁ (2  PONTOS)</t>
         </is>
       </c>
       <c r="K214" t="inlineStr">
@@ -13032,7 +13032,7 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>1000000</v>
+        <v>4000000</v>
       </c>
       <c r="R214" t="n">
         <v>0</v>
@@ -13049,10 +13049,10 @@
         <v>782</v>
       </c>
       <c r="D215" t="n">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="E215" t="n">
-        <v>4275</v>
+        <v>4280</v>
       </c>
       <c r="F215" t="n">
         <v>1</v>
@@ -13065,7 +13065,7 @@
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>ARAÇAÍ - SETE LAGOAS, RODOVIA MUNICIPAL</t>
+          <t>PONTO CRÍTICO: PALMÓPOLIS - RIO DO PRADO (6 PONTOS)/ PONTE SOBRE O RIBEIRÃO JOSÉ FERREIRA (1 PONTO)</t>
         </is>
       </c>
       <c r="K215" t="inlineStr">
@@ -13089,7 +13089,7 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>35359852</v>
+        <v>1000000</v>
       </c>
       <c r="R215" t="n">
         <v>0</v>
@@ -13097,19 +13097,19 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>2301</v>
+        <v>2311</v>
       </c>
       <c r="B216" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C216" t="n">
-        <v>782</v>
+        <v>363</v>
       </c>
       <c r="D216" t="n">
-        <v>81</v>
+        <v>7</v>
       </c>
       <c r="E216" t="n">
-        <v>4275</v>
+        <v>4006</v>
       </c>
       <c r="F216" t="n">
         <v>1</v>
@@ -13122,31 +13122,39 @@
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>ARAGUARI (DISTRITO DE AMANHECE) - DIVISA MG/GO, NA MG-414</t>
+          <t>Construção da escola do Brasil Profissionalizado no município de Unaí-MG</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
-        </is>
+          <t>PARALISADO</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>METRO QUADRADO</t>
+        </is>
+      </c>
+      <c r="M216" t="n">
+        <v>5000</v>
       </c>
       <c r="N216" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O216" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Patos de Minas</t>
         </is>
       </c>
       <c r="P216" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>UNAÍ</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>29030000</v>
+        <v>5000000</v>
       </c>
       <c r="R216" t="n">
         <v>0</v>
@@ -13154,19 +13162,19 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>2301</v>
+        <v>2321</v>
       </c>
       <c r="B217" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="C217" t="n">
-        <v>782</v>
+        <v>302</v>
       </c>
       <c r="D217" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E217" t="n">
-        <v>4275</v>
+        <v>4222</v>
       </c>
       <c r="F217" t="n">
         <v>1</v>
@@ -13179,12 +13187,12 @@
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>CAMPO VERDE (DISTRITO E NOVORIZONTE) - FRUTA DE LEITE, NA LMG-626 (LOTE 01 TSD)</t>
+          <t xml:space="preserve">Projetos em unidade diversas </t>
         </is>
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
@@ -13194,16 +13202,16 @@
       </c>
       <c r="O217" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P217" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>1000000</v>
+        <v>800291</v>
       </c>
       <c r="R217" t="n">
         <v>0</v>
@@ -13211,19 +13219,19 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>2301</v>
+        <v>2321</v>
       </c>
       <c r="B218" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="C218" t="n">
-        <v>782</v>
+        <v>302</v>
       </c>
       <c r="D218" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E218" t="n">
-        <v>4275</v>
+        <v>4222</v>
       </c>
       <c r="F218" t="n">
         <v>1</v>
@@ -13236,12 +13244,12 @@
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>JABOTICATUBAS - LAGOA SANTA, RODOVIA MUNICIPAL - LOTE 01</t>
+          <t xml:space="preserve">Projetos em unidade diversas </t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
@@ -13251,16 +13259,16 @@
       </c>
       <c r="O218" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P218" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>BETIM</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>3541727</v>
+        <v>174673</v>
       </c>
       <c r="R218" t="n">
         <v>0</v>
@@ -13268,19 +13276,19 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>2301</v>
+        <v>2321</v>
       </c>
       <c r="B219" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="C219" t="n">
-        <v>782</v>
+        <v>302</v>
       </c>
       <c r="D219" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E219" t="n">
-        <v>4275</v>
+        <v>4222</v>
       </c>
       <c r="F219" t="n">
         <v>1</v>
@@ -13291,9 +13299,12 @@
       <c r="H219" t="n">
         <v>218</v>
       </c>
+      <c r="I219" t="n">
+        <v>11877</v>
+      </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t xml:space="preserve">LMG-629 (RIO PARDO DE MINAS A ENTRº LMG-635) - LOTE 2 </t>
+          <t>Contrato a obra de reforma e ampliação</t>
         </is>
       </c>
       <c r="K219" t="inlineStr">
@@ -13308,16 +13319,16 @@
       </c>
       <c r="O219" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Barbacena</t>
         </is>
       </c>
       <c r="P219" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>SÃO JOÃO DEL REI</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>31280000</v>
+        <v>1088908</v>
       </c>
       <c r="R219" t="n">
         <v>0</v>
@@ -13325,19 +13336,19 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>2301</v>
+        <v>2361</v>
       </c>
       <c r="B220" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="C220" t="n">
-        <v>782</v>
+        <v>274</v>
       </c>
       <c r="D220" t="n">
-        <v>81</v>
+        <v>767</v>
       </c>
       <c r="E220" t="n">
-        <v>4287</v>
+        <v>2114</v>
       </c>
       <c r="F220" t="n">
         <v>1</v>
@@ -13350,7 +13361,7 @@
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>Empreendimentos do Acordo Judicial do Rio Doce</t>
+          <t>Possível obras de adequação da sede.</t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
@@ -13365,36 +13376,36 @@
       </c>
       <c r="O220" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P220" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="R220" t="n">
-        <v>0</v>
+        <v>2754406</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>2301</v>
+        <v>2371</v>
       </c>
       <c r="B221" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C221" t="n">
-        <v>782</v>
+        <v>609</v>
       </c>
       <c r="D221" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E221" t="n">
-        <v>4289</v>
+        <v>4238</v>
       </c>
       <c r="F221" t="n">
         <v>1</v>
@@ -13407,7 +13418,7 @@
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>Empreendimentos do Acordo Judicial de Brumadinho</t>
+          <t>Reestruturação física e ampliação do Laboratório de Química Agropecuária do Instituto Mineiro de Agropecuária - IMA</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
@@ -13422,16 +13433,16 @@
       </c>
       <c r="O221" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P221" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>1000</v>
+        <v>8311374</v>
       </c>
       <c r="R221" t="n">
         <v>0</v>
@@ -13439,19 +13450,19 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>2301</v>
+        <v>2421</v>
       </c>
       <c r="B222" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="C222" t="n">
-        <v>782</v>
+        <v>544</v>
       </c>
       <c r="D222" t="n">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="E222" t="n">
-        <v>4293</v>
+        <v>1016</v>
       </c>
       <c r="F222" t="n">
         <v>1</v>
@@ -13464,7 +13475,7 @@
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>PROGRAMA DE MICRORREVESTIMENTO ASFÁLTICO</t>
+          <t>Perfuração de Sistemas de Abastecimento de Agua conforme demanda dos municípios atendidos pelo IDENE</t>
         </is>
       </c>
       <c r="K222" t="inlineStr">
@@ -13479,16 +13490,16 @@
       </c>
       <c r="O222" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Montes Claros</t>
         </is>
       </c>
       <c r="P222" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>MONTES CLAROS</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>10000000</v>
+        <v>477508</v>
       </c>
       <c r="R222" t="n">
         <v>0</v>
@@ -13496,19 +13507,19 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>2301</v>
+        <v>3051</v>
       </c>
       <c r="B223" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C223" t="n">
-        <v>782</v>
+        <v>364</v>
       </c>
       <c r="D223" t="n">
-        <v>81</v>
+        <v>15</v>
       </c>
       <c r="E223" t="n">
-        <v>4293</v>
+        <v>4016</v>
       </c>
       <c r="F223" t="n">
         <v>1</v>
@@ -13521,7 +13532,7 @@
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>REALINHAMENTO DE PREÇOS DO FORNECIMENTO DO MATERIAL BETUMINOSO</t>
+          <t>Instalações do curso de Agropecuária de Precisão, com 1.070 m² de área total, além de 5 unidades de tratamento de águas residuárias.</t>
         </is>
       </c>
       <c r="K223" t="inlineStr">
@@ -13545,7 +13556,7 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>1406178</v>
+        <v>4825656</v>
       </c>
       <c r="R223" t="n">
         <v>0</v>
@@ -13553,19 +13564,19 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>2301</v>
+        <v>3051</v>
       </c>
       <c r="B224" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C224" t="n">
-        <v>782</v>
+        <v>364</v>
       </c>
       <c r="D224" t="n">
-        <v>81</v>
+        <v>15</v>
       </c>
       <c r="E224" t="n">
-        <v>4293</v>
+        <v>4016</v>
       </c>
       <c r="F224" t="n">
         <v>1</v>
@@ -13578,7 +13589,7 @@
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>04ª URG BARBACENA</t>
+          <t>Construção de novas instalações no Instituto Tecnológico de Agropecuária de Pitangui - ITAP, totalizando 3.214 m², para salas de aula, plantas-piloto de produção e laboratórios de apoio.</t>
         </is>
       </c>
       <c r="K224" t="inlineStr">
@@ -13602,27 +13613,27 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>0</v>
+        <v>12649000</v>
       </c>
       <c r="R224" t="n">
-        <v>12870000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>2301</v>
+        <v>3051</v>
       </c>
       <c r="B225" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C225" t="n">
-        <v>782</v>
+        <v>364</v>
       </c>
       <c r="D225" t="n">
-        <v>81</v>
+        <v>15</v>
       </c>
       <c r="E225" t="n">
-        <v>4293</v>
+        <v>4016</v>
       </c>
       <c r="F225" t="n">
         <v>1</v>
@@ -13635,7 +13646,7 @@
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>20ª URG FORMIGA</t>
+          <t xml:space="preserve">Reforma do edifício histórico do Instituto de Laticínios Cândido Tostes, localizado no município dde juiz de Fora. </t>
         </is>
       </c>
       <c r="K225" t="inlineStr">
@@ -13659,27 +13670,27 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>0</v>
+        <v>3715000</v>
       </c>
       <c r="R225" t="n">
-        <v>12870000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>2301</v>
+        <v>3051</v>
       </c>
       <c r="B226" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C226" t="n">
-        <v>782</v>
+        <v>571</v>
       </c>
       <c r="D226" t="n">
-        <v>81</v>
+        <v>16</v>
       </c>
       <c r="E226" t="n">
-        <v>4293</v>
+        <v>4018</v>
       </c>
       <c r="F226" t="n">
         <v>1</v>
@@ -13692,7 +13703,7 @@
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>28ª URG TEÓFILO OTONI</t>
+          <t>Melhoria na infraestrutura das unidades de pesquisa.</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
@@ -13719,24 +13730,24 @@
         <v>0</v>
       </c>
       <c r="R226" t="n">
-        <v>9575065</v>
+        <v>250000</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>2301</v>
+        <v>4031</v>
       </c>
       <c r="B227" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="C227" t="n">
-        <v>782</v>
+        <v>61</v>
       </c>
       <c r="D227" t="n">
-        <v>81</v>
+        <v>706</v>
       </c>
       <c r="E227" t="n">
-        <v>4293</v>
+        <v>2091</v>
       </c>
       <c r="F227" t="n">
         <v>1</v>
@@ -13747,53 +13758,64 @@
       <c r="H227" t="n">
         <v>226</v>
       </c>
+      <c r="I227" t="n">
+        <v>12054</v>
+      </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>30ª URG JUIZ DE FORA</t>
+          <t xml:space="preserve"> Construção do novo prédio do Fórum da Comarca de Betim/MG</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
-        </is>
+          <t>EXECUÇÃO</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M227" t="n">
+        <v>1</v>
       </c>
       <c r="N227" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O227" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P227" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>BETIM</t>
         </is>
       </c>
       <c r="Q227" t="n">
         <v>0</v>
       </c>
       <c r="R227" t="n">
-        <v>12375000</v>
+        <v>11016496</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>2301</v>
+        <v>4031</v>
       </c>
       <c r="B228" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="C228" t="n">
-        <v>782</v>
+        <v>61</v>
       </c>
       <c r="D228" t="n">
-        <v>81</v>
+        <v>706</v>
       </c>
       <c r="E228" t="n">
-        <v>4293</v>
+        <v>2091</v>
       </c>
       <c r="F228" t="n">
         <v>1</v>
@@ -13804,53 +13826,64 @@
       <c r="H228" t="n">
         <v>227</v>
       </c>
+      <c r="I228" t="n">
+        <v>12806</v>
+      </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>01ª URG BELO HORIZONTE - SUL</t>
+          <t>Campo Belo/MG - Construção do novo Fórum da Comarca de Campo Belo</t>
         </is>
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
-        </is>
+          <t>EXECUÇÃO</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M228" t="n">
+        <v>1</v>
       </c>
       <c r="N228" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O228" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Varginha</t>
         </is>
       </c>
       <c r="P228" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>CAMPO BELO</t>
         </is>
       </c>
       <c r="Q228" t="n">
         <v>0</v>
       </c>
       <c r="R228" t="n">
-        <v>14850000</v>
+        <v>19994210</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>2301</v>
+        <v>4031</v>
       </c>
       <c r="B229" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="C229" t="n">
-        <v>782</v>
+        <v>61</v>
       </c>
       <c r="D229" t="n">
-        <v>81</v>
+        <v>706</v>
       </c>
       <c r="E229" t="n">
-        <v>4293</v>
+        <v>2091</v>
       </c>
       <c r="F229" t="n">
         <v>1</v>
@@ -13861,53 +13894,64 @@
       <c r="H229" t="n">
         <v>228</v>
       </c>
+      <c r="I229" t="n">
+        <v>12638</v>
+      </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>01ª URG BELO HORIZONTE - NORTE</t>
+          <t>Obra de construção do novo Fórum da Comarca de Carangola.</t>
         </is>
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
-        </is>
+          <t>EXECUÇÃO</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M229" t="n">
+        <v>1</v>
       </c>
       <c r="N229" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O229" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P229" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>CARANGOLA</t>
         </is>
       </c>
       <c r="Q229" t="n">
         <v>0</v>
       </c>
       <c r="R229" t="n">
-        <v>14850000</v>
+        <v>12843388</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>2301</v>
+        <v>4031</v>
       </c>
       <c r="B230" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="C230" t="n">
-        <v>782</v>
+        <v>61</v>
       </c>
       <c r="D230" t="n">
-        <v>81</v>
+        <v>706</v>
       </c>
       <c r="E230" t="n">
-        <v>4293</v>
+        <v>2091</v>
       </c>
       <c r="F230" t="n">
         <v>1</v>
@@ -13918,53 +13962,64 @@
       <c r="H230" t="n">
         <v>229</v>
       </c>
+      <c r="I230" t="n">
+        <v>12400</v>
+      </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>31ª URG ITUIUTABA</t>
+          <t xml:space="preserve"> Contrato a execução da obra de reforma e ampliação do Fórum da Comarca de Ipatinga/MG</t>
         </is>
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
-        </is>
+          <t>EXECUÇÃO</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M230" t="n">
+        <v>1</v>
       </c>
       <c r="N230" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O230" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Ipatinga</t>
         </is>
       </c>
       <c r="P230" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>IPATINGA</t>
         </is>
       </c>
       <c r="Q230" t="n">
         <v>0</v>
       </c>
       <c r="R230" t="n">
-        <v>9900000</v>
+        <v>18849069</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>2301</v>
+        <v>4031</v>
       </c>
       <c r="B231" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="C231" t="n">
-        <v>782</v>
+        <v>61</v>
       </c>
       <c r="D231" t="n">
-        <v>81</v>
+        <v>706</v>
       </c>
       <c r="E231" t="n">
-        <v>4293</v>
+        <v>2091</v>
       </c>
       <c r="F231" t="n">
         <v>1</v>
@@ -13975,53 +14030,64 @@
       <c r="H231" t="n">
         <v>230</v>
       </c>
+      <c r="I231" t="n">
+        <v>12288</v>
+      </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>CONSERVAÇÃO DA MALHA VIÁRIA DAS 40ª URG`S</t>
+          <t xml:space="preserve"> Reforma e Ampliação do Fórum da Comarca de Monte Belo/MG</t>
         </is>
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
-        </is>
+          <t>EXECUÇÃO</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M231" t="n">
+        <v>1</v>
       </c>
       <c r="N231" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O231" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Varginha</t>
         </is>
       </c>
       <c r="P231" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>MONTE BELO</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>654124898</v>
+        <v>0</v>
       </c>
       <c r="R231" t="n">
-        <v>0</v>
+        <v>1950000</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>2301</v>
+        <v>4031</v>
       </c>
       <c r="B232" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="C232" t="n">
-        <v>782</v>
+        <v>61</v>
       </c>
       <c r="D232" t="n">
-        <v>81</v>
+        <v>706</v>
       </c>
       <c r="E232" t="n">
-        <v>4293</v>
+        <v>2091</v>
       </c>
       <c r="F232" t="n">
         <v>1</v>
@@ -14032,53 +14098,64 @@
       <c r="H232" t="n">
         <v>231</v>
       </c>
+      <c r="I232" t="n">
+        <v>12816</v>
+      </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA PARA EXECUÇÃO DE SERVIÇOS DE NATUREZA CONTÍNUA DE SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, EM REGIME DE EMPREITADA POR PREÇO UNITÁRIO, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE</t>
+          <t>Obra de construção do novo Fórum da Comarca de Pirapora/MG</t>
         </is>
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
-        </is>
+          <t>EXECUÇÃO</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M232" t="n">
+        <v>1</v>
       </c>
       <c r="N232" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O232" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Montes Claros</t>
         </is>
       </c>
       <c r="P232" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>PIRAPORA</t>
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>30767861</v>
+        <v>0</v>
       </c>
       <c r="R232" t="n">
-        <v>0</v>
+        <v>22776109</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>2301</v>
+        <v>4031</v>
       </c>
       <c r="B233" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="C233" t="n">
-        <v>782</v>
+        <v>61</v>
       </c>
       <c r="D233" t="n">
-        <v>81</v>
+        <v>706</v>
       </c>
       <c r="E233" t="n">
-        <v>4293</v>
+        <v>2091</v>
       </c>
       <c r="F233" t="n">
         <v>1</v>
@@ -14089,53 +14166,64 @@
       <c r="H233" t="n">
         <v>232</v>
       </c>
+      <c r="I233" t="n">
+        <v>12781</v>
+      </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO LINHA VERDE E COMPLEXO CIDADE ADMINISTRATIVA</t>
+          <t>Construção do novo fórum da Comarca de São Gonçalo do Sapucaí/MG</t>
         </is>
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
-        </is>
+          <t>EXECUÇÃO</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M233" t="n">
+        <v>1</v>
       </c>
       <c r="N233" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O233" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Varginha</t>
         </is>
       </c>
       <c r="P233" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>SÃO GONÇALO DO SAPUCAÍ</t>
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>19976964</v>
+        <v>0</v>
       </c>
       <c r="R233" t="n">
-        <v>0</v>
+        <v>14670005</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>2301</v>
+        <v>4031</v>
       </c>
       <c r="B234" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="C234" t="n">
-        <v>782</v>
+        <v>61</v>
       </c>
       <c r="D234" t="n">
-        <v>81</v>
+        <v>706</v>
       </c>
       <c r="E234" t="n">
-        <v>4293</v>
+        <v>2091</v>
       </c>
       <c r="F234" t="n">
         <v>1</v>
@@ -14146,53 +14234,64 @@
       <c r="H234" t="n">
         <v>233</v>
       </c>
+      <c r="I234" t="n">
+        <v>12799</v>
+      </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE-OBRA ESPECIALIZADA - LOTE 1</t>
+          <t xml:space="preserve">Construção do novo Fórum da Comarca de Timóteo/MG </t>
         </is>
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
-        </is>
+          <t>EXECUÇÃO</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M234" t="n">
+        <v>1</v>
       </c>
       <c r="N234" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O234" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Ipatinga</t>
         </is>
       </c>
       <c r="P234" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>TIMÓTEO</t>
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>12895888</v>
+        <v>0</v>
       </c>
       <c r="R234" t="n">
-        <v>0</v>
+        <v>19506288</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>2301</v>
+        <v>4031</v>
       </c>
       <c r="B235" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="C235" t="n">
-        <v>782</v>
+        <v>61</v>
       </c>
       <c r="D235" t="n">
-        <v>81</v>
+        <v>706</v>
       </c>
       <c r="E235" t="n">
-        <v>4293</v>
+        <v>2091</v>
       </c>
       <c r="F235" t="n">
         <v>1</v>
@@ -14203,9 +14302,12 @@
       <c r="H235" t="n">
         <v>234</v>
       </c>
+      <c r="I235" t="n">
+        <v>12833</v>
+      </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE-OBRA ESPECIALIZADA - LOTE 2</t>
+          <t>Obra de construção do novo Fórum da Comarca de Rio Novo.</t>
         </is>
       </c>
       <c r="K235" t="inlineStr">
@@ -14213,43 +14315,51 @@
           <t>INICIANDO</t>
         </is>
       </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M235" t="n">
+        <v>1</v>
+      </c>
       <c r="N235" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O235" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P235" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>RIO NOVO</t>
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>11846334</v>
+        <v>0</v>
       </c>
       <c r="R235" t="n">
-        <v>0</v>
+        <v>4976096</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>2301</v>
+        <v>4031</v>
       </c>
       <c r="B236" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="C236" t="n">
-        <v>782</v>
+        <v>61</v>
       </c>
       <c r="D236" t="n">
-        <v>81</v>
+        <v>706</v>
       </c>
       <c r="E236" t="n">
-        <v>4293</v>
+        <v>2091</v>
       </c>
       <c r="F236" t="n">
         <v>1</v>
@@ -14260,9 +14370,12 @@
       <c r="H236" t="n">
         <v>235</v>
       </c>
+      <c r="I236" t="n">
+        <v>12629</v>
+      </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE-OBRA ESPECIALIZADA - LOTE 3</t>
+          <t>Obra de construção do novo Fórum da Comarca de Luz.</t>
         </is>
       </c>
       <c r="K236" t="inlineStr">
@@ -14270,43 +14383,51 @@
           <t>INICIANDO</t>
         </is>
       </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M236" t="n">
+        <v>1</v>
+      </c>
       <c r="N236" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O236" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Divinópolis</t>
         </is>
       </c>
       <c r="P236" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>LUZ</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>15201174</v>
+        <v>0</v>
       </c>
       <c r="R236" t="n">
-        <v>0</v>
+        <v>7654409</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>2301</v>
+        <v>4031</v>
       </c>
       <c r="B237" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="C237" t="n">
-        <v>782</v>
+        <v>61</v>
       </c>
       <c r="D237" t="n">
-        <v>81</v>
+        <v>706</v>
       </c>
       <c r="E237" t="n">
-        <v>4293</v>
+        <v>2091</v>
       </c>
       <c r="F237" t="n">
         <v>1</v>
@@ -14317,53 +14438,64 @@
       <c r="H237" t="n">
         <v>236</v>
       </c>
+      <c r="I237" t="n">
+        <v>12607</v>
+      </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE-OBRA ESPECIALIZADA - LOTE 4</t>
+          <t>Reforma e ampliação do Fórum da Comarca de Sete Lagoas/MG.</t>
         </is>
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
-        </is>
+          <t>EXECUÇÃO</t>
+        </is>
+      </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M237" t="n">
+        <v>1</v>
       </c>
       <c r="N237" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O237" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P237" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>SETE LAGOAS</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>12921920</v>
+        <v>0</v>
       </c>
       <c r="R237" t="n">
-        <v>0</v>
+        <v>32235085</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>2301</v>
+        <v>4031</v>
       </c>
       <c r="B238" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="C238" t="n">
-        <v>782</v>
+        <v>61</v>
       </c>
       <c r="D238" t="n">
-        <v>81</v>
+        <v>706</v>
       </c>
       <c r="E238" t="n">
-        <v>4385</v>
+        <v>2091</v>
       </c>
       <c r="F238" t="n">
         <v>1</v>
@@ -14374,53 +14506,64 @@
       <c r="H238" t="n">
         <v>237</v>
       </c>
+      <c r="I238" t="n">
+        <v>12639</v>
+      </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>RECUPERAÇÃO FUNCIONAL MG-232 (BRAÚNAS (DIV. 40ª/ 2ª) - IPATINGA)</t>
+          <t>Obra de construção do novo Fórum da Comarca de Três Pontas</t>
         </is>
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
-        </is>
+          <t>EXECUÇÃO</t>
+        </is>
+      </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M238" t="n">
+        <v>1</v>
       </c>
       <c r="N238" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O238" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Varginha</t>
         </is>
       </c>
       <c r="P238" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>TRÊS PONTAS</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>6382601</v>
+        <v>0</v>
       </c>
       <c r="R238" t="n">
-        <v>0</v>
+        <v>9489687</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>2301</v>
+        <v>4031</v>
       </c>
       <c r="B239" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="C239" t="n">
-        <v>782</v>
+        <v>61</v>
       </c>
       <c r="D239" t="n">
-        <v>81</v>
+        <v>706</v>
       </c>
       <c r="E239" t="n">
-        <v>4385</v>
+        <v>2091</v>
       </c>
       <c r="F239" t="n">
         <v>1</v>
@@ -14431,9 +14574,12 @@
       <c r="H239" t="n">
         <v>238</v>
       </c>
+      <c r="I239" t="n">
+        <v>11547</v>
+      </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>RECUPERAÇÃO FUNCIONAL MGC-259 ( SABINÓPOLIS - SERRO, GUANHÃES - SABINÓPOLIS E ALVORADA MINAS - SERRO) *</t>
+          <t>RETOMADA DA OBRA DE CONSTRUÇÃO DO NOVO PRÉDIO DO FÓRUM DA COMARCA DE ITAJUBÁ/MG</t>
         </is>
       </c>
       <c r="K239" t="inlineStr">
@@ -14441,43 +14587,51 @@
           <t>INICIANDO</t>
         </is>
       </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M239" t="n">
+        <v>1</v>
+      </c>
       <c r="N239" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O239" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Pouso Alegre</t>
         </is>
       </c>
       <c r="P239" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>ITAJUBÁ</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>30000000</v>
+        <v>0</v>
       </c>
       <c r="R239" t="n">
-        <v>0</v>
+        <v>9366263</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>2301</v>
+        <v>4031</v>
       </c>
       <c r="B240" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="C240" t="n">
-        <v>782</v>
+        <v>61</v>
       </c>
       <c r="D240" t="n">
-        <v>81</v>
+        <v>706</v>
       </c>
       <c r="E240" t="n">
-        <v>4385</v>
+        <v>2091</v>
       </c>
       <c r="F240" t="n">
         <v>1</v>
@@ -14488,9 +14642,12 @@
       <c r="H240" t="n">
         <v>239</v>
       </c>
+      <c r="I240" t="n">
+        <v>12856</v>
+      </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>RECUPERAÇÃO FUNCIONAL MGC-455 (PIRAJUBA - ENTRº BR-364 (PLANURA)</t>
+          <t>Retomada da obra de construção do novo Fórum da Comarca de Poços de Caldas.</t>
         </is>
       </c>
       <c r="K240" t="inlineStr">
@@ -14498,43 +14655,51 @@
           <t>INICIANDO</t>
         </is>
       </c>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M240" t="n">
+        <v>1</v>
+      </c>
       <c r="N240" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O240" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Pouso Alegre</t>
         </is>
       </c>
       <c r="P240" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>POÇOS DE CALDAS</t>
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>4000000</v>
+        <v>0</v>
       </c>
       <c r="R240" t="n">
-        <v>0</v>
+        <v>11009635</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>2301</v>
+        <v>4031</v>
       </c>
       <c r="B241" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="C241" t="n">
-        <v>782</v>
+        <v>61</v>
       </c>
       <c r="D241" t="n">
-        <v>139</v>
+        <v>706</v>
       </c>
       <c r="E241" t="n">
-        <v>4280</v>
+        <v>2091</v>
       </c>
       <c r="F241" t="n">
         <v>1</v>
@@ -14545,9 +14710,12 @@
       <c r="H241" t="n">
         <v>240</v>
       </c>
+      <c r="I241" t="n">
+        <v>12344</v>
+      </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>PONTO CRÍTICO: ENTRº BR-040 (BARREIRA DOTRIUNFO) - ENTRº MG-353 (GOIANÁ)</t>
+          <t>Construção do novo prédio do Fórum da Comarca de Camanducaia/MG</t>
         </is>
       </c>
       <c r="K241" t="inlineStr">
@@ -14555,43 +14723,51 @@
           <t>INICIANDO</t>
         </is>
       </c>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M241" t="n">
+        <v>1</v>
+      </c>
       <c r="N241" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O241" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Pouso Alegre</t>
         </is>
       </c>
       <c r="P241" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>CAMANDUCAIA</t>
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>4000000</v>
+        <v>0</v>
       </c>
       <c r="R241" t="n">
-        <v>0</v>
+        <v>4627222</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>2301</v>
+        <v>4031</v>
       </c>
       <c r="B242" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="C242" t="n">
-        <v>782</v>
+        <v>61</v>
       </c>
       <c r="D242" t="n">
-        <v>139</v>
+        <v>706</v>
       </c>
       <c r="E242" t="n">
-        <v>4280</v>
+        <v>2091</v>
       </c>
       <c r="F242" t="n">
         <v>1</v>
@@ -14604,7 +14780,7 @@
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>PONTO CRÍTICO: ENTRº MGC-265 (RIO POMBA) - PONTE RIO POMBA</t>
+          <t>Obra de construção do novo Fórum da Comarca de São João do Paraíso</t>
         </is>
       </c>
       <c r="K242" t="inlineStr">
@@ -14612,43 +14788,51 @@
           <t>INICIANDO</t>
         </is>
       </c>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M242" t="n">
+        <v>1</v>
+      </c>
       <c r="N242" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O242" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Montes Claros</t>
         </is>
       </c>
       <c r="P242" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>SÃO JOÃO DO PARAÍSO</t>
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>470000</v>
+        <v>0</v>
       </c>
       <c r="R242" t="n">
-        <v>0</v>
+        <v>7290196</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>2301</v>
+        <v>4031</v>
       </c>
       <c r="B243" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="C243" t="n">
-        <v>782</v>
+        <v>61</v>
       </c>
       <c r="D243" t="n">
-        <v>139</v>
+        <v>706</v>
       </c>
       <c r="E243" t="n">
-        <v>4280</v>
+        <v>2091</v>
       </c>
       <c r="F243" t="n">
         <v>1</v>
@@ -14661,7 +14845,7 @@
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>PONTO CRÍTICO: ENTRº P/ MARIA DA FÉ - INÍCIO DO PERÍMETRO URBANO DE ITAJUBÁ (2  PONTOS)</t>
+          <t>Implantação do Fórum Digital no município de Brasilândia de Minas</t>
         </is>
       </c>
       <c r="K243" t="inlineStr">
@@ -14669,43 +14853,51 @@
           <t>INICIANDO</t>
         </is>
       </c>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M243" t="n">
+        <v>1</v>
+      </c>
       <c r="N243" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O243" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Patos de Minas</t>
         </is>
       </c>
       <c r="P243" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>BRASILÂNDIA DE MINAS</t>
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>4000000</v>
+        <v>0</v>
       </c>
       <c r="R243" t="n">
-        <v>0</v>
+        <v>1373680</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>2301</v>
+        <v>4031</v>
       </c>
       <c r="B244" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="C244" t="n">
-        <v>782</v>
+        <v>61</v>
       </c>
       <c r="D244" t="n">
-        <v>139</v>
+        <v>706</v>
       </c>
       <c r="E244" t="n">
-        <v>4280</v>
+        <v>2091</v>
       </c>
       <c r="F244" t="n">
         <v>1</v>
@@ -14718,7 +14910,7 @@
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>PONTO CRÍTICO: PALMÓPOLIS - RIO DO PRADO (6 PONTOS)/ PONTE SOBRE O RIBEIRÃO JOSÉ FERREIRA (1 PONTO)</t>
+          <t>Implantação do Fórum Digital no município de São Gonçalo do Abaeté</t>
         </is>
       </c>
       <c r="K244" t="inlineStr">
@@ -14726,43 +14918,51 @@
           <t>INICIANDO</t>
         </is>
       </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M244" t="n">
+        <v>1</v>
+      </c>
       <c r="N244" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O244" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Patos de Minas</t>
         </is>
       </c>
       <c r="P244" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>SÃO GONÇALO DO ABAETÉ</t>
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="R244" t="n">
-        <v>0</v>
+        <v>1373680</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>2301</v>
+        <v>4031</v>
       </c>
       <c r="B245" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="C245" t="n">
-        <v>782</v>
+        <v>61</v>
       </c>
       <c r="D245" t="n">
-        <v>139</v>
+        <v>706</v>
       </c>
       <c r="E245" t="n">
-        <v>4280</v>
+        <v>2091</v>
       </c>
       <c r="F245" t="n">
         <v>1</v>
@@ -14775,7 +14975,7 @@
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>PONTO CRÍTICO: RODEIRO - ENTRº MG-285</t>
+          <t>Implantação do Fórum Digital no município de Ponto Chique</t>
         </is>
       </c>
       <c r="K245" t="inlineStr">
@@ -14783,43 +14983,51 @@
           <t>INICIANDO</t>
         </is>
       </c>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M245" t="n">
+        <v>1</v>
+      </c>
       <c r="N245" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O245" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Montes Claros</t>
         </is>
       </c>
       <c r="P245" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>PONTO CHIQUE</t>
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>420000</v>
+        <v>0</v>
       </c>
       <c r="R245" t="n">
-        <v>0</v>
+        <v>1760000</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>2301</v>
+        <v>4031</v>
       </c>
       <c r="B246" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="C246" t="n">
-        <v>782</v>
+        <v>61</v>
       </c>
       <c r="D246" t="n">
-        <v>139</v>
+        <v>706</v>
       </c>
       <c r="E246" t="n">
-        <v>4280</v>
+        <v>2091</v>
       </c>
       <c r="F246" t="n">
         <v>1</v>
@@ -14830,53 +15038,64 @@
       <c r="H246" t="n">
         <v>245</v>
       </c>
+      <c r="I246" t="n">
+        <v>12627</v>
+      </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>PONTO CRÍTICO: SABARÁ-CAETÉ (3 PONTOS)</t>
+          <t>Execução da 4ª (quarta) parcela da reforma parcial do Edifício-Sede do TRIBUNAL.</t>
         </is>
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
-        </is>
+          <t>EXECUÇÃO</t>
+        </is>
+      </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M246" t="n">
+        <v>1</v>
       </c>
       <c r="N246" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O246" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P246" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>790000</v>
+        <v>0</v>
       </c>
       <c r="R246" t="n">
-        <v>0</v>
+        <v>38084213</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>2311</v>
+        <v>4031</v>
       </c>
       <c r="B247" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C247" t="n">
-        <v>363</v>
+        <v>61</v>
       </c>
       <c r="D247" t="n">
-        <v>7</v>
+        <v>706</v>
       </c>
       <c r="E247" t="n">
-        <v>4006</v>
+        <v>2091</v>
       </c>
       <c r="F247" t="n">
         <v>1</v>
@@ -14887,23 +15106,26 @@
       <c r="H247" t="n">
         <v>246</v>
       </c>
+      <c r="I247" t="n">
+        <v>12146</v>
+      </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>Construção da escola do Brasil Profissionalizado no município de Unaí-MG</t>
+          <t>Reforma geral do Fórum Lafayette, em Belo Horizonte/MG</t>
         </is>
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t>PARALISADO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t>METRO QUADRADO</t>
+          <t>UNIDADE</t>
         </is>
       </c>
       <c r="M247" t="n">
-        <v>5000</v>
+        <v>1</v>
       </c>
       <c r="N247" t="inlineStr">
         <is>
@@ -14912,36 +15134,36 @@
       </c>
       <c r="O247" t="inlineStr">
         <is>
-          <t>Região Intermediária de Patos de Minas</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P247" t="inlineStr">
         <is>
-          <t>UNAÍ</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>5000000</v>
+        <v>0</v>
       </c>
       <c r="R247" t="n">
-        <v>0</v>
+        <v>135013067</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>2321</v>
+        <v>4031</v>
       </c>
       <c r="B248" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C248" t="n">
-        <v>302</v>
+        <v>61</v>
       </c>
       <c r="D248" t="n">
-        <v>87</v>
+        <v>706</v>
       </c>
       <c r="E248" t="n">
-        <v>4222</v>
+        <v>2091</v>
       </c>
       <c r="F248" t="n">
         <v>1</v>
@@ -14952,9 +15174,12 @@
       <c r="H248" t="n">
         <v>247</v>
       </c>
+      <c r="I248" t="n">
+        <v>12703</v>
+      </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Projetos em unidade diversas </t>
+          <t>Cincão - Reforma parcial para adequações da estrutura física dos Armazéns 6, 7 e 8, Galpão 2, Arquivo Central e Permanente</t>
         </is>
       </c>
       <c r="K248" t="inlineStr">
@@ -14962,9 +15187,17 @@
           <t>EXECUÇÃO</t>
         </is>
       </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M248" t="n">
+        <v>1</v>
+      </c>
       <c r="N248" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O248" t="inlineStr">
@@ -14978,27 +15211,27 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>800291</v>
+        <v>0</v>
       </c>
       <c r="R248" t="n">
-        <v>0</v>
+        <v>1052449</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>2321</v>
+        <v>4031</v>
       </c>
       <c r="B249" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C249" t="n">
-        <v>302</v>
+        <v>61</v>
       </c>
       <c r="D249" t="n">
-        <v>87</v>
+        <v>706</v>
       </c>
       <c r="E249" t="n">
-        <v>4222</v>
+        <v>2091</v>
       </c>
       <c r="F249" t="n">
         <v>1</v>
@@ -15011,51 +15244,59 @@
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Projetos em unidade diversas </t>
+          <t>Obra de construção do novo Fórum da Comarca de Monte Alegre de Minas</t>
         </is>
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
-        </is>
+          <t>INICIANDO</t>
+        </is>
+      </c>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M249" t="n">
+        <v>1</v>
       </c>
       <c r="N249" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O249" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Uberlândia</t>
         </is>
       </c>
       <c r="P249" t="inlineStr">
         <is>
-          <t>BETIM</t>
+          <t>MONTE ALEGRE DE MINAS</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>174673</v>
+        <v>0</v>
       </c>
       <c r="R249" t="n">
-        <v>0</v>
+        <v>6139672</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>2321</v>
+        <v>5011</v>
       </c>
       <c r="B250" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C250" t="n">
-        <v>302</v>
+        <v>122</v>
       </c>
       <c r="D250" t="n">
-        <v>87</v>
+        <v>133</v>
       </c>
       <c r="E250" t="n">
-        <v>4222</v>
+        <v>3017</v>
       </c>
       <c r="F250" t="n">
         <v>1</v>
@@ -15066,12 +15307,9 @@
       <c r="H250" t="n">
         <v>249</v>
       </c>
-      <c r="I250" t="n">
-        <v>11877</v>
-      </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>Contrato a obra de reforma e ampliação</t>
+          <t>CENTRO DE CULTURA PRESIDENTE ITAMAR FRANCO</t>
         </is>
       </c>
       <c r="K250" t="inlineStr">
@@ -15086,36 +15324,36 @@
       </c>
       <c r="O250" t="inlineStr">
         <is>
-          <t>Região Intermediária de Barbacena</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P250" t="inlineStr">
         <is>
-          <t>SÃO JOÃO DEL REI</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>1088908</v>
+        <v>0</v>
       </c>
       <c r="R250" t="n">
-        <v>0</v>
+        <v>800000</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>2361</v>
+        <v>5031</v>
       </c>
       <c r="B251" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="C251" t="n">
-        <v>846</v>
+        <v>572</v>
       </c>
       <c r="D251" t="n">
-        <v>705</v>
+        <v>133</v>
       </c>
       <c r="E251" t="n">
-        <v>7004</v>
+        <v>3015</v>
       </c>
       <c r="F251" t="n">
         <v>1</v>
@@ -15128,7 +15366,7 @@
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>Possível adequação da sede</t>
+          <t>BALNEÁRIO ÁGUAS SANTAS - TIRADENTES/MG | BARREIO DE ARAXÁ</t>
         </is>
       </c>
       <c r="K251" t="inlineStr">
@@ -15140,23 +15378,39 @@
         <is>
           <t>Não</t>
         </is>
+      </c>
+      <c r="O251" t="inlineStr">
+        <is>
+          <t>Estadual</t>
+        </is>
+      </c>
+      <c r="P251" t="inlineStr">
+        <is>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+        </is>
+      </c>
+      <c r="Q251" t="n">
+        <v>0</v>
+      </c>
+      <c r="R251" t="n">
+        <v>4782988</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>2361</v>
+        <v>5141</v>
       </c>
       <c r="B252" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C252" t="n">
-        <v>274</v>
+        <v>126</v>
       </c>
       <c r="D252" t="n">
-        <v>766</v>
+        <v>30</v>
       </c>
       <c r="E252" t="n">
-        <v>2113</v>
+        <v>6006</v>
       </c>
       <c r="F252" t="n">
         <v>1</v>
@@ -15169,7 +15423,7 @@
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>Possível adequação da sede</t>
+          <t>ELABORAÇÃO E EXECUÇÃO DE PROJETOS RELACIONADOS À REFORMA, MODERNIZAÇÃO E ADEQUAÇÃO DAS INSTALAÇÕES PREDIAIS DA COMPANHIA.</t>
         </is>
       </c>
       <c r="K252" t="inlineStr">
@@ -15181,23 +15435,39 @@
         <is>
           <t>Não</t>
         </is>
+      </c>
+      <c r="O252" t="inlineStr">
+        <is>
+          <t>Estadual</t>
+        </is>
+      </c>
+      <c r="P252" t="inlineStr">
+        <is>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+        </is>
+      </c>
+      <c r="Q252" t="n">
+        <v>0</v>
+      </c>
+      <c r="R252" t="n">
+        <v>16317109</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>2361</v>
+        <v>5251</v>
       </c>
       <c r="B253" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="C253" t="n">
-        <v>274</v>
+        <v>121</v>
       </c>
       <c r="D253" t="n">
-        <v>767</v>
+        <v>133</v>
       </c>
       <c r="E253" t="n">
-        <v>2114</v>
+        <v>3018</v>
       </c>
       <c r="F253" t="n">
         <v>1</v>
@@ -15210,12 +15480,12 @@
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>Possível obras de adequação da sede.</t>
+          <t>Projeto de Expansão</t>
         </is>
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -15237,24 +15507,24 @@
         <v>0</v>
       </c>
       <c r="R253" t="n">
-        <v>2754406</v>
+        <v>457766318</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>2371</v>
+        <v>5391</v>
       </c>
       <c r="B254" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C254" t="n">
-        <v>609</v>
+        <v>752</v>
       </c>
       <c r="D254" t="n">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="E254" t="n">
-        <v>4238</v>
+        <v>3004</v>
       </c>
       <c r="F254" t="n">
         <v>1</v>
@@ -15267,7 +15537,7 @@
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>Reestruturação física e ampliação do Laboratório de Química Agropecuária do Instituto Mineiro de Agropecuária - IMA</t>
+          <t xml:space="preserve">Expansão e Aquisição do Sistema de Transmissão </t>
         </is>
       </c>
       <c r="K254" t="inlineStr">
@@ -15287,31 +15557,31 @@
       </c>
       <c r="P254" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>8311374</v>
+        <v>0</v>
       </c>
       <c r="R254" t="n">
-        <v>0</v>
+        <v>92004926</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>2421</v>
+        <v>5391</v>
       </c>
       <c r="B255" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="C255" t="n">
-        <v>544</v>
+        <v>752</v>
       </c>
       <c r="D255" t="n">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="E255" t="n">
-        <v>1016</v>
+        <v>3004</v>
       </c>
       <c r="F255" t="n">
         <v>1</v>
@@ -15324,7 +15594,7 @@
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>Perfuração de Sistemas de Abastecimento de Agua conforme demanda dos municípios atendidos pelo IDENE</t>
+          <t xml:space="preserve">Expansão e Aquisição do Sistema de Transmissão </t>
         </is>
       </c>
       <c r="K255" t="inlineStr">
@@ -15344,31 +15614,31 @@
       </c>
       <c r="P255" t="inlineStr">
         <is>
-          <t>MONTES CLAROS</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE MONTES CLAROS</t>
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>477508</v>
+        <v>0</v>
       </c>
       <c r="R255" t="n">
-        <v>0</v>
+        <v>10705994</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>3051</v>
+        <v>5391</v>
       </c>
       <c r="B256" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="C256" t="n">
-        <v>364</v>
+        <v>752</v>
       </c>
       <c r="D256" t="n">
-        <v>15</v>
+        <v>92</v>
       </c>
       <c r="E256" t="n">
-        <v>4016</v>
+        <v>3004</v>
       </c>
       <c r="F256" t="n">
         <v>1</v>
@@ -15381,7 +15651,7 @@
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>Instalações do curso de Agropecuária de Precisão, com 1.070 m² de área total, além de 5 unidades de tratamento de águas residuárias.</t>
+          <t xml:space="preserve">Expansão e Aquisição do Sistema de Transmissão </t>
         </is>
       </c>
       <c r="K256" t="inlineStr">
@@ -15396,36 +15666,36 @@
       </c>
       <c r="O256" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P256" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE JUÍZ DE FORA</t>
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>4825656</v>
+        <v>0</v>
       </c>
       <c r="R256" t="n">
-        <v>0</v>
+        <v>10464844</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>3051</v>
+        <v>5391</v>
       </c>
       <c r="B257" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="C257" t="n">
-        <v>364</v>
+        <v>752</v>
       </c>
       <c r="D257" t="n">
-        <v>15</v>
+        <v>92</v>
       </c>
       <c r="E257" t="n">
-        <v>4016</v>
+        <v>3004</v>
       </c>
       <c r="F257" t="n">
         <v>1</v>
@@ -15438,7 +15708,7 @@
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>Construção de novas instalações no Instituto Tecnológico de Agropecuária de Pitangui - ITAP, totalizando 3.214 m², para salas de aula, plantas-piloto de produção e laboratórios de apoio.</t>
+          <t xml:space="preserve">Expansão e Aquisição do Sistema de Transmissão </t>
         </is>
       </c>
       <c r="K257" t="inlineStr">
@@ -15453,36 +15723,36 @@
       </c>
       <c r="O257" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Uberlândia</t>
         </is>
       </c>
       <c r="P257" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERLÂNDIA</t>
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>12649000</v>
+        <v>0</v>
       </c>
       <c r="R257" t="n">
-        <v>0</v>
+        <v>2098278</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>3051</v>
+        <v>5391</v>
       </c>
       <c r="B258" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="C258" t="n">
-        <v>364</v>
+        <v>752</v>
       </c>
       <c r="D258" t="n">
-        <v>15</v>
+        <v>92</v>
       </c>
       <c r="E258" t="n">
-        <v>4016</v>
+        <v>3004</v>
       </c>
       <c r="F258" t="n">
         <v>1</v>
@@ -15495,7 +15765,7 @@
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reforma do edifício histórico do Instituto de Laticínios Cândido Tostes, localizado no município dde juiz de Fora. </t>
+          <t xml:space="preserve">Expansão e Aquisição do Sistema de Transmissão </t>
         </is>
       </c>
       <c r="K258" t="inlineStr">
@@ -15519,27 +15789,27 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>3715000</v>
+        <v>0</v>
       </c>
       <c r="R258" t="n">
-        <v>0</v>
+        <v>96721858</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>3051</v>
+        <v>5391</v>
       </c>
       <c r="B259" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C259" t="n">
-        <v>571</v>
+        <v>752</v>
       </c>
       <c r="D259" t="n">
-        <v>16</v>
+        <v>92</v>
       </c>
       <c r="E259" t="n">
-        <v>4018</v>
+        <v>3004</v>
       </c>
       <c r="F259" t="n">
         <v>1</v>
@@ -15552,7 +15822,7 @@
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>Melhoria na infraestrutura das unidades de pesquisa.</t>
+          <t xml:space="preserve">Expansão e Aquisição do Sistema de Transmissão </t>
         </is>
       </c>
       <c r="K259" t="inlineStr">
@@ -15567,36 +15837,36 @@
       </c>
       <c r="O259" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Uberaba</t>
         </is>
       </c>
       <c r="P259" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERABA</t>
         </is>
       </c>
       <c r="Q259" t="n">
         <v>0</v>
       </c>
       <c r="R259" t="n">
-        <v>250000</v>
+        <v>16415074</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>4031</v>
+        <v>5391</v>
       </c>
       <c r="B260" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C260" t="n">
-        <v>61</v>
+        <v>752</v>
       </c>
       <c r="D260" t="n">
-        <v>706</v>
+        <v>92</v>
       </c>
       <c r="E260" t="n">
-        <v>2091</v>
+        <v>3004</v>
       </c>
       <c r="F260" t="n">
         <v>1</v>
@@ -15607,64 +15877,53 @@
       <c r="H260" t="n">
         <v>259</v>
       </c>
-      <c r="I260" t="n">
-        <v>12054</v>
-      </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Construção do novo prédio do Fórum da Comarca de Betim/MG</t>
+          <t xml:space="preserve">Expansão e Aquisição do Sistema de Transmissão </t>
         </is>
       </c>
       <c r="K260" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
-        </is>
-      </c>
-      <c r="L260" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M260" t="n">
-        <v>1</v>
+          <t>INICIANDO</t>
+        </is>
       </c>
       <c r="N260" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="O260" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Ipatinga</t>
         </is>
       </c>
       <c r="P260" t="inlineStr">
         <is>
-          <t>BETIM</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE IPATINGA</t>
         </is>
       </c>
       <c r="Q260" t="n">
         <v>0</v>
       </c>
       <c r="R260" t="n">
-        <v>11016496</v>
+        <v>1</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>4031</v>
+        <v>5391</v>
       </c>
       <c r="B261" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C261" t="n">
-        <v>61</v>
+        <v>752</v>
       </c>
       <c r="D261" t="n">
-        <v>706</v>
+        <v>92</v>
       </c>
       <c r="E261" t="n">
-        <v>2091</v>
+        <v>3005</v>
       </c>
       <c r="F261" t="n">
         <v>1</v>
@@ -15675,64 +15934,53 @@
       <c r="H261" t="n">
         <v>260</v>
       </c>
-      <c r="I261" t="n">
-        <v>12806</v>
-      </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>Campo Belo/MG - Construção do novo Fórum da Comarca de Campo Belo</t>
+          <t>Reformas de Subestações e Linhas de Transmissão</t>
         </is>
       </c>
       <c r="K261" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
-        </is>
-      </c>
-      <c r="L261" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M261" t="n">
-        <v>1</v>
+          <t>INICIANDO</t>
+        </is>
       </c>
       <c r="N261" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="O261" t="inlineStr">
         <is>
-          <t>Região Intermediária de Varginha</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P261" t="inlineStr">
         <is>
-          <t>CAMPO BELO</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q261" t="n">
         <v>0</v>
       </c>
       <c r="R261" t="n">
-        <v>19994210</v>
+        <v>126817302</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>4031</v>
+        <v>5391</v>
       </c>
       <c r="B262" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C262" t="n">
-        <v>61</v>
+        <v>752</v>
       </c>
       <c r="D262" t="n">
-        <v>706</v>
+        <v>92</v>
       </c>
       <c r="E262" t="n">
-        <v>2091</v>
+        <v>3005</v>
       </c>
       <c r="F262" t="n">
         <v>1</v>
@@ -15743,64 +15991,53 @@
       <c r="H262" t="n">
         <v>261</v>
       </c>
-      <c r="I262" t="n">
-        <v>12638</v>
-      </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>Obra de construção do novo Fórum da Comarca de Carangola.</t>
+          <t>Reformas de Subestações e Linhas de Transmissão</t>
         </is>
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
-        </is>
-      </c>
-      <c r="L262" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M262" t="n">
-        <v>1</v>
+          <t>INICIANDO</t>
+        </is>
       </c>
       <c r="N262" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="O262" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Montes Claros</t>
         </is>
       </c>
       <c r="P262" t="inlineStr">
         <is>
-          <t>CARANGOLA</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE MONTES CLAROS</t>
         </is>
       </c>
       <c r="Q262" t="n">
         <v>0</v>
       </c>
       <c r="R262" t="n">
-        <v>12843388</v>
+        <v>16058991</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>4031</v>
+        <v>5391</v>
       </c>
       <c r="B263" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C263" t="n">
-        <v>61</v>
+        <v>752</v>
       </c>
       <c r="D263" t="n">
-        <v>706</v>
+        <v>92</v>
       </c>
       <c r="E263" t="n">
-        <v>2091</v>
+        <v>3005</v>
       </c>
       <c r="F263" t="n">
         <v>1</v>
@@ -15811,64 +16048,53 @@
       <c r="H263" t="n">
         <v>262</v>
       </c>
-      <c r="I263" t="n">
-        <v>12400</v>
-      </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Contrato a execução da obra de reforma e ampliação do Fórum da Comarca de Ipatinga/MG</t>
+          <t>Reformas de Subestações e Linhas de Transmissão</t>
         </is>
       </c>
       <c r="K263" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
-        </is>
-      </c>
-      <c r="L263" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M263" t="n">
-        <v>1</v>
+          <t>INICIANDO</t>
+        </is>
       </c>
       <c r="N263" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="O263" t="inlineStr">
         <is>
-          <t>Região Intermediária de Ipatinga</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P263" t="inlineStr">
         <is>
-          <t>IPATINGA</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE JUÍZ DE FORA</t>
         </is>
       </c>
       <c r="Q263" t="n">
         <v>0</v>
       </c>
       <c r="R263" t="n">
-        <v>18849069</v>
+        <v>65795530</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>4031</v>
+        <v>5391</v>
       </c>
       <c r="B264" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C264" t="n">
-        <v>61</v>
+        <v>752</v>
       </c>
       <c r="D264" t="n">
-        <v>706</v>
+        <v>92</v>
       </c>
       <c r="E264" t="n">
-        <v>2091</v>
+        <v>3005</v>
       </c>
       <c r="F264" t="n">
         <v>1</v>
@@ -15879,64 +16105,53 @@
       <c r="H264" t="n">
         <v>263</v>
       </c>
-      <c r="I264" t="n">
-        <v>12288</v>
-      </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Reforma e Ampliação do Fórum da Comarca de Monte Belo/MG</t>
+          <t>Reformas de Subestações e Linhas de Transmissão</t>
         </is>
       </c>
       <c r="K264" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
-        </is>
-      </c>
-      <c r="L264" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M264" t="n">
-        <v>1</v>
+          <t>INICIANDO</t>
+        </is>
       </c>
       <c r="N264" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="O264" t="inlineStr">
         <is>
-          <t>Região Intermediária de Varginha</t>
+          <t>Região Intermediária de Uberlândia</t>
         </is>
       </c>
       <c r="P264" t="inlineStr">
         <is>
-          <t>MONTE BELO</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERLÂNDIA</t>
         </is>
       </c>
       <c r="Q264" t="n">
         <v>0</v>
       </c>
       <c r="R264" t="n">
-        <v>1950000</v>
+        <v>44156794</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>4031</v>
+        <v>5391</v>
       </c>
       <c r="B265" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C265" t="n">
-        <v>61</v>
+        <v>752</v>
       </c>
       <c r="D265" t="n">
-        <v>706</v>
+        <v>92</v>
       </c>
       <c r="E265" t="n">
-        <v>2091</v>
+        <v>3005</v>
       </c>
       <c r="F265" t="n">
         <v>1</v>
@@ -15947,64 +16162,53 @@
       <c r="H265" t="n">
         <v>264</v>
       </c>
-      <c r="I265" t="n">
-        <v>12816</v>
-      </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>Obra de construção do novo Fórum da Comarca de Pirapora/MG</t>
+          <t>Reformas de Subestações e Linhas de Transmissão</t>
         </is>
       </c>
       <c r="K265" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
-        </is>
-      </c>
-      <c r="L265" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M265" t="n">
-        <v>1</v>
+          <t>INICIANDO</t>
+        </is>
       </c>
       <c r="N265" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="O265" t="inlineStr">
         <is>
-          <t>Região Intermediária de Montes Claros</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P265" t="inlineStr">
         <is>
-          <t>PIRAPORA</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q265" t="n">
         <v>0</v>
       </c>
       <c r="R265" t="n">
-        <v>22776109</v>
+        <v>140716908</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>4031</v>
+        <v>5391</v>
       </c>
       <c r="B266" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C266" t="n">
-        <v>61</v>
+        <v>752</v>
       </c>
       <c r="D266" t="n">
-        <v>706</v>
+        <v>92</v>
       </c>
       <c r="E266" t="n">
-        <v>2091</v>
+        <v>3005</v>
       </c>
       <c r="F266" t="n">
         <v>1</v>
@@ -16015,64 +16219,53 @@
       <c r="H266" t="n">
         <v>265</v>
       </c>
-      <c r="I266" t="n">
-        <v>12781</v>
-      </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>Construção do novo fórum da Comarca de São Gonçalo do Sapucaí/MG</t>
+          <t>Reformas de Subestações e Linhas de Transmissão</t>
         </is>
       </c>
       <c r="K266" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
-        </is>
-      </c>
-      <c r="L266" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M266" t="n">
-        <v>1</v>
+          <t>INICIANDO</t>
+        </is>
       </c>
       <c r="N266" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="O266" t="inlineStr">
         <is>
-          <t>Região Intermediária de Varginha</t>
+          <t>Região Intermediária de Ipatinga</t>
         </is>
       </c>
       <c r="P266" t="inlineStr">
         <is>
-          <t>SÃO GONÇALO DO SAPUCAÍ</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE IPATINGA</t>
         </is>
       </c>
       <c r="Q266" t="n">
         <v>0</v>
       </c>
       <c r="R266" t="n">
-        <v>14670005</v>
+        <v>8715687</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>4031</v>
+        <v>5391</v>
       </c>
       <c r="B267" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C267" t="n">
-        <v>61</v>
+        <v>752</v>
       </c>
       <c r="D267" t="n">
-        <v>706</v>
+        <v>92</v>
       </c>
       <c r="E267" t="n">
-        <v>2091</v>
+        <v>3005</v>
       </c>
       <c r="F267" t="n">
         <v>1</v>
@@ -16083,64 +16276,53 @@
       <c r="H267" t="n">
         <v>266</v>
       </c>
-      <c r="I267" t="n">
-        <v>12799</v>
-      </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t xml:space="preserve">Construção do novo Fórum da Comarca de Timóteo/MG </t>
+          <t>Reformas de Subestações e Linhas de Transmissão</t>
         </is>
       </c>
       <c r="K267" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
-        </is>
-      </c>
-      <c r="L267" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M267" t="n">
-        <v>1</v>
+          <t>INICIANDO</t>
+        </is>
       </c>
       <c r="N267" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="O267" t="inlineStr">
         <is>
-          <t>Região Intermediária de Ipatinga</t>
+          <t>Região Intermediária de Uberaba</t>
         </is>
       </c>
       <c r="P267" t="inlineStr">
         <is>
-          <t>TIMÓTEO</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERABA</t>
         </is>
       </c>
       <c r="Q267" t="n">
         <v>0</v>
       </c>
       <c r="R267" t="n">
-        <v>19506288</v>
+        <v>24622611</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>4031</v>
+        <v>5391</v>
       </c>
       <c r="B268" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C268" t="n">
-        <v>61</v>
+        <v>752</v>
       </c>
       <c r="D268" t="n">
-        <v>706</v>
+        <v>94</v>
       </c>
       <c r="E268" t="n">
-        <v>2091</v>
+        <v>3001</v>
       </c>
       <c r="F268" t="n">
         <v>1</v>
@@ -16151,12 +16333,9 @@
       <c r="H268" t="n">
         <v>267</v>
       </c>
-      <c r="I268" t="n">
-        <v>12833</v>
-      </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>Obra de construção do novo Fórum da Comarca de Rio Novo.</t>
+          <t>Expansão do Sistema de Geração</t>
         </is>
       </c>
       <c r="K268" t="inlineStr">
@@ -16164,2053 +16343,25 @@
           <t>INICIANDO</t>
         </is>
       </c>
-      <c r="L268" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M268" t="n">
-        <v>1</v>
-      </c>
       <c r="N268" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="O268" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P268" t="inlineStr">
         <is>
-          <t>RIO NOVO</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q268" t="n">
         <v>0</v>
       </c>
       <c r="R268" t="n">
-        <v>4976096</v>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" t="n">
-        <v>4031</v>
-      </c>
-      <c r="B269" t="n">
-        <v>2</v>
-      </c>
-      <c r="C269" t="n">
-        <v>61</v>
-      </c>
-      <c r="D269" t="n">
-        <v>706</v>
-      </c>
-      <c r="E269" t="n">
-        <v>2091</v>
-      </c>
-      <c r="F269" t="n">
-        <v>1</v>
-      </c>
-      <c r="G269" t="n">
-        <v>0</v>
-      </c>
-      <c r="H269" t="n">
-        <v>268</v>
-      </c>
-      <c r="I269" t="n">
-        <v>12629</v>
-      </c>
-      <c r="J269" t="inlineStr">
-        <is>
-          <t>Obra de construção do novo Fórum da Comarca de Luz.</t>
-        </is>
-      </c>
-      <c r="K269" t="inlineStr">
-        <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="L269" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M269" t="n">
-        <v>1</v>
-      </c>
-      <c r="N269" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="O269" t="inlineStr">
-        <is>
-          <t>Região Intermediária de Divinópolis</t>
-        </is>
-      </c>
-      <c r="P269" t="inlineStr">
-        <is>
-          <t>LUZ</t>
-        </is>
-      </c>
-      <c r="Q269" t="n">
-        <v>0</v>
-      </c>
-      <c r="R269" t="n">
-        <v>7654409</v>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" t="n">
-        <v>4031</v>
-      </c>
-      <c r="B270" t="n">
-        <v>2</v>
-      </c>
-      <c r="C270" t="n">
-        <v>61</v>
-      </c>
-      <c r="D270" t="n">
-        <v>706</v>
-      </c>
-      <c r="E270" t="n">
-        <v>2091</v>
-      </c>
-      <c r="F270" t="n">
-        <v>1</v>
-      </c>
-      <c r="G270" t="n">
-        <v>0</v>
-      </c>
-      <c r="H270" t="n">
-        <v>269</v>
-      </c>
-      <c r="I270" t="n">
-        <v>12607</v>
-      </c>
-      <c r="J270" t="inlineStr">
-        <is>
-          <t>Reforma e ampliação do Fórum da Comarca de Sete Lagoas/MG.</t>
-        </is>
-      </c>
-      <c r="K270" t="inlineStr">
-        <is>
-          <t>EXECUÇÃO</t>
-        </is>
-      </c>
-      <c r="L270" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M270" t="n">
-        <v>1</v>
-      </c>
-      <c r="N270" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="O270" t="inlineStr">
-        <is>
-          <t>Região Intermediária de Belo Horizonte</t>
-        </is>
-      </c>
-      <c r="P270" t="inlineStr">
-        <is>
-          <t>SETE LAGOAS</t>
-        </is>
-      </c>
-      <c r="Q270" t="n">
-        <v>0</v>
-      </c>
-      <c r="R270" t="n">
-        <v>32235085</v>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" t="n">
-        <v>4031</v>
-      </c>
-      <c r="B271" t="n">
-        <v>2</v>
-      </c>
-      <c r="C271" t="n">
-        <v>61</v>
-      </c>
-      <c r="D271" t="n">
-        <v>706</v>
-      </c>
-      <c r="E271" t="n">
-        <v>2091</v>
-      </c>
-      <c r="F271" t="n">
-        <v>1</v>
-      </c>
-      <c r="G271" t="n">
-        <v>0</v>
-      </c>
-      <c r="H271" t="n">
-        <v>270</v>
-      </c>
-      <c r="I271" t="n">
-        <v>12639</v>
-      </c>
-      <c r="J271" t="inlineStr">
-        <is>
-          <t>Obra de construção do novo Fórum da Comarca de Três Pontas</t>
-        </is>
-      </c>
-      <c r="K271" t="inlineStr">
-        <is>
-          <t>EXECUÇÃO</t>
-        </is>
-      </c>
-      <c r="L271" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M271" t="n">
-        <v>1</v>
-      </c>
-      <c r="N271" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="O271" t="inlineStr">
-        <is>
-          <t>Região Intermediária de Varginha</t>
-        </is>
-      </c>
-      <c r="P271" t="inlineStr">
-        <is>
-          <t>TRÊS PONTAS</t>
-        </is>
-      </c>
-      <c r="Q271" t="n">
-        <v>0</v>
-      </c>
-      <c r="R271" t="n">
-        <v>9489687</v>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" t="n">
-        <v>4031</v>
-      </c>
-      <c r="B272" t="n">
-        <v>2</v>
-      </c>
-      <c r="C272" t="n">
-        <v>61</v>
-      </c>
-      <c r="D272" t="n">
-        <v>706</v>
-      </c>
-      <c r="E272" t="n">
-        <v>2091</v>
-      </c>
-      <c r="F272" t="n">
-        <v>1</v>
-      </c>
-      <c r="G272" t="n">
-        <v>0</v>
-      </c>
-      <c r="H272" t="n">
-        <v>271</v>
-      </c>
-      <c r="I272" t="n">
-        <v>11547</v>
-      </c>
-      <c r="J272" t="inlineStr">
-        <is>
-          <t>RETOMADA DA OBRA DE CONSTRUÇÃO DO NOVO PRÉDIO DO FÓRUM DA COMARCA DE ITAJUBÁ/MG</t>
-        </is>
-      </c>
-      <c r="K272" t="inlineStr">
-        <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="L272" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M272" t="n">
-        <v>1</v>
-      </c>
-      <c r="N272" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="O272" t="inlineStr">
-        <is>
-          <t>Região Intermediária de Pouso Alegre</t>
-        </is>
-      </c>
-      <c r="P272" t="inlineStr">
-        <is>
-          <t>ITAJUBÁ</t>
-        </is>
-      </c>
-      <c r="Q272" t="n">
-        <v>0</v>
-      </c>
-      <c r="R272" t="n">
-        <v>9366263</v>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="n">
-        <v>4031</v>
-      </c>
-      <c r="B273" t="n">
-        <v>2</v>
-      </c>
-      <c r="C273" t="n">
-        <v>61</v>
-      </c>
-      <c r="D273" t="n">
-        <v>706</v>
-      </c>
-      <c r="E273" t="n">
-        <v>2091</v>
-      </c>
-      <c r="F273" t="n">
-        <v>1</v>
-      </c>
-      <c r="G273" t="n">
-        <v>0</v>
-      </c>
-      <c r="H273" t="n">
-        <v>272</v>
-      </c>
-      <c r="I273" t="n">
-        <v>12856</v>
-      </c>
-      <c r="J273" t="inlineStr">
-        <is>
-          <t>Retomada da obra de construção do novo Fórum da Comarca de Poços de Caldas.</t>
-        </is>
-      </c>
-      <c r="K273" t="inlineStr">
-        <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="L273" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M273" t="n">
-        <v>1</v>
-      </c>
-      <c r="N273" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="O273" t="inlineStr">
-        <is>
-          <t>Região Intermediária de Pouso Alegre</t>
-        </is>
-      </c>
-      <c r="P273" t="inlineStr">
-        <is>
-          <t>POÇOS DE CALDAS</t>
-        </is>
-      </c>
-      <c r="Q273" t="n">
-        <v>0</v>
-      </c>
-      <c r="R273" t="n">
-        <v>11009635</v>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="n">
-        <v>4031</v>
-      </c>
-      <c r="B274" t="n">
-        <v>2</v>
-      </c>
-      <c r="C274" t="n">
-        <v>61</v>
-      </c>
-      <c r="D274" t="n">
-        <v>706</v>
-      </c>
-      <c r="E274" t="n">
-        <v>2091</v>
-      </c>
-      <c r="F274" t="n">
-        <v>1</v>
-      </c>
-      <c r="G274" t="n">
-        <v>0</v>
-      </c>
-      <c r="H274" t="n">
-        <v>273</v>
-      </c>
-      <c r="I274" t="n">
-        <v>12344</v>
-      </c>
-      <c r="J274" t="inlineStr">
-        <is>
-          <t>Construção do novo prédio do Fórum da Comarca de Camanducaia/MG</t>
-        </is>
-      </c>
-      <c r="K274" t="inlineStr">
-        <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="L274" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M274" t="n">
-        <v>1</v>
-      </c>
-      <c r="N274" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="O274" t="inlineStr">
-        <is>
-          <t>Região Intermediária de Pouso Alegre</t>
-        </is>
-      </c>
-      <c r="P274" t="inlineStr">
-        <is>
-          <t>CAMANDUCAIA</t>
-        </is>
-      </c>
-      <c r="Q274" t="n">
-        <v>0</v>
-      </c>
-      <c r="R274" t="n">
-        <v>4627222</v>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="n">
-        <v>4031</v>
-      </c>
-      <c r="B275" t="n">
-        <v>2</v>
-      </c>
-      <c r="C275" t="n">
-        <v>61</v>
-      </c>
-      <c r="D275" t="n">
-        <v>706</v>
-      </c>
-      <c r="E275" t="n">
-        <v>2091</v>
-      </c>
-      <c r="F275" t="n">
-        <v>1</v>
-      </c>
-      <c r="G275" t="n">
-        <v>0</v>
-      </c>
-      <c r="H275" t="n">
-        <v>274</v>
-      </c>
-      <c r="J275" t="inlineStr">
-        <is>
-          <t>Obra de construção do novo Fórum da Comarca de São João do Paraíso</t>
-        </is>
-      </c>
-      <c r="K275" t="inlineStr">
-        <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="L275" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M275" t="n">
-        <v>1</v>
-      </c>
-      <c r="N275" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="O275" t="inlineStr">
-        <is>
-          <t>Região Intermediária de Montes Claros</t>
-        </is>
-      </c>
-      <c r="P275" t="inlineStr">
-        <is>
-          <t>SÃO JOÃO DO PARAÍSO</t>
-        </is>
-      </c>
-      <c r="Q275" t="n">
-        <v>0</v>
-      </c>
-      <c r="R275" t="n">
-        <v>7290196</v>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="n">
-        <v>4031</v>
-      </c>
-      <c r="B276" t="n">
-        <v>2</v>
-      </c>
-      <c r="C276" t="n">
-        <v>61</v>
-      </c>
-      <c r="D276" t="n">
-        <v>706</v>
-      </c>
-      <c r="E276" t="n">
-        <v>2091</v>
-      </c>
-      <c r="F276" t="n">
-        <v>1</v>
-      </c>
-      <c r="G276" t="n">
-        <v>0</v>
-      </c>
-      <c r="H276" t="n">
-        <v>275</v>
-      </c>
-      <c r="J276" t="inlineStr">
-        <is>
-          <t>Implantação do Fórum Digital no município de Brasilândia de Minas</t>
-        </is>
-      </c>
-      <c r="K276" t="inlineStr">
-        <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="L276" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M276" t="n">
-        <v>1</v>
-      </c>
-      <c r="N276" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="O276" t="inlineStr">
-        <is>
-          <t>Região Intermediária de Patos de Minas</t>
-        </is>
-      </c>
-      <c r="P276" t="inlineStr">
-        <is>
-          <t>BRASILÂNDIA DE MINAS</t>
-        </is>
-      </c>
-      <c r="Q276" t="n">
-        <v>0</v>
-      </c>
-      <c r="R276" t="n">
-        <v>1373680</v>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="n">
-        <v>4031</v>
-      </c>
-      <c r="B277" t="n">
-        <v>2</v>
-      </c>
-      <c r="C277" t="n">
-        <v>61</v>
-      </c>
-      <c r="D277" t="n">
-        <v>706</v>
-      </c>
-      <c r="E277" t="n">
-        <v>2091</v>
-      </c>
-      <c r="F277" t="n">
-        <v>1</v>
-      </c>
-      <c r="G277" t="n">
-        <v>0</v>
-      </c>
-      <c r="H277" t="n">
-        <v>276</v>
-      </c>
-      <c r="J277" t="inlineStr">
-        <is>
-          <t>Implantação do Fórum Digital no município de São Gonçalo do Abaeté</t>
-        </is>
-      </c>
-      <c r="K277" t="inlineStr">
-        <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="L277" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M277" t="n">
-        <v>1</v>
-      </c>
-      <c r="N277" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="O277" t="inlineStr">
-        <is>
-          <t>Região Intermediária de Patos de Minas</t>
-        </is>
-      </c>
-      <c r="P277" t="inlineStr">
-        <is>
-          <t>SÃO GONÇALO DO ABAETÉ</t>
-        </is>
-      </c>
-      <c r="Q277" t="n">
-        <v>0</v>
-      </c>
-      <c r="R277" t="n">
-        <v>1373680</v>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="n">
-        <v>4031</v>
-      </c>
-      <c r="B278" t="n">
-        <v>2</v>
-      </c>
-      <c r="C278" t="n">
-        <v>61</v>
-      </c>
-      <c r="D278" t="n">
-        <v>706</v>
-      </c>
-      <c r="E278" t="n">
-        <v>2091</v>
-      </c>
-      <c r="F278" t="n">
-        <v>1</v>
-      </c>
-      <c r="G278" t="n">
-        <v>0</v>
-      </c>
-      <c r="H278" t="n">
-        <v>277</v>
-      </c>
-      <c r="J278" t="inlineStr">
-        <is>
-          <t>Implantação do Fórum Digital no município de Ponto Chique</t>
-        </is>
-      </c>
-      <c r="K278" t="inlineStr">
-        <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="L278" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M278" t="n">
-        <v>1</v>
-      </c>
-      <c r="N278" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="O278" t="inlineStr">
-        <is>
-          <t>Região Intermediária de Montes Claros</t>
-        </is>
-      </c>
-      <c r="P278" t="inlineStr">
-        <is>
-          <t>PONTO CHIQUE</t>
-        </is>
-      </c>
-      <c r="Q278" t="n">
-        <v>0</v>
-      </c>
-      <c r="R278" t="n">
-        <v>1760000</v>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="n">
-        <v>4031</v>
-      </c>
-      <c r="B279" t="n">
-        <v>2</v>
-      </c>
-      <c r="C279" t="n">
-        <v>61</v>
-      </c>
-      <c r="D279" t="n">
-        <v>706</v>
-      </c>
-      <c r="E279" t="n">
-        <v>2091</v>
-      </c>
-      <c r="F279" t="n">
-        <v>1</v>
-      </c>
-      <c r="G279" t="n">
-        <v>0</v>
-      </c>
-      <c r="H279" t="n">
-        <v>278</v>
-      </c>
-      <c r="I279" t="n">
-        <v>12627</v>
-      </c>
-      <c r="J279" t="inlineStr">
-        <is>
-          <t>Execução da 4ª (quarta) parcela da reforma parcial do Edifício-Sede do TRIBUNAL.</t>
-        </is>
-      </c>
-      <c r="K279" t="inlineStr">
-        <is>
-          <t>EXECUÇÃO</t>
-        </is>
-      </c>
-      <c r="L279" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M279" t="n">
-        <v>1</v>
-      </c>
-      <c r="N279" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="O279" t="inlineStr">
-        <is>
-          <t>Região Intermediária de Belo Horizonte</t>
-        </is>
-      </c>
-      <c r="P279" t="inlineStr">
-        <is>
-          <t>BELO HORIZONTE</t>
-        </is>
-      </c>
-      <c r="Q279" t="n">
-        <v>0</v>
-      </c>
-      <c r="R279" t="n">
-        <v>38084213</v>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="n">
-        <v>4031</v>
-      </c>
-      <c r="B280" t="n">
-        <v>2</v>
-      </c>
-      <c r="C280" t="n">
-        <v>61</v>
-      </c>
-      <c r="D280" t="n">
-        <v>706</v>
-      </c>
-      <c r="E280" t="n">
-        <v>2091</v>
-      </c>
-      <c r="F280" t="n">
-        <v>1</v>
-      </c>
-      <c r="G280" t="n">
-        <v>0</v>
-      </c>
-      <c r="H280" t="n">
-        <v>279</v>
-      </c>
-      <c r="I280" t="n">
-        <v>12146</v>
-      </c>
-      <c r="J280" t="inlineStr">
-        <is>
-          <t>Reforma geral do Fórum Lafayette, em Belo Horizonte/MG</t>
-        </is>
-      </c>
-      <c r="K280" t="inlineStr">
-        <is>
-          <t>EXECUÇÃO</t>
-        </is>
-      </c>
-      <c r="L280" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M280" t="n">
-        <v>1</v>
-      </c>
-      <c r="N280" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="O280" t="inlineStr">
-        <is>
-          <t>Região Intermediária de Belo Horizonte</t>
-        </is>
-      </c>
-      <c r="P280" t="inlineStr">
-        <is>
-          <t>BELO HORIZONTE</t>
-        </is>
-      </c>
-      <c r="Q280" t="n">
-        <v>0</v>
-      </c>
-      <c r="R280" t="n">
-        <v>135013067</v>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="n">
-        <v>4031</v>
-      </c>
-      <c r="B281" t="n">
-        <v>2</v>
-      </c>
-      <c r="C281" t="n">
-        <v>61</v>
-      </c>
-      <c r="D281" t="n">
-        <v>706</v>
-      </c>
-      <c r="E281" t="n">
-        <v>2091</v>
-      </c>
-      <c r="F281" t="n">
-        <v>1</v>
-      </c>
-      <c r="G281" t="n">
-        <v>0</v>
-      </c>
-      <c r="H281" t="n">
-        <v>280</v>
-      </c>
-      <c r="I281" t="n">
-        <v>12703</v>
-      </c>
-      <c r="J281" t="inlineStr">
-        <is>
-          <t>Cincão - Reforma parcial para adequações da estrutura física dos Armazéns 6, 7 e 8, Galpão 2, Arquivo Central e Permanente</t>
-        </is>
-      </c>
-      <c r="K281" t="inlineStr">
-        <is>
-          <t>EXECUÇÃO</t>
-        </is>
-      </c>
-      <c r="L281" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M281" t="n">
-        <v>1</v>
-      </c>
-      <c r="N281" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="O281" t="inlineStr">
-        <is>
-          <t>Região Intermediária de Belo Horizonte</t>
-        </is>
-      </c>
-      <c r="P281" t="inlineStr">
-        <is>
-          <t>BELO HORIZONTE</t>
-        </is>
-      </c>
-      <c r="Q281" t="n">
-        <v>0</v>
-      </c>
-      <c r="R281" t="n">
-        <v>1052449</v>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" t="n">
-        <v>4031</v>
-      </c>
-      <c r="B282" t="n">
-        <v>2</v>
-      </c>
-      <c r="C282" t="n">
-        <v>61</v>
-      </c>
-      <c r="D282" t="n">
-        <v>706</v>
-      </c>
-      <c r="E282" t="n">
-        <v>2091</v>
-      </c>
-      <c r="F282" t="n">
-        <v>1</v>
-      </c>
-      <c r="G282" t="n">
-        <v>0</v>
-      </c>
-      <c r="H282" t="n">
-        <v>281</v>
-      </c>
-      <c r="J282" t="inlineStr">
-        <is>
-          <t>Obra de construção do novo Fórum da Comarca de Monte Alegre de Minas</t>
-        </is>
-      </c>
-      <c r="K282" t="inlineStr">
-        <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="L282" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M282" t="n">
-        <v>1</v>
-      </c>
-      <c r="N282" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="O282" t="inlineStr">
-        <is>
-          <t>Região Intermediária de Uberlândia</t>
-        </is>
-      </c>
-      <c r="P282" t="inlineStr">
-        <is>
-          <t>MONTE ALEGRE DE MINAS</t>
-        </is>
-      </c>
-      <c r="Q282" t="n">
-        <v>0</v>
-      </c>
-      <c r="R282" t="n">
-        <v>6139672</v>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" t="n">
-        <v>5011</v>
-      </c>
-      <c r="B283" t="n">
-        <v>4</v>
-      </c>
-      <c r="C283" t="n">
-        <v>122</v>
-      </c>
-      <c r="D283" t="n">
-        <v>133</v>
-      </c>
-      <c r="E283" t="n">
-        <v>3017</v>
-      </c>
-      <c r="F283" t="n">
-        <v>1</v>
-      </c>
-      <c r="G283" t="n">
-        <v>0</v>
-      </c>
-      <c r="H283" t="n">
-        <v>282</v>
-      </c>
-      <c r="J283" t="inlineStr">
-        <is>
-          <t>CENTRO DE CULTURA PRESIDENTE ITAMAR FRANCO</t>
-        </is>
-      </c>
-      <c r="K283" t="inlineStr">
-        <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="N283" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="O283" t="inlineStr">
-        <is>
-          <t>Estadual</t>
-        </is>
-      </c>
-      <c r="P283" t="inlineStr">
-        <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
-        </is>
-      </c>
-      <c r="Q283" t="n">
-        <v>0</v>
-      </c>
-      <c r="R283" t="n">
-        <v>800000</v>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" t="n">
-        <v>5031</v>
-      </c>
-      <c r="B284" t="n">
-        <v>19</v>
-      </c>
-      <c r="C284" t="n">
-        <v>572</v>
-      </c>
-      <c r="D284" t="n">
-        <v>133</v>
-      </c>
-      <c r="E284" t="n">
-        <v>3015</v>
-      </c>
-      <c r="F284" t="n">
-        <v>1</v>
-      </c>
-      <c r="G284" t="n">
-        <v>0</v>
-      </c>
-      <c r="H284" t="n">
-        <v>283</v>
-      </c>
-      <c r="J284" t="inlineStr">
-        <is>
-          <t>BALNEÁRIO ÁGUAS SANTAS - TIRADENTES/MG | BARREIO DE ARAXÁ</t>
-        </is>
-      </c>
-      <c r="K284" t="inlineStr">
-        <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="N284" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="O284" t="inlineStr">
-        <is>
-          <t>Estadual</t>
-        </is>
-      </c>
-      <c r="P284" t="inlineStr">
-        <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
-        </is>
-      </c>
-      <c r="Q284" t="n">
-        <v>0</v>
-      </c>
-      <c r="R284" t="n">
-        <v>4782988</v>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" t="n">
-        <v>5141</v>
-      </c>
-      <c r="B285" t="n">
-        <v>4</v>
-      </c>
-      <c r="C285" t="n">
-        <v>126</v>
-      </c>
-      <c r="D285" t="n">
-        <v>30</v>
-      </c>
-      <c r="E285" t="n">
-        <v>6006</v>
-      </c>
-      <c r="F285" t="n">
-        <v>1</v>
-      </c>
-      <c r="G285" t="n">
-        <v>0</v>
-      </c>
-      <c r="H285" t="n">
-        <v>284</v>
-      </c>
-      <c r="J285" t="inlineStr">
-        <is>
-          <t>ELABORAÇÃO E EXECUÇÃO DE PROJETOS RELACIONADOS À REFORMA, MODERNIZAÇÃO E ADEQUAÇÃO DAS INSTALAÇÕES PREDIAIS DA COMPANHIA.</t>
-        </is>
-      </c>
-      <c r="K285" t="inlineStr">
-        <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="N285" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="O285" t="inlineStr">
-        <is>
-          <t>Estadual</t>
-        </is>
-      </c>
-      <c r="P285" t="inlineStr">
-        <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
-        </is>
-      </c>
-      <c r="Q285" t="n">
-        <v>0</v>
-      </c>
-      <c r="R285" t="n">
-        <v>16317109</v>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" t="n">
-        <v>5251</v>
-      </c>
-      <c r="B286" t="n">
-        <v>25</v>
-      </c>
-      <c r="C286" t="n">
-        <v>121</v>
-      </c>
-      <c r="D286" t="n">
-        <v>133</v>
-      </c>
-      <c r="E286" t="n">
-        <v>3018</v>
-      </c>
-      <c r="F286" t="n">
-        <v>1</v>
-      </c>
-      <c r="G286" t="n">
-        <v>0</v>
-      </c>
-      <c r="H286" t="n">
-        <v>285</v>
-      </c>
-      <c r="J286" t="inlineStr">
-        <is>
-          <t>Projeto de Expansão</t>
-        </is>
-      </c>
-      <c r="K286" t="inlineStr">
-        <is>
-          <t>EXECUÇÃO</t>
-        </is>
-      </c>
-      <c r="N286" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="O286" t="inlineStr">
-        <is>
-          <t>Região Intermediária de Belo Horizonte</t>
-        </is>
-      </c>
-      <c r="P286" t="inlineStr">
-        <is>
-          <t>BELO HORIZONTE</t>
-        </is>
-      </c>
-      <c r="Q286" t="n">
-        <v>0</v>
-      </c>
-      <c r="R286" t="n">
-        <v>457766318</v>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" t="n">
-        <v>5391</v>
-      </c>
-      <c r="B287" t="n">
-        <v>25</v>
-      </c>
-      <c r="C287" t="n">
-        <v>752</v>
-      </c>
-      <c r="D287" t="n">
-        <v>92</v>
-      </c>
-      <c r="E287" t="n">
-        <v>3004</v>
-      </c>
-      <c r="F287" t="n">
-        <v>1</v>
-      </c>
-      <c r="G287" t="n">
-        <v>0</v>
-      </c>
-      <c r="H287" t="n">
-        <v>286</v>
-      </c>
-      <c r="J287" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Expansão e Aquisição do Sistema de Transmissão </t>
-        </is>
-      </c>
-      <c r="K287" t="inlineStr">
-        <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="N287" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="O287" t="inlineStr">
-        <is>
-          <t>Região Intermediária de Belo Horizonte</t>
-        </is>
-      </c>
-      <c r="P287" t="inlineStr">
-        <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BELO HORIZONTE</t>
-        </is>
-      </c>
-      <c r="Q287" t="n">
-        <v>0</v>
-      </c>
-      <c r="R287" t="n">
-        <v>92004926</v>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" t="n">
-        <v>5391</v>
-      </c>
-      <c r="B288" t="n">
-        <v>25</v>
-      </c>
-      <c r="C288" t="n">
-        <v>752</v>
-      </c>
-      <c r="D288" t="n">
-        <v>92</v>
-      </c>
-      <c r="E288" t="n">
-        <v>3004</v>
-      </c>
-      <c r="F288" t="n">
-        <v>1</v>
-      </c>
-      <c r="G288" t="n">
-        <v>0</v>
-      </c>
-      <c r="H288" t="n">
-        <v>287</v>
-      </c>
-      <c r="J288" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Expansão e Aquisição do Sistema de Transmissão </t>
-        </is>
-      </c>
-      <c r="K288" t="inlineStr">
-        <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="N288" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="O288" t="inlineStr">
-        <is>
-          <t>Região Intermediária de Montes Claros</t>
-        </is>
-      </c>
-      <c r="P288" t="inlineStr">
-        <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE MONTES CLAROS</t>
-        </is>
-      </c>
-      <c r="Q288" t="n">
-        <v>0</v>
-      </c>
-      <c r="R288" t="n">
-        <v>10705994</v>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" t="n">
-        <v>5391</v>
-      </c>
-      <c r="B289" t="n">
-        <v>25</v>
-      </c>
-      <c r="C289" t="n">
-        <v>752</v>
-      </c>
-      <c r="D289" t="n">
-        <v>92</v>
-      </c>
-      <c r="E289" t="n">
-        <v>3004</v>
-      </c>
-      <c r="F289" t="n">
-        <v>1</v>
-      </c>
-      <c r="G289" t="n">
-        <v>0</v>
-      </c>
-      <c r="H289" t="n">
-        <v>288</v>
-      </c>
-      <c r="J289" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Expansão e Aquisição do Sistema de Transmissão </t>
-        </is>
-      </c>
-      <c r="K289" t="inlineStr">
-        <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="N289" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="O289" t="inlineStr">
-        <is>
-          <t>Região Intermediária de Juíz de Fora</t>
-        </is>
-      </c>
-      <c r="P289" t="inlineStr">
-        <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE JUÍZ DE FORA</t>
-        </is>
-      </c>
-      <c r="Q289" t="n">
-        <v>0</v>
-      </c>
-      <c r="R289" t="n">
-        <v>10464844</v>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" t="n">
-        <v>5391</v>
-      </c>
-      <c r="B290" t="n">
-        <v>25</v>
-      </c>
-      <c r="C290" t="n">
-        <v>752</v>
-      </c>
-      <c r="D290" t="n">
-        <v>92</v>
-      </c>
-      <c r="E290" t="n">
-        <v>3004</v>
-      </c>
-      <c r="F290" t="n">
-        <v>1</v>
-      </c>
-      <c r="G290" t="n">
-        <v>0</v>
-      </c>
-      <c r="H290" t="n">
-        <v>289</v>
-      </c>
-      <c r="J290" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Expansão e Aquisição do Sistema de Transmissão </t>
-        </is>
-      </c>
-      <c r="K290" t="inlineStr">
-        <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="N290" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="O290" t="inlineStr">
-        <is>
-          <t>Região Intermediária de Uberlândia</t>
-        </is>
-      </c>
-      <c r="P290" t="inlineStr">
-        <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERLÂNDIA</t>
-        </is>
-      </c>
-      <c r="Q290" t="n">
-        <v>0</v>
-      </c>
-      <c r="R290" t="n">
-        <v>2098278</v>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" t="n">
-        <v>5391</v>
-      </c>
-      <c r="B291" t="n">
-        <v>25</v>
-      </c>
-      <c r="C291" t="n">
-        <v>752</v>
-      </c>
-      <c r="D291" t="n">
-        <v>92</v>
-      </c>
-      <c r="E291" t="n">
-        <v>3004</v>
-      </c>
-      <c r="F291" t="n">
-        <v>1</v>
-      </c>
-      <c r="G291" t="n">
-        <v>0</v>
-      </c>
-      <c r="H291" t="n">
-        <v>290</v>
-      </c>
-      <c r="J291" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Expansão e Aquisição do Sistema de Transmissão </t>
-        </is>
-      </c>
-      <c r="K291" t="inlineStr">
-        <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="N291" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="O291" t="inlineStr">
-        <is>
-          <t>Estadual</t>
-        </is>
-      </c>
-      <c r="P291" t="inlineStr">
-        <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
-        </is>
-      </c>
-      <c r="Q291" t="n">
-        <v>0</v>
-      </c>
-      <c r="R291" t="n">
-        <v>96721858</v>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" t="n">
-        <v>5391</v>
-      </c>
-      <c r="B292" t="n">
-        <v>25</v>
-      </c>
-      <c r="C292" t="n">
-        <v>752</v>
-      </c>
-      <c r="D292" t="n">
-        <v>92</v>
-      </c>
-      <c r="E292" t="n">
-        <v>3004</v>
-      </c>
-      <c r="F292" t="n">
-        <v>1</v>
-      </c>
-      <c r="G292" t="n">
-        <v>0</v>
-      </c>
-      <c r="H292" t="n">
-        <v>291</v>
-      </c>
-      <c r="J292" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Expansão e Aquisição do Sistema de Transmissão </t>
-        </is>
-      </c>
-      <c r="K292" t="inlineStr">
-        <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="N292" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="O292" t="inlineStr">
-        <is>
-          <t>Região Intermediária de Uberaba</t>
-        </is>
-      </c>
-      <c r="P292" t="inlineStr">
-        <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERABA</t>
-        </is>
-      </c>
-      <c r="Q292" t="n">
-        <v>0</v>
-      </c>
-      <c r="R292" t="n">
-        <v>16415074</v>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" t="n">
-        <v>5391</v>
-      </c>
-      <c r="B293" t="n">
-        <v>25</v>
-      </c>
-      <c r="C293" t="n">
-        <v>752</v>
-      </c>
-      <c r="D293" t="n">
-        <v>92</v>
-      </c>
-      <c r="E293" t="n">
-        <v>3004</v>
-      </c>
-      <c r="F293" t="n">
-        <v>1</v>
-      </c>
-      <c r="G293" t="n">
-        <v>0</v>
-      </c>
-      <c r="H293" t="n">
-        <v>292</v>
-      </c>
-      <c r="J293" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Expansão e Aquisição do Sistema de Transmissão </t>
-        </is>
-      </c>
-      <c r="K293" t="inlineStr">
-        <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="N293" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="O293" t="inlineStr">
-        <is>
-          <t>Região Intermediária de Ipatinga</t>
-        </is>
-      </c>
-      <c r="P293" t="inlineStr">
-        <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE IPATINGA</t>
-        </is>
-      </c>
-      <c r="Q293" t="n">
-        <v>0</v>
-      </c>
-      <c r="R293" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" t="n">
-        <v>5391</v>
-      </c>
-      <c r="B294" t="n">
-        <v>25</v>
-      </c>
-      <c r="C294" t="n">
-        <v>752</v>
-      </c>
-      <c r="D294" t="n">
-        <v>92</v>
-      </c>
-      <c r="E294" t="n">
-        <v>3005</v>
-      </c>
-      <c r="F294" t="n">
-        <v>1</v>
-      </c>
-      <c r="G294" t="n">
-        <v>0</v>
-      </c>
-      <c r="H294" t="n">
-        <v>293</v>
-      </c>
-      <c r="J294" t="inlineStr">
-        <is>
-          <t>Reformas de Subestações e Linhas de Transmissão</t>
-        </is>
-      </c>
-      <c r="K294" t="inlineStr">
-        <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="N294" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="O294" t="inlineStr">
-        <is>
-          <t>Região Intermediária de Belo Horizonte</t>
-        </is>
-      </c>
-      <c r="P294" t="inlineStr">
-        <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BELO HORIZONTE</t>
-        </is>
-      </c>
-      <c r="Q294" t="n">
-        <v>0</v>
-      </c>
-      <c r="R294" t="n">
-        <v>126817302</v>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" t="n">
-        <v>5391</v>
-      </c>
-      <c r="B295" t="n">
-        <v>25</v>
-      </c>
-      <c r="C295" t="n">
-        <v>752</v>
-      </c>
-      <c r="D295" t="n">
-        <v>92</v>
-      </c>
-      <c r="E295" t="n">
-        <v>3005</v>
-      </c>
-      <c r="F295" t="n">
-        <v>1</v>
-      </c>
-      <c r="G295" t="n">
-        <v>0</v>
-      </c>
-      <c r="H295" t="n">
-        <v>294</v>
-      </c>
-      <c r="J295" t="inlineStr">
-        <is>
-          <t>Reformas de Subestações e Linhas de Transmissão</t>
-        </is>
-      </c>
-      <c r="K295" t="inlineStr">
-        <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="N295" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="O295" t="inlineStr">
-        <is>
-          <t>Região Intermediária de Montes Claros</t>
-        </is>
-      </c>
-      <c r="P295" t="inlineStr">
-        <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE MONTES CLAROS</t>
-        </is>
-      </c>
-      <c r="Q295" t="n">
-        <v>0</v>
-      </c>
-      <c r="R295" t="n">
-        <v>16058991</v>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" t="n">
-        <v>5391</v>
-      </c>
-      <c r="B296" t="n">
-        <v>25</v>
-      </c>
-      <c r="C296" t="n">
-        <v>752</v>
-      </c>
-      <c r="D296" t="n">
-        <v>92</v>
-      </c>
-      <c r="E296" t="n">
-        <v>3005</v>
-      </c>
-      <c r="F296" t="n">
-        <v>1</v>
-      </c>
-      <c r="G296" t="n">
-        <v>0</v>
-      </c>
-      <c r="H296" t="n">
-        <v>295</v>
-      </c>
-      <c r="J296" t="inlineStr">
-        <is>
-          <t>Reformas de Subestações e Linhas de Transmissão</t>
-        </is>
-      </c>
-      <c r="K296" t="inlineStr">
-        <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="N296" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="O296" t="inlineStr">
-        <is>
-          <t>Região Intermediária de Juíz de Fora</t>
-        </is>
-      </c>
-      <c r="P296" t="inlineStr">
-        <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE JUÍZ DE FORA</t>
-        </is>
-      </c>
-      <c r="Q296" t="n">
-        <v>0</v>
-      </c>
-      <c r="R296" t="n">
-        <v>65795530</v>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" t="n">
-        <v>5391</v>
-      </c>
-      <c r="B297" t="n">
-        <v>25</v>
-      </c>
-      <c r="C297" t="n">
-        <v>752</v>
-      </c>
-      <c r="D297" t="n">
-        <v>92</v>
-      </c>
-      <c r="E297" t="n">
-        <v>3005</v>
-      </c>
-      <c r="F297" t="n">
-        <v>1</v>
-      </c>
-      <c r="G297" t="n">
-        <v>0</v>
-      </c>
-      <c r="H297" t="n">
-        <v>296</v>
-      </c>
-      <c r="J297" t="inlineStr">
-        <is>
-          <t>Reformas de Subestações e Linhas de Transmissão</t>
-        </is>
-      </c>
-      <c r="K297" t="inlineStr">
-        <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="N297" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="O297" t="inlineStr">
-        <is>
-          <t>Região Intermediária de Uberlândia</t>
-        </is>
-      </c>
-      <c r="P297" t="inlineStr">
-        <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERLÂNDIA</t>
-        </is>
-      </c>
-      <c r="Q297" t="n">
-        <v>0</v>
-      </c>
-      <c r="R297" t="n">
-        <v>44156794</v>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" t="n">
-        <v>5391</v>
-      </c>
-      <c r="B298" t="n">
-        <v>25</v>
-      </c>
-      <c r="C298" t="n">
-        <v>752</v>
-      </c>
-      <c r="D298" t="n">
-        <v>92</v>
-      </c>
-      <c r="E298" t="n">
-        <v>3005</v>
-      </c>
-      <c r="F298" t="n">
-        <v>1</v>
-      </c>
-      <c r="G298" t="n">
-        <v>0</v>
-      </c>
-      <c r="H298" t="n">
-        <v>297</v>
-      </c>
-      <c r="J298" t="inlineStr">
-        <is>
-          <t>Reformas de Subestações e Linhas de Transmissão</t>
-        </is>
-      </c>
-      <c r="K298" t="inlineStr">
-        <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="N298" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="O298" t="inlineStr">
-        <is>
-          <t>Estadual</t>
-        </is>
-      </c>
-      <c r="P298" t="inlineStr">
-        <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
-        </is>
-      </c>
-      <c r="Q298" t="n">
-        <v>0</v>
-      </c>
-      <c r="R298" t="n">
-        <v>140716908</v>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" t="n">
-        <v>5391</v>
-      </c>
-      <c r="B299" t="n">
-        <v>25</v>
-      </c>
-      <c r="C299" t="n">
-        <v>752</v>
-      </c>
-      <c r="D299" t="n">
-        <v>92</v>
-      </c>
-      <c r="E299" t="n">
-        <v>3005</v>
-      </c>
-      <c r="F299" t="n">
-        <v>1</v>
-      </c>
-      <c r="G299" t="n">
-        <v>0</v>
-      </c>
-      <c r="H299" t="n">
-        <v>298</v>
-      </c>
-      <c r="J299" t="inlineStr">
-        <is>
-          <t>Reformas de Subestações e Linhas de Transmissão</t>
-        </is>
-      </c>
-      <c r="K299" t="inlineStr">
-        <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="N299" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="O299" t="inlineStr">
-        <is>
-          <t>Região Intermediária de Ipatinga</t>
-        </is>
-      </c>
-      <c r="P299" t="inlineStr">
-        <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE IPATINGA</t>
-        </is>
-      </c>
-      <c r="Q299" t="n">
-        <v>0</v>
-      </c>
-      <c r="R299" t="n">
-        <v>8715687</v>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" t="n">
-        <v>5391</v>
-      </c>
-      <c r="B300" t="n">
-        <v>25</v>
-      </c>
-      <c r="C300" t="n">
-        <v>752</v>
-      </c>
-      <c r="D300" t="n">
-        <v>92</v>
-      </c>
-      <c r="E300" t="n">
-        <v>3005</v>
-      </c>
-      <c r="F300" t="n">
-        <v>1</v>
-      </c>
-      <c r="G300" t="n">
-        <v>0</v>
-      </c>
-      <c r="H300" t="n">
-        <v>299</v>
-      </c>
-      <c r="J300" t="inlineStr">
-        <is>
-          <t>Reformas de Subestações e Linhas de Transmissão</t>
-        </is>
-      </c>
-      <c r="K300" t="inlineStr">
-        <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="N300" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="O300" t="inlineStr">
-        <is>
-          <t>Região Intermediária de Uberaba</t>
-        </is>
-      </c>
-      <c r="P300" t="inlineStr">
-        <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERABA</t>
-        </is>
-      </c>
-      <c r="Q300" t="n">
-        <v>0</v>
-      </c>
-      <c r="R300" t="n">
-        <v>24622611</v>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" t="n">
-        <v>5391</v>
-      </c>
-      <c r="B301" t="n">
-        <v>25</v>
-      </c>
-      <c r="C301" t="n">
-        <v>752</v>
-      </c>
-      <c r="D301" t="n">
-        <v>94</v>
-      </c>
-      <c r="E301" t="n">
-        <v>3001</v>
-      </c>
-      <c r="F301" t="n">
-        <v>1</v>
-      </c>
-      <c r="G301" t="n">
-        <v>0</v>
-      </c>
-      <c r="H301" t="n">
-        <v>300</v>
-      </c>
-      <c r="J301" t="inlineStr">
-        <is>
-          <t>Expansão do Sistema de Geração</t>
-        </is>
-      </c>
-      <c r="K301" t="inlineStr">
-        <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="N301" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="O301" t="inlineStr">
-        <is>
-          <t>Estadual</t>
-        </is>
-      </c>
-      <c r="P301" t="inlineStr">
-        <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
-        </is>
-      </c>
-      <c r="Q301" t="n">
-        <v>0</v>
-      </c>
-      <c r="R301" t="n">
         <v>1</v>
       </c>
     </row>

--- a/bancos/SISOR/BASE_DETALHAMENTO_OBRAS.xlsx
+++ b/bancos/SISOR/BASE_DETALHAMENTO_OBRAS.xlsx
@@ -16362,7 +16362,7 @@
         <v>0</v>
       </c>
       <c r="R268" t="n">
-        <v>1</v>
+        <v>1000</v>
       </c>
     </row>
   </sheetData>

--- a/bancos/SISOR/BASE_DETALHAMENTO_OBRAS.xlsx
+++ b/bancos/SISOR/BASE_DETALHAMENTO_OBRAS.xlsx
@@ -884,10 +884,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
         <v>60000</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -952,10 +952,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
         <v>197857</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1020,10 +1020,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
         <v>1929103</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1088,10 +1088,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
         <v>1929103</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1156,10 +1156,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
         <v>41022</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1224,10 +1224,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
         <v>100000</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -4824,10 +4824,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>280106</v>
+        <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>519640</v>
+        <v>799746</v>
       </c>
     </row>
     <row r="73">
@@ -4884,10 +4884,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>894720</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>4087644</v>
+        <v>4982364</v>
       </c>
     </row>
     <row r="74">
@@ -4944,10 +4944,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>8264640</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>19153735</v>
+        <v>27418375</v>
       </c>
     </row>
     <row r="75">
@@ -5004,10 +5004,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>3155040</v>
+        <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>23943007</v>
+        <v>27098047</v>
       </c>
     </row>
     <row r="76">
@@ -5064,10 +5064,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>4840800</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>26593690</v>
+        <v>31434490</v>
       </c>
     </row>
     <row r="77">
@@ -5124,10 +5124,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>613500</v>
+        <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>2870210</v>
+        <v>3483710</v>
       </c>
     </row>
     <row r="78">
@@ -5184,10 +5184,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>5963400</v>
+        <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>23280000</v>
+        <v>29243400</v>
       </c>
     </row>
     <row r="79">
@@ -5244,10 +5244,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>3620820</v>
+        <v>0</v>
       </c>
       <c r="R79" t="n">
-        <v>19100000</v>
+        <v>22720820</v>
       </c>
     </row>
     <row r="80">
@@ -5361,10 +5361,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>1839798</v>
+        <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>3269655</v>
+        <v>5109453</v>
       </c>
     </row>
     <row r="82">
@@ -5421,10 +5421,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
+        <v>0</v>
+      </c>
+      <c r="R82" t="n">
         <v>222899</v>
-      </c>
-      <c r="R82" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -6429,10 +6429,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
+        <v>0</v>
+      </c>
+      <c r="R99" t="n">
         <v>299895</v>
-      </c>
-      <c r="R99" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -6489,10 +6489,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
+        <v>0</v>
+      </c>
+      <c r="R100" t="n">
         <v>4565604</v>
-      </c>
-      <c r="R100" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -6549,10 +6549,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>6286532</v>
+        <v>0</v>
       </c>
       <c r="R101" t="n">
-        <v>2728583</v>
+        <v>9015115</v>
       </c>
     </row>
     <row r="102">
@@ -6609,10 +6609,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
+        <v>0</v>
+      </c>
+      <c r="R102" t="n">
         <v>193263</v>
-      </c>
-      <c r="R102" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -6780,10 +6780,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>904245</v>
+        <v>0</v>
       </c>
       <c r="R105" t="n">
-        <v>44308050</v>
+        <v>45212295</v>
       </c>
     </row>
     <row r="106">
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
+        <v>0</v>
+      </c>
+      <c r="R106" t="n">
         <v>6999284</v>
-      </c>
-      <c r="R106" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -6894,10 +6894,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
+        <v>0</v>
+      </c>
+      <c r="R107" t="n">
         <v>651694</v>
-      </c>
-      <c r="R107" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -6951,10 +6951,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
+        <v>0</v>
+      </c>
+      <c r="R108" t="n">
         <v>651694</v>
-      </c>
-      <c r="R108" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -7008,10 +7008,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
+        <v>0</v>
+      </c>
+      <c r="R109" t="n">
         <v>1472757</v>
-      </c>
-      <c r="R109" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -7065,10 +7065,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
+        <v>0</v>
+      </c>
+      <c r="R110" t="n">
         <v>651694</v>
-      </c>
-      <c r="R110" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -7122,10 +7122,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
+        <v>0</v>
+      </c>
+      <c r="R111" t="n">
         <v>18572878</v>
-      </c>
-      <c r="R111" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -7643,10 +7643,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="R120" t="n">
-        <v>19850000</v>
+        <v>20000000</v>
       </c>
     </row>
     <row r="121">
@@ -7945,10 +7945,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
+        <v>0</v>
+      </c>
+      <c r="R125" t="n">
         <v>350000</v>
-      </c>
-      <c r="R125" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -8010,10 +8010,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
+        <v>0</v>
+      </c>
+      <c r="R126" t="n">
         <v>1000000</v>
-      </c>
-      <c r="R126" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -8700,10 +8700,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
+        <v>0</v>
+      </c>
+      <c r="R138" t="n">
         <v>1000000</v>
-      </c>
-      <c r="R138" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="139">
@@ -8757,10 +8757,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
+        <v>0</v>
+      </c>
+      <c r="R139" t="n">
         <v>143000</v>
-      </c>
-      <c r="R139" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="140">
@@ -8814,10 +8814,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
+        <v>0</v>
+      </c>
+      <c r="R140" t="n">
         <v>5876140</v>
-      </c>
-      <c r="R140" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="141">
@@ -8871,10 +8871,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
+        <v>0</v>
+      </c>
+      <c r="R141" t="n">
         <v>1132500</v>
-      </c>
-      <c r="R141" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="142">
@@ -8928,10 +8928,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
+        <v>0</v>
+      </c>
+      <c r="R142" t="n">
         <v>34710000</v>
-      </c>
-      <c r="R142" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="143">
@@ -8985,10 +8985,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
+        <v>0</v>
+      </c>
+      <c r="R143" t="n">
         <v>59000000</v>
-      </c>
-      <c r="R143" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="144">
@@ -9042,10 +9042,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
+        <v>0</v>
+      </c>
+      <c r="R144" t="n">
         <v>1000000</v>
-      </c>
-      <c r="R144" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="145">
@@ -9099,10 +9099,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
+        <v>0</v>
+      </c>
+      <c r="R145" t="n">
         <v>200000</v>
-      </c>
-      <c r="R145" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="146">
@@ -9156,10 +9156,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
+        <v>0</v>
+      </c>
+      <c r="R146" t="n">
         <v>30980000</v>
-      </c>
-      <c r="R146" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="147">
@@ -9213,10 +9213,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
+        <v>0</v>
+      </c>
+      <c r="R147" t="n">
         <v>25655000</v>
-      </c>
-      <c r="R147" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="148">
@@ -9270,10 +9270,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
+        <v>0</v>
+      </c>
+      <c r="R148" t="n">
         <v>66560000</v>
-      </c>
-      <c r="R148" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="149">
@@ -9327,10 +9327,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
+        <v>0</v>
+      </c>
+      <c r="R149" t="n">
         <v>25464500</v>
-      </c>
-      <c r="R149" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="150">
@@ -9384,10 +9384,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
+        <v>0</v>
+      </c>
+      <c r="R150" t="n">
         <v>1202905</v>
-      </c>
-      <c r="R150" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="151">
@@ -9441,10 +9441,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
+        <v>0</v>
+      </c>
+      <c r="R151" t="n">
         <v>1000000</v>
-      </c>
-      <c r="R151" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="152">
@@ -9498,10 +9498,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
+        <v>0</v>
+      </c>
+      <c r="R152" t="n">
         <v>14920000</v>
-      </c>
-      <c r="R152" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="153">
@@ -9555,10 +9555,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
+        <v>0</v>
+      </c>
+      <c r="R153" t="n">
         <v>8798400</v>
-      </c>
-      <c r="R153" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="154">
@@ -9612,10 +9612,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
+        <v>0</v>
+      </c>
+      <c r="R154" t="n">
         <v>1000000</v>
-      </c>
-      <c r="R154" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="155">
@@ -9669,10 +9669,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
+        <v>0</v>
+      </c>
+      <c r="R155" t="n">
         <v>1203643</v>
-      </c>
-      <c r="R155" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="156">
@@ -9726,10 +9726,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
+        <v>0</v>
+      </c>
+      <c r="R156" t="n">
         <v>66620</v>
-      </c>
-      <c r="R156" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="157">
@@ -9783,10 +9783,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
+        <v>0</v>
+      </c>
+      <c r="R157" t="n">
         <v>1000000</v>
-      </c>
-      <c r="R157" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="158">
@@ -9840,10 +9840,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
+        <v>0</v>
+      </c>
+      <c r="R158" t="n">
         <v>2940000</v>
-      </c>
-      <c r="R158" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="159">
@@ -9897,10 +9897,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
+        <v>0</v>
+      </c>
+      <c r="R159" t="n">
         <v>1000000</v>
-      </c>
-      <c r="R159" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="160">
@@ -9954,10 +9954,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
+        <v>0</v>
+      </c>
+      <c r="R160" t="n">
         <v>542000</v>
-      </c>
-      <c r="R160" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="161">
@@ -10011,10 +10011,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
+        <v>0</v>
+      </c>
+      <c r="R161" t="n">
         <v>2163814</v>
-      </c>
-      <c r="R161" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="162">
@@ -10068,10 +10068,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
+        <v>0</v>
+      </c>
+      <c r="R162" t="n">
         <v>11974837</v>
-      </c>
-      <c r="R162" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="163">
@@ -10125,10 +10125,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
+        <v>0</v>
+      </c>
+      <c r="R163" t="n">
         <v>1382535</v>
-      </c>
-      <c r="R163" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="164">
@@ -10182,10 +10182,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
+        <v>0</v>
+      </c>
+      <c r="R164" t="n">
         <v>1000000</v>
-      </c>
-      <c r="R164" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="165">
@@ -10239,10 +10239,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
+        <v>0</v>
+      </c>
+      <c r="R165" t="n">
         <v>35359853</v>
-      </c>
-      <c r="R165" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="166">
@@ -10296,10 +10296,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
+        <v>0</v>
+      </c>
+      <c r="R166" t="n">
         <v>13982612</v>
-      </c>
-      <c r="R166" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="167">
@@ -10353,10 +10353,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
+        <v>0</v>
+      </c>
+      <c r="R167" t="n">
         <v>1000000</v>
-      </c>
-      <c r="R167" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="168">
@@ -10410,10 +10410,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
+        <v>0</v>
+      </c>
+      <c r="R168" t="n">
         <v>10459632</v>
-      </c>
-      <c r="R168" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="169">
@@ -10467,10 +10467,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
+        <v>0</v>
+      </c>
+      <c r="R169" t="n">
         <v>17000000</v>
-      </c>
-      <c r="R169" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="170">
@@ -10524,10 +10524,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
+        <v>0</v>
+      </c>
+      <c r="R170" t="n">
         <v>74941121</v>
-      </c>
-      <c r="R170" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="171">
@@ -10581,10 +10581,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
+        <v>0</v>
+      </c>
+      <c r="R171" t="n">
         <v>38460000</v>
-      </c>
-      <c r="R171" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="172">
@@ -10638,10 +10638,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
+        <v>0</v>
+      </c>
+      <c r="R172" t="n">
         <v>1000000</v>
-      </c>
-      <c r="R172" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="173">
@@ -10695,10 +10695,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
+        <v>0</v>
+      </c>
+      <c r="R173" t="n">
         <v>7000000</v>
-      </c>
-      <c r="R173" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="174">
@@ -10752,10 +10752,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
+        <v>0</v>
+      </c>
+      <c r="R174" t="n">
         <v>1000000</v>
-      </c>
-      <c r="R174" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="175">
@@ -11265,10 +11265,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
+        <v>0</v>
+      </c>
+      <c r="R183" t="n">
         <v>100000</v>
-      </c>
-      <c r="R183" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="184">
@@ -11322,10 +11322,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
+        <v>0</v>
+      </c>
+      <c r="R184" t="n">
         <v>6121132</v>
-      </c>
-      <c r="R184" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="185">
@@ -11379,10 +11379,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
+        <v>0</v>
+      </c>
+      <c r="R185" t="n">
         <v>3541728</v>
-      </c>
-      <c r="R185" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="186">
@@ -11436,10 +11436,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
+        <v>0</v>
+      </c>
+      <c r="R186" t="n">
         <v>22254062</v>
-      </c>
-      <c r="R186" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="187">
@@ -11493,10 +11493,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
+        <v>0</v>
+      </c>
+      <c r="R187" t="n">
         <v>1000000</v>
-      </c>
-      <c r="R187" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="188">
@@ -11550,10 +11550,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
+        <v>0</v>
+      </c>
+      <c r="R188" t="n">
         <v>1000000</v>
-      </c>
-      <c r="R188" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="189">
@@ -11607,10 +11607,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
+        <v>0</v>
+      </c>
+      <c r="R189" t="n">
         <v>431809</v>
-      </c>
-      <c r="R189" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="190">
@@ -11664,10 +11664,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
+        <v>0</v>
+      </c>
+      <c r="R190" t="n">
         <v>1000000</v>
-      </c>
-      <c r="R190" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="191">
@@ -11721,10 +11721,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
+        <v>0</v>
+      </c>
+      <c r="R191" t="n">
         <v>14356790</v>
-      </c>
-      <c r="R191" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="192">
@@ -11778,10 +11778,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
+        <v>0</v>
+      </c>
+      <c r="R192" t="n">
         <v>1000</v>
-      </c>
-      <c r="R192" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="193">
@@ -11835,10 +11835,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
+        <v>0</v>
+      </c>
+      <c r="R193" t="n">
         <v>1000</v>
-      </c>
-      <c r="R193" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="194">
@@ -12291,10 +12291,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
+        <v>0</v>
+      </c>
+      <c r="R201" t="n">
         <v>50000000</v>
-      </c>
-      <c r="R201" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="202">
@@ -12348,10 +12348,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
+        <v>0</v>
+      </c>
+      <c r="R202" t="n">
         <v>8151612</v>
-      </c>
-      <c r="R202" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="203">
@@ -12405,10 +12405,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
+        <v>0</v>
+      </c>
+      <c r="R203" t="n">
         <v>7488179</v>
-      </c>
-      <c r="R203" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="204">
@@ -12462,10 +12462,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
+        <v>0</v>
+      </c>
+      <c r="R204" t="n">
         <v>9608804</v>
-      </c>
-      <c r="R204" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="205">
@@ -12519,10 +12519,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
+        <v>0</v>
+      </c>
+      <c r="R205" t="n">
         <v>8168067</v>
-      </c>
-      <c r="R205" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="206">
@@ -12576,10 +12576,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
+        <v>0</v>
+      </c>
+      <c r="R206" t="n">
         <v>571386707</v>
-      </c>
-      <c r="R206" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="207">
@@ -12633,10 +12633,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
+        <v>0</v>
+      </c>
+      <c r="R207" t="n">
         <v>15000000</v>
-      </c>
-      <c r="R207" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="208">
@@ -12690,10 +12690,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
+        <v>0</v>
+      </c>
+      <c r="R208" t="n">
         <v>1406178</v>
-      </c>
-      <c r="R208" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="209">
@@ -12747,10 +12747,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
+        <v>0</v>
+      </c>
+      <c r="R209" t="n">
         <v>19448656</v>
-      </c>
-      <c r="R209" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="210">
@@ -12804,10 +12804,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
+        <v>0</v>
+      </c>
+      <c r="R210" t="n">
         <v>1000000</v>
-      </c>
-      <c r="R210" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="211">
@@ -12861,10 +12861,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
+        <v>0</v>
+      </c>
+      <c r="R211" t="n">
         <v>30000000</v>
-      </c>
-      <c r="R211" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="212">
@@ -12918,10 +12918,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
+        <v>0</v>
+      </c>
+      <c r="R212" t="n">
         <v>1000000</v>
-      </c>
-      <c r="R212" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="213">
@@ -12975,10 +12975,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
+        <v>0</v>
+      </c>
+      <c r="R213" t="n">
         <v>4000000</v>
-      </c>
-      <c r="R213" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="214">
@@ -13032,10 +13032,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
+        <v>0</v>
+      </c>
+      <c r="R214" t="n">
         <v>4000000</v>
-      </c>
-      <c r="R214" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="215">
@@ -13089,10 +13089,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
+        <v>0</v>
+      </c>
+      <c r="R215" t="n">
         <v>1000000</v>
-      </c>
-      <c r="R215" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="216">
@@ -13442,10 +13442,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
+        <v>0</v>
+      </c>
+      <c r="R221" t="n">
         <v>8311374</v>
-      </c>
-      <c r="R221" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="222">
@@ -13499,10 +13499,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
+        <v>0</v>
+      </c>
+      <c r="R222" t="n">
         <v>477508</v>
-      </c>
-      <c r="R222" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="223">
